--- a/Data/Default_Template.xlsx
+++ b/Data/Default_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PONDERATION" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="615">
   <si>
     <t>Cybersecurity Governance &amp; Protection</t>
   </si>
@@ -2012,6 +2012,9 @@
   <si>
     <t>Dhia</t>
   </si>
+  <si>
+    <t>Question</t>
+  </si>
 </sst>
 </file>
 
@@ -2020,7 +2023,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2144,6 +2147,13 @@
     </font>
     <font>
       <sz val="36"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2567,7 +2577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2984,43 +2994,97 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3040,58 +3104,7 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3103,7 +3116,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3115,247 +3134,119 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="53">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <u val="double"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
       <border>
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <u val="double"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
       <border>
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <u val="double"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
       <border>
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <u val="double"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -4287,7 +4178,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5364,10 +5255,10 @@
     </row>
     <row r="2" spans="1:22" ht="97.5" customHeight="1" thickBot="1">
       <c r="A2" s="50"/>
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="156" t="s">
+      <c r="C2" s="154" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -5420,8 +5311,8 @@
     </row>
     <row r="3" spans="1:22" ht="81" customHeight="1">
       <c r="A3" s="50"/>
-      <c r="B3" s="153"/>
-      <c r="C3" s="156"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="154"/>
       <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
@@ -5457,7 +5348,7 @@
     </row>
     <row r="4" spans="1:22" ht="79.95" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="153"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
@@ -5495,7 +5386,7 @@
     </row>
     <row r="5" spans="1:22" ht="87" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="153"/>
+      <c r="B5" s="150"/>
       <c r="C5" s="3" t="s">
         <v>283</v>
       </c>
@@ -5531,8 +5422,8 @@
     </row>
     <row r="6" spans="1:22" ht="91.05" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="157" t="s">
+      <c r="B6" s="150"/>
+      <c r="C6" s="155" t="s">
         <v>293</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -5561,27 +5452,27 @@
     </row>
     <row r="7" spans="1:22" ht="43.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="153"/>
-      <c r="C7" s="158"/>
-      <c r="D7" s="151" t="s">
+      <c r="B7" s="150"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="149" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="154" t="s">
+      <c r="E7" s="152" t="s">
         <v>456</v>
       </c>
-      <c r="F7" s="154" t="s">
+      <c r="F7" s="152" t="s">
         <v>457</v>
       </c>
-      <c r="G7" s="154" t="s">
+      <c r="G7" s="152" t="s">
         <v>458</v>
       </c>
-      <c r="H7" s="154" t="s">
+      <c r="H7" s="152" t="s">
         <v>302</v>
       </c>
       <c r="I7" s="81" t="s">
         <v>555</v>
       </c>
-      <c r="J7" s="151" t="s">
+      <c r="J7" s="149" t="s">
         <v>273</v>
       </c>
       <c r="K7" s="50"/>
@@ -5589,23 +5480,23 @@
     </row>
     <row r="8" spans="1:22" ht="43.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="153"/>
-      <c r="C8" s="158"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="155"/>
-      <c r="F8" s="155"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
       <c r="I8" s="82"/>
-      <c r="J8" s="152"/>
+      <c r="J8" s="151"/>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
     </row>
     <row r="9" spans="1:22" ht="49.95" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="153"/>
-      <c r="C9" s="158"/>
-      <c r="D9" s="152"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="156"/>
+      <c r="D9" s="151"/>
       <c r="E9" s="24" t="s">
         <v>459</v>
       </c>
@@ -5629,9 +5520,9 @@
     </row>
     <row r="10" spans="1:22" ht="43.5" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="153"/>
-      <c r="C10" s="158"/>
-      <c r="D10" s="151" t="s">
+      <c r="B10" s="150"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="149" t="s">
         <v>288</v>
       </c>
       <c r="E10" s="24" t="s">
@@ -5657,25 +5548,25 @@
     </row>
     <row r="11" spans="1:22" ht="43.5" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="153"/>
-      <c r="C11" s="158"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="154" t="s">
+      <c r="B11" s="150"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="152" t="s">
         <v>465</v>
       </c>
-      <c r="F11" s="154" t="s">
+      <c r="F11" s="152" t="s">
         <v>466</v>
       </c>
-      <c r="G11" s="154" t="s">
+      <c r="G11" s="152" t="s">
         <v>467</v>
       </c>
-      <c r="H11" s="154" t="s">
+      <c r="H11" s="152" t="s">
         <v>295</v>
       </c>
       <c r="I11" s="81" t="s">
         <v>558</v>
       </c>
-      <c r="J11" s="151" t="s">
+      <c r="J11" s="149" t="s">
         <v>275</v>
       </c>
       <c r="K11" s="50"/>
@@ -5683,23 +5574,23 @@
     </row>
     <row r="12" spans="1:22" ht="43.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="153"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="155"/>
-      <c r="F12" s="155"/>
-      <c r="G12" s="155"/>
-      <c r="H12" s="155"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
       <c r="I12" s="82"/>
-      <c r="J12" s="152"/>
+      <c r="J12" s="151"/>
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
     </row>
     <row r="13" spans="1:22" ht="43.2">
       <c r="A13" s="50"/>
-      <c r="B13" s="153"/>
-      <c r="C13" s="158"/>
-      <c r="D13" s="151" t="s">
+      <c r="B13" s="150"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="149" t="s">
         <v>289</v>
       </c>
       <c r="E13" s="42" t="s">
@@ -5725,9 +5616,9 @@
     </row>
     <row r="14" spans="1:22" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="153"/>
-      <c r="C14" s="158"/>
-      <c r="D14" s="153"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="150"/>
       <c r="E14" s="42" t="s">
         <v>469</v>
       </c>
@@ -5751,9 +5642,9 @@
     </row>
     <row r="15" spans="1:22" ht="51" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="153"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="152"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="151"/>
       <c r="E15" s="42" t="s">
         <v>470</v>
       </c>
@@ -5777,27 +5668,27 @@
     </row>
     <row r="16" spans="1:22" ht="47.55" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="153"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="151" t="s">
+      <c r="B16" s="150"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="149" t="s">
         <v>290</v>
       </c>
-      <c r="E16" s="154" t="s">
+      <c r="E16" s="152" t="s">
         <v>477</v>
       </c>
-      <c r="F16" s="154" t="s">
+      <c r="F16" s="152" t="s">
         <v>478</v>
       </c>
-      <c r="G16" s="154" t="s">
+      <c r="G16" s="152" t="s">
         <v>479</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="152" t="s">
         <v>301</v>
       </c>
       <c r="I16" s="81" t="s">
         <v>562</v>
       </c>
-      <c r="J16" s="151" t="s">
+      <c r="J16" s="149" t="s">
         <v>275</v>
       </c>
       <c r="K16" s="50"/>
@@ -5805,37 +5696,37 @@
     </row>
     <row r="17" spans="1:12" ht="22.05" hidden="1" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="161"/>
-      <c r="F17" s="161"/>
-      <c r="G17" s="161"/>
-      <c r="H17" s="161"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="159"/>
+      <c r="F17" s="159"/>
+      <c r="G17" s="159"/>
+      <c r="H17" s="159"/>
       <c r="I17" s="83"/>
-      <c r="J17" s="153"/>
+      <c r="J17" s="150"/>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="50"/>
-      <c r="B18" s="153"/>
-      <c r="C18" s="158"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="155"/>
+      <c r="B18" s="150"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="153"/>
       <c r="I18" s="82"/>
-      <c r="J18" s="152"/>
+      <c r="J18" s="151"/>
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
     </row>
     <row r="19" spans="1:12" ht="61.95" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="153"/>
-      <c r="C19" s="158"/>
-      <c r="D19" s="151" t="s">
+      <c r="B19" s="150"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="149" t="s">
         <v>291</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -5861,23 +5752,23 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="50"/>
-      <c r="B20" s="153"/>
-      <c r="C20" s="158"/>
-      <c r="D20" s="153"/>
-      <c r="E20" s="154" t="s">
+      <c r="B20" s="150"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="152" t="s">
         <v>481</v>
       </c>
-      <c r="F20" s="154" t="s">
+      <c r="F20" s="152" t="s">
         <v>485</v>
       </c>
-      <c r="G20" s="149" t="s">
+      <c r="G20" s="160" t="s">
         <v>489</v>
       </c>
-      <c r="H20" s="154" t="s">
+      <c r="H20" s="152" t="s">
         <v>300</v>
       </c>
       <c r="I20" s="81"/>
-      <c r="J20" s="151" t="s">
+      <c r="J20" s="149" t="s">
         <v>275</v>
       </c>
       <c r="K20" s="50"/>
@@ -5885,25 +5776,25 @@
     </row>
     <row r="21" spans="1:12" ht="28.95" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="153"/>
-      <c r="C21" s="158"/>
-      <c r="D21" s="153"/>
-      <c r="E21" s="155"/>
-      <c r="F21" s="155"/>
-      <c r="G21" s="150"/>
-      <c r="H21" s="155"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="161"/>
+      <c r="H21" s="153"/>
       <c r="I21" s="82" t="s">
         <v>564</v>
       </c>
-      <c r="J21" s="152"/>
+      <c r="J21" s="151"/>
       <c r="K21" s="50"/>
       <c r="L21" s="50"/>
     </row>
     <row r="22" spans="1:12" ht="39.450000000000003" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="153"/>
-      <c r="C22" s="158"/>
-      <c r="D22" s="153"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="150"/>
       <c r="E22" s="24" t="s">
         <v>482</v>
       </c>
@@ -5927,27 +5818,27 @@
     </row>
     <row r="23" spans="1:12" ht="42" customHeight="1">
       <c r="A23" s="50"/>
-      <c r="B23" s="153"/>
-      <c r="C23" s="158"/>
-      <c r="D23" s="156" t="s">
+      <c r="B23" s="150"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="154" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="154" t="s">
+      <c r="E23" s="152" t="s">
         <v>483</v>
       </c>
-      <c r="F23" s="160" t="s">
+      <c r="F23" s="158" t="s">
         <v>487</v>
       </c>
-      <c r="G23" s="154" t="s">
+      <c r="G23" s="152" t="s">
         <v>491</v>
       </c>
-      <c r="H23" s="154" t="s">
+      <c r="H23" s="152" t="s">
         <v>299</v>
       </c>
       <c r="I23" s="81" t="s">
         <v>566</v>
       </c>
-      <c r="J23" s="151" t="s">
+      <c r="J23" s="149" t="s">
         <v>275</v>
       </c>
       <c r="K23" s="50"/>
@@ -5955,15 +5846,15 @@
     </row>
     <row r="24" spans="1:12" ht="28.95" customHeight="1">
       <c r="A24" s="50"/>
-      <c r="B24" s="152"/>
-      <c r="C24" s="159"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="155"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="154"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="158"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="153"/>
       <c r="I24" s="82"/>
-      <c r="J24" s="152"/>
+      <c r="J24" s="151"/>
       <c r="K24" s="50"/>
       <c r="L24" s="50"/>
     </row>
@@ -5997,16 +5888,14 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="D19:D22"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="C6:C24"/>
@@ -6023,39 +5912,41 @@
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:E1">
-    <cfRule type="expression" dxfId="64" priority="9">
+    <cfRule type="expression" dxfId="52" priority="9">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J1">
-    <cfRule type="expression" dxfId="63" priority="5">
+    <cfRule type="expression" dxfId="51" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="6">
+    <cfRule type="expression" dxfId="50" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J7 J9:J11 J13:J16 J19:J20 J22:J23">
-    <cfRule type="cellIs" dxfId="61" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6076,7 +5967,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24.21875" customWidth="1"/>
@@ -6094,9 +5985,11 @@
     <col min="16" max="16" width="19" customWidth="1"/>
     <col min="17" max="17" width="20.88671875" customWidth="1"/>
     <col min="18" max="18" width="38.5546875" customWidth="1"/>
+    <col min="22" max="22" width="62.6640625" customWidth="1"/>
+    <col min="23" max="23" width="37.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25.05" customHeight="1" thickBot="1">
+    <row r="1" spans="1:23" ht="25.05" customHeight="1" thickBot="1">
       <c r="A1" s="59"/>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -6117,22 +6010,22 @@
       <c r="R1" s="59"/>
       <c r="S1" s="59"/>
     </row>
-    <row r="2" spans="1:19" ht="21.45" customHeight="1" thickBot="1">
-      <c r="A2" s="175"/>
-      <c r="B2" s="176"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="176"/>
+    <row r="2" spans="1:23" ht="21.45" customHeight="1" thickBot="1">
+      <c r="A2" s="168"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
       <c r="I2" s="53"/>
-      <c r="J2" s="175"/>
-      <c r="K2" s="175"/>
-      <c r="L2" s="178" t="s">
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="172" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="179"/>
+      <c r="M2" s="173"/>
       <c r="N2" s="58" t="s">
         <v>275</v>
       </c>
@@ -6150,8 +6043,8 @@
       </c>
       <c r="S2" s="59"/>
     </row>
-    <row r="3" spans="1:19" ht="28.05" customHeight="1">
-      <c r="A3" s="175"/>
+    <row r="3" spans="1:23" ht="28.05" customHeight="1">
+      <c r="A3" s="168"/>
       <c r="B3" s="43" t="s">
         <v>148</v>
       </c>
@@ -6176,109 +6069,125 @@
       <c r="I3" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
-      <c r="L3" s="169">
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
+      <c r="L3" s="162">
         <f>COUNTA(I4:I13)</f>
         <v>4</v>
       </c>
-      <c r="M3" s="180"/>
-      <c r="N3" s="183">
+      <c r="M3" s="174"/>
+      <c r="N3" s="177">
         <f>COUNTIF(I4:I12,"Yes")</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="162">
+        <v>1</v>
+      </c>
+      <c r="O3" s="180">
         <f>COUNTIF(I4:I12,"No")</f>
-        <v>4</v>
-      </c>
-      <c r="P3" s="165">
+        <v>3</v>
+      </c>
+      <c r="P3" s="183">
         <f>COUNTIF(I4:I12,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="169">
+      <c r="Q3" s="162">
         <f>L3-P3</f>
         <v>4</v>
       </c>
-      <c r="R3" s="172">
+      <c r="R3" s="165">
         <f>N3/Q3</f>
+        <v>0.25</v>
+      </c>
+      <c r="S3" s="59"/>
+      <c r="V3" s="56" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="93.6" customHeight="1">
+      <c r="A4" s="168"/>
+      <c r="B4" s="149" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="59"/>
-    </row>
-    <row r="4" spans="1:19" ht="73.95" customHeight="1">
-      <c r="A4" s="175"/>
-      <c r="B4" s="151" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="151" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="160" t="s">
+      <c r="D4" s="158" t="s">
         <v>228</v>
       </c>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="158" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="154" t="s">
+      <c r="F4" s="152" t="s">
         <v>249</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="168" t="s">
+      <c r="H4" s="171" t="s">
         <v>262</v>
       </c>
-      <c r="I4" s="156" t="s">
+      <c r="I4" s="154" t="s">
         <v>273</v>
       </c>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="170"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="184"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="166"/>
-      <c r="Q4" s="170"/>
-      <c r="R4" s="173"/>
+      <c r="J4" s="168"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="178"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="184"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="166"/>
       <c r="S4" s="59"/>
-    </row>
-    <row r="5" spans="1:19" ht="78" customHeight="1" thickBot="1">
-      <c r="A5" s="175"/>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="160"/>
-      <c r="F5" s="161"/>
+      <c r="V4" s="212" t="str">
+        <f>IF(I4="No",H4,"")</f>
+        <v>Pouvez-vous fournir les rapports d’audit réalisés au cours des 12 derniers mois, ainsi que les preuves de leur dépôt auprès de l’ANSI ?</v>
+      </c>
+      <c r="W4" s="212"/>
+    </row>
+    <row r="5" spans="1:23" ht="78" customHeight="1" thickBot="1">
+      <c r="A5" s="168"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="159"/>
       <c r="G5" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="168"/>
-      <c r="I5" s="156"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="185"/>
-      <c r="O5" s="164"/>
-      <c r="P5" s="167"/>
-      <c r="Q5" s="171"/>
-      <c r="R5" s="174"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="168"/>
+      <c r="K5" s="168"/>
+      <c r="L5" s="164"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="182"/>
+      <c r="P5" s="185"/>
+      <c r="Q5" s="164"/>
+      <c r="R5" s="167"/>
       <c r="S5" s="59"/>
-    </row>
-    <row r="6" spans="1:19" ht="72.599999999999994" thickBot="1">
-      <c r="A6" s="175"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="155"/>
+      <c r="V5" s="212" t="str">
+        <f t="shared" ref="V5:V11" si="0">IF(I5="No",H5,"")</f>
+        <v/>
+      </c>
+      <c r="W5" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W5))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="105.6" thickBot="1">
+      <c r="A6" s="168"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="153"/>
       <c r="G6" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="H6" s="168"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="175"/>
-      <c r="K6" s="175"/>
+      <c r="H6" s="171"/>
+      <c r="I6" s="154"/>
+      <c r="J6" s="168"/>
+      <c r="K6" s="168"/>
       <c r="L6" s="59"/>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -6287,11 +6196,19 @@
       <c r="Q6" s="59"/>
       <c r="R6" s="59"/>
       <c r="S6" s="59"/>
-    </row>
-    <row r="7" spans="1:19" ht="109.05" customHeight="1" thickBot="1">
-      <c r="A7" s="175"/>
-      <c r="B7" s="153"/>
-      <c r="C7" s="153"/>
+      <c r="V6" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W6" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W6))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="109.05" customHeight="1" thickBot="1">
+      <c r="A7" s="168"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
       <c r="D7" s="24" t="s">
         <v>234</v>
       </c>
@@ -6304,14 +6221,14 @@
       <c r="G7" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="168" t="s">
+      <c r="H7" s="171" t="s">
         <v>263</v>
       </c>
-      <c r="I7" s="156" t="s">
+      <c r="I7" s="154" t="s">
         <v>273</v>
       </c>
-      <c r="J7" s="175"/>
-      <c r="K7" s="175"/>
+      <c r="J7" s="168"/>
+      <c r="K7" s="168"/>
       <c r="L7" s="91" t="s">
         <v>611</v>
       </c>
@@ -6319,11 +6236,19 @@
         <v>612</v>
       </c>
       <c r="N7" s="113"/>
-    </row>
-    <row r="8" spans="1:19" ht="102" customHeight="1">
-      <c r="A8" s="175"/>
-      <c r="B8" s="153"/>
-      <c r="C8" s="153"/>
+      <c r="V7" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>Est-ce que vos équipements électroniques et logiciels, ainsi que vos fournisseurs de services cloud, possèdent respectivement les labels « Sécurisé » et « G-Cloud / N-Cloud » valides délivrés par l’ANSI ?</v>
+      </c>
+      <c r="W7" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W7))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="102" customHeight="1">
+      <c r="A8" s="168"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="150"/>
       <c r="D8" s="24" t="s">
         <v>235</v>
       </c>
@@ -6336,16 +6261,25 @@
       <c r="G8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="H8" s="168"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="175"/>
-      <c r="K8" s="175"/>
+      <c r="H8" s="171"/>
+      <c r="I8" s="154"/>
+      <c r="J8" s="168"/>
+      <c r="K8" s="168"/>
       <c r="N8" s="114"/>
-    </row>
-    <row r="9" spans="1:19" ht="252" customHeight="1">
-      <c r="A9" s="175"/>
-      <c r="B9" s="153"/>
-      <c r="C9" s="153"/>
+      <c r="Q8" s="211"/>
+      <c r="V8" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W8" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W8))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="252" customHeight="1">
+      <c r="A9" s="168"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="150"/>
       <c r="D9" s="24" t="s">
         <v>244</v>
       </c>
@@ -6358,19 +6292,27 @@
       <c r="G9" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H9" s="168" t="s">
+      <c r="H9" s="171" t="s">
         <v>265</v>
       </c>
-      <c r="I9" s="156" t="s">
-        <v>273</v>
-      </c>
-      <c r="J9" s="175"/>
-      <c r="K9" s="175"/>
-    </row>
-    <row r="10" spans="1:19" ht="139.05000000000001" customHeight="1">
-      <c r="A10" s="175"/>
-      <c r="B10" s="153"/>
-      <c r="C10" s="153"/>
+      <c r="I9" s="154" t="s">
+        <v>275</v>
+      </c>
+      <c r="J9" s="168"/>
+      <c r="K9" s="168"/>
+      <c r="V9" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W9" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W9))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="139.05000000000001" customHeight="1">
+      <c r="A10" s="168"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="150"/>
       <c r="D10" s="24" t="s">
         <v>248</v>
       </c>
@@ -6383,15 +6325,23 @@
       <c r="G10" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="168"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="175"/>
-      <c r="K10" s="175"/>
-    </row>
-    <row r="11" spans="1:19" ht="64.95" customHeight="1">
-      <c r="A11" s="175"/>
-      <c r="B11" s="152"/>
-      <c r="C11" s="152"/>
+      <c r="H10" s="171"/>
+      <c r="I10" s="154"/>
+      <c r="J10" s="168"/>
+      <c r="K10" s="168"/>
+      <c r="V10" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W10" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W10))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="64.95" customHeight="1">
+      <c r="A11" s="168"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="151"/>
       <c r="D11" s="24" t="s">
         <v>239</v>
       </c>
@@ -6410,37 +6360,59 @@
       <c r="I11" s="136" t="s">
         <v>273</v>
       </c>
-      <c r="J11" s="175"/>
-      <c r="K11" s="175"/>
-    </row>
-    <row r="12" spans="1:19">
-      <c r="A12" s="175"/>
-      <c r="B12" s="177"/>
-      <c r="C12" s="177"/>
-      <c r="D12" s="177"/>
-      <c r="E12" s="177"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="177"/>
+      <c r="J11" s="168"/>
+      <c r="K11" s="168"/>
+      <c r="V11" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>L’organisation possède-t-elle un niveau de sécurité délivré par l’ANSI ? Si oui, quel est ce niveau ?</v>
+      </c>
+      <c r="W11" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W11))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="21">
+      <c r="A12" s="168"/>
+      <c r="B12" s="170"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="170"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
       <c r="I12" s="53"/>
-      <c r="J12" s="175"/>
-      <c r="K12" s="175"/>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="A13" s="175"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="175"/>
+      <c r="J12" s="168"/>
+      <c r="K12" s="168"/>
+      <c r="V12" s="212" t="str">
+        <f t="shared" ref="V8:V12" si="1">IF(I9="No",H9,"")</f>
+        <v/>
+      </c>
+      <c r="W12" s="212" t="str">
+        <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W12))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="168"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="168"/>
+      <c r="D13" s="168"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="168"/>
+      <c r="G13" s="168"/>
+      <c r="H13" s="168"/>
       <c r="I13" s="53"/>
-      <c r="J13" s="175"/>
-      <c r="K13" s="175"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="H7:H8"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="B4:B11"/>
@@ -6457,33 +6429,35 @@
     <mergeCell ref="J2:K13"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="H7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:I3">
-    <cfRule type="expression" dxfId="57" priority="5">
+    <cfRule type="expression" dxfId="45" priority="7">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="6">
+    <cfRule type="expression" dxfId="44" priority="8">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I7 I9 I11">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
       <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V3">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$A3="header"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -6495,6 +6469,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6556,19 +6531,19 @@
       <c r="L1" s="95" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="186" t="s">
+      <c r="M1" s="187" t="s">
         <v>588</v>
       </c>
-      <c r="N1" s="187"/>
+      <c r="N1" s="188"/>
       <c r="O1" s="94" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="128.4" thickBot="1">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="154" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="160" t="s">
+      <c r="B2" s="158" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="24" t="s">
@@ -6637,8 +6612,8 @@
       <c r="AF2" s="90"/>
     </row>
     <row r="3" spans="1:32" ht="115.95" customHeight="1" thickBot="1">
-      <c r="A3" s="156"/>
-      <c r="B3" s="160"/>
+      <c r="A3" s="154"/>
+      <c r="B3" s="158"/>
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -6683,8 +6658,8 @@
       <c r="AC3" s="90"/>
     </row>
     <row r="4" spans="1:32" ht="87" customHeight="1" thickBot="1">
-      <c r="A4" s="156"/>
-      <c r="B4" s="160"/>
+      <c r="A4" s="154"/>
+      <c r="B4" s="158"/>
       <c r="C4" s="24" t="s">
         <v>72</v>
       </c>
@@ -6731,8 +6706,8 @@
       <c r="AC4" s="90"/>
     </row>
     <row r="5" spans="1:32" ht="126.45" customHeight="1">
-      <c r="A5" s="156"/>
-      <c r="B5" s="160"/>
+      <c r="A5" s="154"/>
+      <c r="B5" s="158"/>
       <c r="C5" s="68" t="s">
         <v>75</v>
       </c>
@@ -6773,8 +6748,8 @@
       <c r="AC5" s="90"/>
     </row>
     <row r="6" spans="1:32" ht="86.4">
-      <c r="A6" s="156"/>
-      <c r="B6" s="160"/>
+      <c r="A6" s="154"/>
+      <c r="B6" s="158"/>
       <c r="C6" s="24" t="s">
         <v>78</v>
       </c>
@@ -6813,8 +6788,8 @@
       <c r="AC6" s="90"/>
     </row>
     <row r="7" spans="1:32" ht="86.4">
-      <c r="A7" s="156"/>
-      <c r="B7" s="160"/>
+      <c r="A7" s="154"/>
+      <c r="B7" s="158"/>
       <c r="C7" s="24" t="s">
         <v>81</v>
       </c>
@@ -6853,11 +6828,11 @@
       <c r="AC7" s="90"/>
     </row>
     <row r="8" spans="1:32" ht="96.6">
-      <c r="A8" s="156"/>
-      <c r="B8" s="156" t="s">
+      <c r="A8" s="154"/>
+      <c r="B8" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="156" t="s">
+      <c r="C8" s="154" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -6895,9 +6870,9 @@
       <c r="AC8" s="90"/>
     </row>
     <row r="9" spans="1:32" ht="69">
-      <c r="A9" s="156"/>
-      <c r="B9" s="156"/>
-      <c r="C9" s="156"/>
+      <c r="A9" s="154"/>
+      <c r="B9" s="154"/>
+      <c r="C9" s="154"/>
       <c r="D9" s="31" t="s">
         <v>10</v>
       </c>
@@ -6933,9 +6908,9 @@
       <c r="AC9" s="90"/>
     </row>
     <row r="10" spans="1:32" ht="82.8">
-      <c r="A10" s="156"/>
-      <c r="B10" s="156"/>
-      <c r="C10" s="189"/>
+      <c r="A10" s="154"/>
+      <c r="B10" s="154"/>
+      <c r="C10" s="186"/>
       <c r="D10" s="31" t="s">
         <v>13</v>
       </c>
@@ -6971,9 +6946,9 @@
       <c r="AC10" s="90"/>
     </row>
     <row r="11" spans="1:32" ht="72">
-      <c r="A11" s="156"/>
-      <c r="B11" s="156"/>
-      <c r="C11" s="189"/>
+      <c r="A11" s="154"/>
+      <c r="B11" s="154"/>
+      <c r="C11" s="186"/>
       <c r="D11" s="31" t="s">
         <v>15</v>
       </c>
@@ -7009,8 +6984,8 @@
       <c r="AC11" s="90"/>
     </row>
     <row r="12" spans="1:32" ht="72">
-      <c r="A12" s="156"/>
-      <c r="B12" s="156"/>
+      <c r="A12" s="154"/>
+      <c r="B12" s="154"/>
       <c r="C12" s="3"/>
       <c r="D12" s="31" t="s">
         <v>20</v>
@@ -7047,8 +7022,8 @@
       <c r="AC12" s="90"/>
     </row>
     <row r="13" spans="1:32" ht="69">
-      <c r="A13" s="156"/>
-      <c r="B13" s="156"/>
+      <c r="A13" s="154"/>
+      <c r="B13" s="154"/>
       <c r="C13" s="3"/>
       <c r="D13" s="31" t="s">
         <v>22</v>
@@ -7085,8 +7060,8 @@
       <c r="AC13" s="90"/>
     </row>
     <row r="14" spans="1:32" ht="86.4">
-      <c r="A14" s="156"/>
-      <c r="B14" s="156"/>
+      <c r="A14" s="154"/>
+      <c r="B14" s="154"/>
       <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
@@ -7125,9 +7100,9 @@
       <c r="AC14" s="90"/>
     </row>
     <row r="15" spans="1:32" ht="82.8">
-      <c r="A15" s="156"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="189" t="s">
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="186" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="31" t="s">
@@ -7165,9 +7140,9 @@
       <c r="AC15" s="90"/>
     </row>
     <row r="16" spans="1:32" ht="72">
-      <c r="A16" s="156"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="189"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="186"/>
       <c r="D16" s="30" t="s">
         <v>52</v>
       </c>
@@ -7203,8 +7178,8 @@
       <c r="AC16" s="90"/>
     </row>
     <row r="17" spans="1:29" ht="100.8">
-      <c r="A17" s="156"/>
-      <c r="B17" s="156"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
@@ -7243,7 +7218,7 @@
       <c r="AC17" s="90"/>
     </row>
     <row r="18" spans="1:29" ht="86.4">
-      <c r="A18" s="156"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
@@ -7285,7 +7260,7 @@
       <c r="AC18" s="90"/>
     </row>
     <row r="19" spans="1:29" ht="115.2">
-      <c r="A19" s="156"/>
+      <c r="A19" s="154"/>
       <c r="B19" s="4" t="s">
         <v>38</v>
       </c>
@@ -7327,8 +7302,8 @@
       <c r="AC19" s="90"/>
     </row>
     <row r="20" spans="1:29" ht="115.2">
-      <c r="A20" s="156"/>
-      <c r="B20" s="156" t="s">
+      <c r="A20" s="154"/>
+      <c r="B20" s="154" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -7369,8 +7344,8 @@
       <c r="AC20" s="90"/>
     </row>
     <row r="21" spans="1:29" ht="86.4">
-      <c r="A21" s="156"/>
-      <c r="B21" s="156"/>
+      <c r="A21" s="154"/>
+      <c r="B21" s="154"/>
       <c r="C21" s="25" t="s">
         <v>51</v>
       </c>
@@ -7409,8 +7384,8 @@
       <c r="AC21" s="90"/>
     </row>
     <row r="22" spans="1:29" ht="100.8">
-      <c r="A22" s="156"/>
-      <c r="B22" s="156"/>
+      <c r="A22" s="154"/>
+      <c r="B22" s="154"/>
       <c r="C22" s="25" t="s">
         <v>54</v>
       </c>
@@ -7449,8 +7424,8 @@
       <c r="AC22" s="90"/>
     </row>
     <row r="23" spans="1:29" ht="115.2">
-      <c r="A23" s="156"/>
-      <c r="B23" s="156"/>
+      <c r="A23" s="154"/>
+      <c r="B23" s="154"/>
       <c r="C23" s="25" t="s">
         <v>56</v>
       </c>
@@ -7489,8 +7464,8 @@
       <c r="AC23" s="90"/>
     </row>
     <row r="24" spans="1:29" ht="69">
-      <c r="A24" s="156"/>
-      <c r="B24" s="156"/>
+      <c r="A24" s="154"/>
+      <c r="B24" s="154"/>
       <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
@@ -7529,8 +7504,8 @@
       <c r="AC24" s="90"/>
     </row>
     <row r="25" spans="1:29" ht="86.4">
-      <c r="A25" s="156"/>
-      <c r="B25" s="156"/>
+      <c r="A25" s="154"/>
+      <c r="B25" s="154"/>
       <c r="C25" s="4" t="s">
         <v>69</v>
       </c>
@@ -7569,8 +7544,8 @@
       <c r="AC25" s="90"/>
     </row>
     <row r="26" spans="1:29" ht="86.4">
-      <c r="A26" s="156"/>
-      <c r="B26" s="156"/>
+      <c r="A26" s="154"/>
+      <c r="B26" s="154"/>
       <c r="C26" s="4" t="s">
         <v>75</v>
       </c>
@@ -7609,9 +7584,9 @@
       <c r="AC26" s="90"/>
     </row>
     <row r="27" spans="1:29" ht="86.4">
-      <c r="A27" s="156"/>
-      <c r="B27" s="156"/>
-      <c r="C27" s="156" t="s">
+      <c r="A27" s="154"/>
+      <c r="B27" s="154"/>
+      <c r="C27" s="154" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="31" t="s">
@@ -7649,9 +7624,9 @@
       <c r="AC27" s="90"/>
     </row>
     <row r="28" spans="1:29" ht="86.4">
-      <c r="A28" s="156"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="156"/>
+      <c r="A28" s="154"/>
+      <c r="B28" s="154"/>
+      <c r="C28" s="154"/>
       <c r="D28" s="31" t="s">
         <v>127</v>
       </c>
@@ -7687,11 +7662,11 @@
       <c r="AC28" s="90"/>
     </row>
     <row r="29" spans="1:29" ht="86.4">
-      <c r="A29" s="156"/>
-      <c r="B29" s="156" t="s">
+      <c r="A29" s="154"/>
+      <c r="B29" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="156" t="s">
+      <c r="C29" s="154" t="s">
         <v>92</v>
       </c>
       <c r="D29" s="31" t="s">
@@ -7729,9 +7704,9 @@
       <c r="AC29" s="90"/>
     </row>
     <row r="30" spans="1:29" ht="82.8">
-      <c r="A30" s="156"/>
-      <c r="B30" s="156"/>
-      <c r="C30" s="156"/>
+      <c r="A30" s="154"/>
+      <c r="B30" s="154"/>
+      <c r="C30" s="154"/>
       <c r="D30" s="31" t="s">
         <v>103</v>
       </c>
@@ -7765,8 +7740,8 @@
       <c r="AC30" s="90"/>
     </row>
     <row r="31" spans="1:29" ht="69">
-      <c r="A31" s="156"/>
-      <c r="B31" s="156"/>
+      <c r="A31" s="154"/>
+      <c r="B31" s="154"/>
       <c r="C31" s="4"/>
       <c r="D31" s="31" t="s">
         <v>114</v>
@@ -7777,7 +7752,7 @@
       <c r="F31" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="160" t="s">
+      <c r="G31" s="158" t="s">
         <v>517</v>
       </c>
       <c r="H31" s="24"/>
@@ -7801,8 +7776,8 @@
       <c r="AC31" s="90"/>
     </row>
     <row r="32" spans="1:29" ht="69">
-      <c r="A32" s="156"/>
-      <c r="B32" s="156" t="s">
+      <c r="A32" s="154"/>
+      <c r="B32" s="154" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7817,7 +7792,7 @@
       <c r="F32" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G32" s="160"/>
+      <c r="G32" s="158"/>
       <c r="H32" s="24"/>
       <c r="I32" s="4" t="s">
         <v>275</v>
@@ -7825,8 +7800,8 @@
       <c r="J32" s="50"/>
     </row>
     <row r="33" spans="1:10" ht="55.2">
-      <c r="A33" s="156"/>
-      <c r="B33" s="156"/>
+      <c r="A33" s="154"/>
+      <c r="B33" s="154"/>
       <c r="C33" s="4" t="s">
         <v>98</v>
       </c>
@@ -7839,7 +7814,7 @@
       <c r="F33" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="160"/>
+      <c r="G33" s="158"/>
       <c r="H33" s="24"/>
       <c r="I33" s="4" t="s">
         <v>275</v>
@@ -7847,8 +7822,8 @@
       <c r="J33" s="50"/>
     </row>
     <row r="34" spans="1:10" ht="69">
-      <c r="A34" s="156"/>
-      <c r="B34" s="156" t="s">
+      <c r="A34" s="154"/>
+      <c r="B34" s="154" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="85"/>
@@ -7871,9 +7846,9 @@
       <c r="J34" s="50"/>
     </row>
     <row r="35" spans="1:10" ht="69">
-      <c r="A35" s="156"/>
-      <c r="B35" s="156"/>
-      <c r="C35" s="156" t="s">
+      <c r="A35" s="154"/>
+      <c r="B35" s="154"/>
+      <c r="C35" s="154" t="s">
         <v>124</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -7895,36 +7870,36 @@
       <c r="J35" s="50"/>
     </row>
     <row r="36" spans="1:10" ht="232.05" customHeight="1">
-      <c r="A36" s="156"/>
-      <c r="B36" s="156"/>
-      <c r="C36" s="156"/>
-      <c r="D36" s="188" t="s">
+      <c r="A36" s="154"/>
+      <c r="B36" s="154"/>
+      <c r="C36" s="154"/>
+      <c r="D36" s="189" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="156" t="s">
+      <c r="E36" s="154" t="s">
         <v>255</v>
       </c>
-      <c r="F36" s="156" t="s">
+      <c r="F36" s="154" t="s">
         <v>261</v>
       </c>
-      <c r="G36" s="156" t="s">
+      <c r="G36" s="154" t="s">
         <v>518</v>
       </c>
-      <c r="H36" s="156"/>
-      <c r="I36" s="156" t="s">
+      <c r="H36" s="154"/>
+      <c r="I36" s="154" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="156"/>
-      <c r="B37" s="156"/>
-      <c r="C37" s="156"/>
-      <c r="D37" s="188"/>
-      <c r="E37" s="156"/>
-      <c r="F37" s="156"/>
-      <c r="G37" s="156"/>
-      <c r="H37" s="156"/>
-      <c r="I37" s="156"/>
+      <c r="A37" s="154"/>
+      <c r="B37" s="154"/>
+      <c r="C37" s="154"/>
+      <c r="D37" s="189"/>
+      <c r="E37" s="154"/>
+      <c r="F37" s="154"/>
+      <c r="G37" s="154"/>
+      <c r="H37" s="154"/>
+      <c r="I37" s="154"/>
       <c r="J37" s="50"/>
     </row>
     <row r="38" spans="1:10">
@@ -7932,6 +7907,17 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
     <mergeCell ref="A2:A37"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B6:B7"/>
@@ -7945,42 +7931,31 @@
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="C29:C30"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:D1">
-    <cfRule type="expression" dxfId="51" priority="7">
+    <cfRule type="expression" dxfId="39" priority="7">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I1">
-    <cfRule type="expression" dxfId="50" priority="5">
+    <cfRule type="expression" dxfId="38" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="6">
+    <cfRule type="expression" dxfId="37" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I36">
-    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8044,10 +8019,10 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="178" t="s">
+      <c r="L2" s="172" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="179"/>
+      <c r="M2" s="173"/>
       <c r="N2" s="116" t="s">
         <v>600</v>
       </c>
@@ -8092,44 +8067,44 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="169">
+      <c r="L3" s="162">
         <f>COUNTA(H4:H25)</f>
         <v>21</v>
       </c>
-      <c r="M3" s="180"/>
-      <c r="N3" s="193">
+      <c r="M3" s="174"/>
+      <c r="N3" s="190">
         <f>L3-Q3</f>
         <v>20</v>
       </c>
-      <c r="O3" s="183">
+      <c r="O3" s="177">
         <f>COUNTIF(J4:J21,"Yes")</f>
         <v>6</v>
       </c>
-      <c r="P3" s="162">
+      <c r="P3" s="180">
         <f>COUNTIF(J4:J21,"No")</f>
         <v>10</v>
       </c>
-      <c r="Q3" s="165">
+      <c r="Q3" s="183">
         <f>COUNTIF(J4:J21,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R3" s="172">
+      <c r="R3" s="165">
         <f>O3/N3</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="94.5" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="155" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="151" t="s">
+      <c r="C4" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="156" t="s">
+      <c r="D4" s="154" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="190" t="s">
+      <c r="E4" s="193" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -8138,54 +8113,54 @@
       <c r="G4" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="160" t="s">
+      <c r="H4" s="158" t="s">
         <v>321</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="J4" s="156" t="s">
+      <c r="J4" s="154" t="s">
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="170"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="194"/>
-      <c r="O4" s="184"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="166"/>
-      <c r="R4" s="173"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="178"/>
+      <c r="P4" s="181"/>
+      <c r="Q4" s="184"/>
+      <c r="R4" s="166"/>
     </row>
     <row r="5" spans="1:18" ht="81" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="158"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="190"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="193"/>
       <c r="F5" s="12" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="H5" s="160"/>
+      <c r="H5" s="158"/>
       <c r="I5" s="24" t="s">
         <v>568</v>
       </c>
-      <c r="J5" s="156"/>
+      <c r="J5" s="154"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="195"/>
-      <c r="O5" s="185"/>
-      <c r="P5" s="164"/>
-      <c r="Q5" s="167"/>
-      <c r="R5" s="174"/>
+      <c r="L5" s="164"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="192"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="182"/>
+      <c r="Q5" s="185"/>
+      <c r="R5" s="167"/>
     </row>
     <row r="6" spans="1:18" ht="111" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="158"/>
-      <c r="C6" s="152"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="151"/>
       <c r="D6" s="2" t="s">
         <v>384</v>
       </c>
@@ -8217,20 +8192,20 @@
     </row>
     <row r="7" spans="1:18" ht="61.95" customHeight="1" thickBot="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="158"/>
-      <c r="C7" s="156" t="s">
+      <c r="B7" s="156"/>
+      <c r="C7" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="156" t="s">
+      <c r="D7" s="154" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="190" t="s">
+      <c r="E7" s="193" t="s">
         <v>546</v>
       </c>
-      <c r="F7" s="191" t="s">
+      <c r="F7" s="194" t="s">
         <v>547</v>
       </c>
-      <c r="G7" s="192" t="s">
+      <c r="G7" s="195" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -8254,12 +8229,12 @@
     </row>
     <row r="8" spans="1:18" ht="53.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="190"/>
-      <c r="F8" s="191"/>
-      <c r="G8" s="192"/>
+      <c r="B8" s="156"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="194"/>
+      <c r="G8" s="195"/>
       <c r="H8" s="24" t="s">
         <v>320</v>
       </c>
@@ -8277,7 +8252,7 @@
     </row>
     <row r="9" spans="1:18" ht="57.6">
       <c r="A9" s="50"/>
-      <c r="B9" s="158"/>
+      <c r="B9" s="156"/>
       <c r="C9" s="4" t="s">
         <v>306</v>
       </c>
@@ -8310,11 +8285,11 @@
     </row>
     <row r="10" spans="1:18" ht="58.05" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="158"/>
-      <c r="C10" s="189" t="s">
+      <c r="B10" s="156"/>
+      <c r="C10" s="186" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="151" t="s">
+      <c r="D10" s="149" t="s">
         <v>439</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -8343,9 +8318,9 @@
     </row>
     <row r="11" spans="1:18" ht="43.2">
       <c r="A11" s="50"/>
-      <c r="B11" s="158"/>
-      <c r="C11" s="189"/>
-      <c r="D11" s="152"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="151"/>
       <c r="E11" s="2" t="s">
         <v>392</v>
       </c>
@@ -8372,11 +8347,11 @@
     </row>
     <row r="12" spans="1:18" ht="52.05" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="158"/>
-      <c r="C12" s="157" t="s">
+      <c r="B12" s="156"/>
+      <c r="C12" s="155" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="189" t="s">
+      <c r="D12" s="186" t="s">
         <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -8404,9 +8379,9 @@
     </row>
     <row r="13" spans="1:18" ht="58.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="158"/>
-      <c r="C13" s="158"/>
-      <c r="D13" s="189"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="186"/>
       <c r="E13" s="2" t="s">
         <v>401</v>
       </c>
@@ -8432,8 +8407,8 @@
     </row>
     <row r="14" spans="1:18" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="158"/>
-      <c r="C14" s="159"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="157"/>
       <c r="D14" s="3" t="s">
         <v>441</v>
       </c>
@@ -8457,11 +8432,11 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="66" customHeight="1">
-      <c r="B15" s="158"/>
-      <c r="C15" s="156" t="s">
+      <c r="B15" s="156"/>
+      <c r="C15" s="154" t="s">
         <v>315</v>
       </c>
-      <c r="D15" s="157" t="s">
+      <c r="D15" s="155" t="s">
         <v>442</v>
       </c>
       <c r="E15" s="24" t="s">
@@ -8484,9 +8459,9 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="43.2">
-      <c r="B16" s="158"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="159"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="157"/>
       <c r="E16" s="24" t="s">
         <v>407</v>
       </c>
@@ -8507,11 +8482,11 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="77.55" customHeight="1">
-      <c r="B17" s="158"/>
-      <c r="C17" s="151" t="s">
+      <c r="B17" s="156"/>
+      <c r="C17" s="149" t="s">
         <v>316</v>
       </c>
-      <c r="D17" s="157" t="s">
+      <c r="D17" s="155" t="s">
         <v>443</v>
       </c>
       <c r="E17" s="74" t="s">
@@ -8534,9 +8509,9 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="57.6">
-      <c r="B18" s="158"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="159"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="157"/>
       <c r="E18" s="72" t="s">
         <v>413</v>
       </c>
@@ -8557,8 +8532,8 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="42" customHeight="1">
-      <c r="B19" s="158"/>
-      <c r="C19" s="189" t="s">
+      <c r="B19" s="156"/>
+      <c r="C19" s="186" t="s">
         <v>323</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -8584,8 +8559,8 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="39" customHeight="1">
-      <c r="B20" s="158"/>
-      <c r="C20" s="189"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="186"/>
       <c r="D20" s="3" t="s">
         <v>445</v>
       </c>
@@ -8609,11 +8584,11 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="43.2">
-      <c r="B21" s="158"/>
-      <c r="C21" s="156" t="s">
+      <c r="B21" s="156"/>
+      <c r="C21" s="154" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="157" t="s">
+      <c r="D21" s="155" t="s">
         <v>446</v>
       </c>
       <c r="E21" s="65" t="s">
@@ -8636,9 +8611,9 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="41.55" customHeight="1">
-      <c r="B22" s="158"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="159"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="157"/>
       <c r="E22" s="24" t="s">
         <v>427</v>
       </c>
@@ -8659,7 +8634,7 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="57.6">
-      <c r="B23" s="158"/>
+      <c r="B23" s="156"/>
       <c r="C23" s="4" t="s">
         <v>330</v>
       </c>
@@ -8686,8 +8661,8 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="43.2">
-      <c r="B24" s="158"/>
-      <c r="C24" s="189" t="s">
+      <c r="B24" s="156"/>
+      <c r="C24" s="186" t="s">
         <v>333</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -8713,8 +8688,8 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="43.2">
-      <c r="B25" s="159"/>
-      <c r="C25" s="189"/>
+      <c r="B25" s="157"/>
+      <c r="C25" s="186"/>
       <c r="D25" s="3" t="s">
         <v>447</v>
       </c>
@@ -8742,20 +8717,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
     <mergeCell ref="B4:B25"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="D12:D13"/>
@@ -8772,31 +8733,45 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="Q3:Q5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="44" priority="11">
+    <cfRule type="expression" dxfId="32" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="43" priority="5">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="6">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6:J26">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8851,10 +8826,10 @@
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="178" t="s">
+      <c r="L2" s="172" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="179"/>
+      <c r="M2" s="173"/>
       <c r="N2" s="116" t="s">
         <v>601</v>
       </c>
@@ -8901,38 +8876,38 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="169">
+      <c r="L3" s="162">
         <f>COUNTA(H4:H25)</f>
         <v>11</v>
       </c>
-      <c r="M3" s="180"/>
-      <c r="N3" s="193">
+      <c r="M3" s="174"/>
+      <c r="N3" s="190">
         <f>L3-Q3</f>
         <v>9</v>
       </c>
-      <c r="O3" s="183">
+      <c r="O3" s="177">
         <f>COUNTIF(J4:J25,"Yes")</f>
         <v>4</v>
       </c>
-      <c r="P3" s="162">
+      <c r="P3" s="180">
         <f>COUNTIF(J4:J25,"No")</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="165">
+      <c r="Q3" s="183">
         <f>COUNTIF(J4:J25,"N/A")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="172">
+      <c r="R3" s="165">
         <f>O3/N3</f>
         <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="120" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="154" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="199" t="s">
@@ -8950,20 +8925,20 @@
       <c r="H4" s="199" t="s">
         <v>346</v>
       </c>
-      <c r="I4" s="200" t="s">
+      <c r="I4" s="196" t="s">
         <v>525</v>
       </c>
-      <c r="J4" s="156" t="s">
+      <c r="J4" s="154" t="s">
         <v>273</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="170"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="194"/>
-      <c r="O4" s="184"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="166"/>
-      <c r="R4" s="173"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="178"/>
+      <c r="P4" s="181"/>
+      <c r="Q4" s="184"/>
+      <c r="R4" s="166"/>
       <c r="S4" s="91" t="s">
         <v>611</v>
       </c>
@@ -8973,8 +8948,8 @@
     </row>
     <row r="5" spans="1:20" ht="169.05" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154"/>
       <c r="D5" s="199"/>
       <c r="E5" s="8" t="s">
         <v>347</v>
@@ -8986,21 +8961,21 @@
         <v>154</v>
       </c>
       <c r="H5" s="199"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="156"/>
+      <c r="I5" s="197"/>
+      <c r="J5" s="154"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="195"/>
-      <c r="O5" s="185"/>
-      <c r="P5" s="164"/>
-      <c r="Q5" s="167"/>
-      <c r="R5" s="174"/>
+      <c r="L5" s="164"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="192"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="182"/>
+      <c r="Q5" s="185"/>
+      <c r="R5" s="167"/>
     </row>
     <row r="6" spans="1:20" ht="141" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
       <c r="D6" s="199"/>
       <c r="E6" s="8" t="s">
         <v>349</v>
@@ -9014,10 +8989,10 @@
       <c r="H6" s="199" t="s">
         <v>351</v>
       </c>
-      <c r="I6" s="200" t="s">
+      <c r="I6" s="196" t="s">
         <v>526</v>
       </c>
-      <c r="J6" s="156" t="s">
+      <c r="J6" s="154" t="s">
         <v>273</v>
       </c>
       <c r="K6" s="50"/>
@@ -9028,8 +9003,8 @@
     </row>
     <row r="7" spans="1:20" ht="151.94999999999999" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="156"/>
-      <c r="C7" s="156"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
       <c r="D7" s="199"/>
       <c r="E7" s="27" t="s">
         <v>352</v>
@@ -9041,8 +9016,8 @@
         <v>155</v>
       </c>
       <c r="H7" s="199"/>
-      <c r="I7" s="201"/>
-      <c r="J7" s="156"/>
+      <c r="I7" s="197"/>
+      <c r="J7" s="154"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
@@ -9051,9 +9026,9 @@
     </row>
     <row r="8" spans="1:20" ht="109.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="156"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="160" t="s">
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="158" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="27" t="s">
@@ -9065,13 +9040,13 @@
       <c r="G8" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="160" t="s">
+      <c r="H8" s="158" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="151" t="s">
+      <c r="I8" s="149" t="s">
         <v>527</v>
       </c>
-      <c r="J8" s="156" t="s">
+      <c r="J8" s="154" t="s">
         <v>274</v>
       </c>
       <c r="K8" s="50"/>
@@ -9079,9 +9054,9 @@
     </row>
     <row r="9" spans="1:20" ht="136.05000000000001" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="156"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="160"/>
+      <c r="B9" s="154"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="158"/>
       <c r="E9" s="27" t="s">
         <v>356</v>
       </c>
@@ -9091,18 +9066,18 @@
       <c r="G9" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="H9" s="160"/>
-      <c r="I9" s="152"/>
-      <c r="J9" s="156"/>
+      <c r="H9" s="158"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="154"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:20" ht="132.44999999999999" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="156"/>
-      <c r="C10" s="156" t="s">
+      <c r="B10" s="154"/>
+      <c r="C10" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="160" t="s">
+      <c r="D10" s="158" t="s">
         <v>358</v>
       </c>
       <c r="E10" s="27" t="s">
@@ -9117,19 +9092,19 @@
       <c r="H10" s="199" t="s">
         <v>528</v>
       </c>
-      <c r="I10" s="200" t="s">
+      <c r="I10" s="196" t="s">
         <v>529</v>
       </c>
-      <c r="J10" s="156" t="s">
+      <c r="J10" s="154" t="s">
         <v>275</v>
       </c>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:20" ht="138.44999999999999" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="160"/>
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
+      <c r="D11" s="158"/>
       <c r="E11" s="31" t="s">
         <v>361</v>
       </c>
@@ -9140,15 +9115,15 @@
         <v>163</v>
       </c>
       <c r="H11" s="199"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="156"/>
+      <c r="I11" s="197"/>
+      <c r="J11" s="154"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:20" ht="121.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="156"/>
-      <c r="C12" s="156"/>
-      <c r="D12" s="160" t="s">
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
+      <c r="D12" s="158" t="s">
         <v>307</v>
       </c>
       <c r="E12" s="31" t="s">
@@ -9163,19 +9138,19 @@
       <c r="H12" s="199" t="s">
         <v>342</v>
       </c>
-      <c r="I12" s="200" t="s">
+      <c r="I12" s="196" t="s">
         <v>530</v>
       </c>
-      <c r="J12" s="156" t="s">
+      <c r="J12" s="154" t="s">
         <v>274</v>
       </c>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:20" ht="154.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="156"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="160"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="154"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="31" t="s">
         <v>364</v>
       </c>
@@ -9186,14 +9161,14 @@
         <v>164</v>
       </c>
       <c r="H13" s="199"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="156"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="154"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:20" ht="144.44999999999999" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
       <c r="D14" s="24" t="s">
         <v>18</v>
       </c>
@@ -9207,24 +9182,24 @@
         <v>170</v>
       </c>
       <c r="H14" s="199"/>
-      <c r="I14" s="201"/>
-      <c r="J14" s="156"/>
+      <c r="I14" s="197"/>
+      <c r="J14" s="154"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:20" ht="52.95" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156" t="s">
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="196" t="s">
+      <c r="E15" s="202" t="s">
         <v>369</v>
       </c>
-      <c r="F15" s="197" t="s">
+      <c r="F15" s="200" t="s">
         <v>370</v>
       </c>
-      <c r="G15" s="198" t="s">
+      <c r="G15" s="203" t="s">
         <v>169</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -9240,12 +9215,12 @@
     </row>
     <row r="16" spans="1:20" ht="91.05" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="196"/>
-      <c r="F16" s="197"/>
-      <c r="G16" s="198"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="202"/>
+      <c r="F16" s="200"/>
+      <c r="G16" s="203"/>
       <c r="H16" s="70" t="s">
         <v>532</v>
       </c>
@@ -9259,8 +9234,8 @@
     </row>
     <row r="17" spans="1:15" ht="124.05" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
       <c r="D17" s="60" t="s">
         <v>368</v>
       </c>
@@ -9276,18 +9251,18 @@
       <c r="H17" s="199" t="s">
         <v>371</v>
       </c>
-      <c r="I17" s="200" t="s">
+      <c r="I17" s="196" t="s">
         <v>534</v>
       </c>
-      <c r="J17" s="156" t="s">
+      <c r="J17" s="154" t="s">
         <v>273</v>
       </c>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:15" ht="123" customHeight="1">
       <c r="A18" s="50"/>
-      <c r="B18" s="156"/>
-      <c r="C18" s="156"/>
+      <c r="B18" s="154"/>
+      <c r="C18" s="154"/>
       <c r="D18" s="24" t="s">
         <v>19</v>
       </c>
@@ -9301,15 +9276,15 @@
         <v>171</v>
       </c>
       <c r="H18" s="199"/>
-      <c r="I18" s="201"/>
-      <c r="J18" s="156"/>
+      <c r="I18" s="197"/>
+      <c r="J18" s="154"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:15" ht="118.05" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="156"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="160" t="s">
+      <c r="B19" s="154"/>
+      <c r="C19" s="154"/>
+      <c r="D19" s="158" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="31" t="s">
@@ -9321,13 +9296,13 @@
       <c r="G19" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="203" t="s">
+      <c r="H19" s="198" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="200" t="s">
+      <c r="I19" s="196" t="s">
         <v>535</v>
       </c>
-      <c r="J19" s="156" t="s">
+      <c r="J19" s="154" t="s">
         <v>275</v>
       </c>
       <c r="K19" s="50"/>
@@ -9336,9 +9311,9 @@
     </row>
     <row r="20" spans="1:15" ht="123" customHeight="1">
       <c r="A20" s="50"/>
-      <c r="B20" s="156"/>
-      <c r="C20" s="156"/>
-      <c r="D20" s="160"/>
+      <c r="B20" s="154"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="158"/>
       <c r="E20" s="31" t="s">
         <v>30</v>
       </c>
@@ -9348,9 +9323,9 @@
       <c r="G20" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="203"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="156"/>
+      <c r="H20" s="198"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="154"/>
       <c r="K20" s="51"/>
       <c r="L20" s="45"/>
       <c r="M20" s="45"/>
@@ -9359,9 +9334,9 @@
     </row>
     <row r="21" spans="1:15" ht="106.05" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="156"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="160"/>
+      <c r="B21" s="154"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="158"/>
       <c r="E21" s="31" t="s">
         <v>26</v>
       </c>
@@ -9371,24 +9346,24 @@
       <c r="G21" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="203"/>
-      <c r="I21" s="201"/>
-      <c r="J21" s="156"/>
+      <c r="H21" s="198"/>
+      <c r="I21" s="197"/>
+      <c r="J21" s="154"/>
       <c r="K21" s="50"/>
     </row>
     <row r="22" spans="1:15" ht="78" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="156"/>
-      <c r="C22" s="156" t="s">
+      <c r="B22" s="154"/>
+      <c r="C22" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="156" t="s">
+      <c r="D22" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="196" t="s">
+      <c r="E22" s="202" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="197" t="s">
+      <c r="F22" s="200" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="30" t="s">
@@ -9397,33 +9372,33 @@
       <c r="H22" s="199" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="200" t="s">
+      <c r="I22" s="196" t="s">
         <v>536</v>
       </c>
-      <c r="J22" s="156" t="s">
+      <c r="J22" s="154" t="s">
         <v>275</v>
       </c>
       <c r="K22" s="50"/>
     </row>
     <row r="23" spans="1:15" ht="72">
       <c r="A23" s="50"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="197"/>
+      <c r="B23" s="154"/>
+      <c r="C23" s="154"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="200"/>
       <c r="G23" s="30" t="s">
         <v>158</v>
       </c>
       <c r="H23" s="199"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="156"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="154"/>
       <c r="K23" s="50"/>
     </row>
     <row r="24" spans="1:15" ht="72">
       <c r="A24" s="50"/>
-      <c r="B24" s="156"/>
-      <c r="C24" s="156"/>
+      <c r="B24" s="154"/>
+      <c r="C24" s="154"/>
       <c r="D24" s="24" t="s">
         <v>12</v>
       </c>
@@ -9437,14 +9412,14 @@
         <v>166</v>
       </c>
       <c r="H24" s="199"/>
-      <c r="I24" s="201"/>
-      <c r="J24" s="156"/>
+      <c r="I24" s="197"/>
+      <c r="J24" s="154"/>
       <c r="K24" s="50"/>
     </row>
     <row r="25" spans="1:15" ht="100.8">
       <c r="A25" s="50"/>
-      <c r="B25" s="156"/>
-      <c r="C25" s="156"/>
+      <c r="B25" s="154"/>
+      <c r="C25" s="154"/>
       <c r="D25" s="2" t="s">
         <v>17</v>
       </c>
@@ -9483,37 +9458,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="C10:C21"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I6:I7"/>
     <mergeCell ref="B4:B25"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="P3:P5"/>
@@ -9530,61 +9474,92 @@
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="J17:J18"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="C10:C21"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:D3 E3:E4">
-    <cfRule type="expression" dxfId="37" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="36" priority="5">
+    <cfRule type="expression" dxfId="24" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="6">
+    <cfRule type="expression" dxfId="23" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="34" priority="18">
+    <cfRule type="expression" dxfId="22" priority="18">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$A6="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="31" priority="13">
+    <cfRule type="expression" dxfId="19" priority="13">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$A5="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F4">
-    <cfRule type="expression" dxfId="28" priority="9">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>$A4="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J8 J10 J12 J19 J22 J25 J6 J15:J17">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9627,7 +9602,10 @@
     <col min="20" max="20" width="42.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1"/>
+    <row r="1" spans="1:20" ht="15" thickBot="1">
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+    </row>
     <row r="2" spans="1:20" ht="24" thickBot="1">
       <c r="A2" s="50"/>
       <c r="B2" s="50"/>
@@ -9639,13 +9617,13 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="K2" s="205"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-      <c r="N2" s="178" t="s">
+      <c r="N2" s="172" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="179"/>
+      <c r="O2" s="173"/>
       <c r="P2" s="116" t="s">
         <v>601</v>
       </c>
@@ -9691,44 +9669,44 @@
       <c r="J3" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="K3" s="6"/>
+      <c r="K3" s="206"/>
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="169">
+      <c r="N3" s="162">
         <f>COUNTA(H4:H13)</f>
         <v>4</v>
       </c>
-      <c r="O3" s="180"/>
-      <c r="P3" s="193">
+      <c r="O3" s="174"/>
+      <c r="P3" s="190">
         <f>N3-S3</f>
         <v>4</v>
       </c>
-      <c r="Q3" s="183">
+      <c r="Q3" s="177">
         <f>COUNTIF(J4:J10,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="162">
+      <c r="R3" s="180">
         <f>COUNTIF(J4:J11,"No")</f>
         <v>2</v>
       </c>
-      <c r="S3" s="165">
+      <c r="S3" s="183">
         <f>COUNTIF(J4:J10,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="T3" s="183">
+      <c r="T3" s="177">
         <f>Q3/P3</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="78" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="154" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="154" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="156" t="s">
+      <c r="D4" s="154" t="s">
         <v>102</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -9740,31 +9718,31 @@
       <c r="G4" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="H4" s="160" t="s">
+      <c r="H4" s="158" t="s">
         <v>268</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>544</v>
       </c>
-      <c r="J4" s="156" t="s">
+      <c r="J4" s="154" t="s">
         <v>275</v>
       </c>
-      <c r="K4" s="50"/>
+      <c r="K4" s="205"/>
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
-      <c r="N4" s="170"/>
-      <c r="O4" s="181"/>
-      <c r="P4" s="194"/>
-      <c r="Q4" s="184"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="166"/>
-      <c r="T4" s="184"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="191"/>
+      <c r="Q4" s="178"/>
+      <c r="R4" s="181"/>
+      <c r="S4" s="184"/>
+      <c r="T4" s="178"/>
     </row>
     <row r="5" spans="1:20" ht="82.95" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
       <c r="E5" s="12" t="s">
         <v>107</v>
       </c>
@@ -9774,27 +9752,27 @@
       <c r="G5" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="160"/>
+      <c r="H5" s="158"/>
       <c r="I5" s="24" t="s">
         <v>545</v>
       </c>
-      <c r="J5" s="156"/>
+      <c r="J5" s="154"/>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
       <c r="N5" s="204"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="185"/>
-      <c r="R5" s="164"/>
-      <c r="S5" s="167"/>
-      <c r="T5" s="185"/>
+      <c r="O5" s="176"/>
+      <c r="P5" s="192"/>
+      <c r="Q5" s="179"/>
+      <c r="R5" s="182"/>
+      <c r="S5" s="185"/>
+      <c r="T5" s="179"/>
     </row>
     <row r="6" spans="1:20" ht="88.5" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156" t="s">
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -9806,13 +9784,13 @@
       <c r="G6" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H6" s="154" t="s">
+      <c r="H6" s="152" t="s">
         <v>267</v>
       </c>
       <c r="I6" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="J6" s="156" t="s">
+      <c r="J6" s="154" t="s">
         <v>275</v>
       </c>
       <c r="K6" s="50"/>
@@ -9828,9 +9806,9 @@
     </row>
     <row r="7" spans="1:20" ht="76.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="156"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
       <c r="E7" s="12" t="s">
         <v>109</v>
       </c>
@@ -9840,11 +9818,11 @@
       <c r="G7" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="H7" s="155"/>
+      <c r="H7" s="153"/>
       <c r="I7" s="24" t="s">
         <v>539</v>
       </c>
-      <c r="J7" s="156"/>
+      <c r="J7" s="154"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
@@ -9855,9 +9833,9 @@
     </row>
     <row r="8" spans="1:20" ht="98.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="156"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156" t="s">
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154" t="s">
         <v>110</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -9869,25 +9847,26 @@
       <c r="G8" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="H8" s="160" t="s">
+      <c r="H8" s="158" t="s">
         <v>266</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>540</v>
       </c>
-      <c r="J8" s="151" t="s">
+      <c r="J8" s="149" t="s">
         <v>273</v>
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
       <c r="Q8" s="117"/>
+      <c r="R8" s="50"/>
     </row>
     <row r="9" spans="1:20" ht="75.45" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="156"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
+      <c r="B9" s="154"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="154"/>
       <c r="E9" s="12" t="s">
         <v>112</v>
       </c>
@@ -9897,11 +9876,11 @@
       <c r="G9" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H9" s="160"/>
+      <c r="H9" s="158"/>
       <c r="I9" s="24" t="s">
         <v>541</v>
       </c>
-      <c r="J9" s="153"/>
+      <c r="J9" s="150"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
@@ -9909,23 +9888,23 @@
     </row>
     <row r="10" spans="1:20" ht="109.95" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="156"/>
-      <c r="C10" s="156"/>
-      <c r="D10" s="156"/>
-      <c r="E10" s="191" t="s">
+      <c r="B10" s="154"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="194" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="191" t="s">
+      <c r="F10" s="194" t="s">
         <v>227</v>
       </c>
-      <c r="G10" s="192" t="s">
+      <c r="G10" s="195" t="s">
         <v>206</v>
       </c>
-      <c r="H10" s="160"/>
+      <c r="H10" s="158"/>
       <c r="I10" s="24" t="s">
         <v>542</v>
       </c>
-      <c r="J10" s="152"/>
+      <c r="J10" s="151"/>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
@@ -9933,12 +9912,12 @@
     </row>
     <row r="11" spans="1:20" ht="63" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="191"/>
-      <c r="F11" s="191"/>
-      <c r="G11" s="192"/>
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
+      <c r="D11" s="154"/>
+      <c r="E11" s="194"/>
+      <c r="F11" s="194"/>
+      <c r="G11" s="195"/>
       <c r="H11" s="2" t="s">
         <v>280</v>
       </c>
@@ -9960,6 +9939,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N3:O5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="T3:T5"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="H4:H5"/>
@@ -9969,43 +9960,31 @@
     <mergeCell ref="J8:J10"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="C4:C11"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N3:O5"/>
-    <mergeCell ref="J4:J5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="22" priority="9">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:K3">
-    <cfRule type="expression" dxfId="21" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J11">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10026,12 +10005,14 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
     <col min="7" max="7" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10226,11 +10207,11 @@
       </c>
       <c r="D6" s="110">
         <f>'Questionnaire Confirmitee'!$N$3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="110">
         <f>'Questionnaire Confirmitee'!$O$3</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="110">
         <f>'Questionnaire Confirmitee'!$P$3</f>
@@ -10238,7 +10219,7 @@
       </c>
       <c r="G6" s="121">
         <f>'Questionnaire Confirmitee'!$R$3</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H6" s="124">
         <f>PONDERATION!$L$21</f>
@@ -10300,11 +10281,11 @@
       </c>
       <c r="D8" s="18">
         <f t="shared" ref="D8:F8" si="0">SUM(D2:D7)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="18">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" s="18">
         <f t="shared" si="0"/>
@@ -10312,7 +10293,7 @@
       </c>
       <c r="G8" s="133">
         <f>G2*H2+G3*H3+G4*H4+G5*H5+G6*H6+G7*H7</f>
-        <v>55.095436507936512</v>
+        <v>56.595436507936512</v>
       </c>
       <c r="H8" s="18">
         <f>SUM(H2:H7)</f>
@@ -10430,7 +10411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:7">
       <c r="A17" s="120">
         <v>6</v>
       </c>
@@ -10446,6 +10427,39 @@
       <c r="E17" s="111">
         <v>6</v>
       </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="210" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" s="210" t="s">
+        <v>596</v>
+      </c>
+      <c r="C20" s="210" t="s">
+        <v>597</v>
+      </c>
+      <c r="D20" s="210" t="s">
+        <v>598</v>
+      </c>
+      <c r="E20" s="210" t="s">
+        <v>599</v>
+      </c>
+      <c r="F20" s="210" t="s">
+        <v>594</v>
+      </c>
+      <c r="G20" s="209"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="207"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="208"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="207"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="207"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Default_Template.xlsx
+++ b/Data/Default_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="PONDERATION" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="614">
   <si>
     <t>Cybersecurity Governance &amp; Protection</t>
   </si>
@@ -2011,9 +2011,6 @@
   </si>
   <si>
     <t>Dhia</t>
-  </si>
-  <si>
-    <t>Question</t>
   </si>
 </sst>
 </file>
@@ -2228,7 +2225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2573,11 +2570,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2797,9 +2820,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2858,12 +2878,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2880,9 +2894,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2957,208 +2968,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3178,79 +2994,237 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="51">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3731,6 +3705,40 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4202,8 +4210,8 @@
     <col min="15" max="15" width="13.44140625" customWidth="1"/>
     <col min="16" max="16" width="14.77734375" customWidth="1"/>
     <col min="18" max="18" width="6.77734375" customWidth="1"/>
-    <col min="20" max="20" width="11.44140625" style="96"/>
-    <col min="21" max="21" width="11.44140625" style="93"/>
+    <col min="20" max="20" width="11.44140625" style="95"/>
+    <col min="21" max="21" width="11.44140625" style="92"/>
     <col min="28" max="28" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4227,40 +4235,40 @@
       <c r="Q1" s="50"/>
       <c r="R1" s="50"/>
       <c r="S1" s="50"/>
-      <c r="T1" s="98" t="s">
+      <c r="T1" s="97" t="s">
         <v>592</v>
       </c>
-      <c r="U1" s="98" t="s">
+      <c r="U1" s="97" t="s">
         <v>593</v>
       </c>
-      <c r="V1" s="98" t="s">
+      <c r="V1" s="97" t="s">
         <v>592</v>
       </c>
-      <c r="W1" s="98" t="s">
+      <c r="W1" s="97" t="s">
         <v>593</v>
       </c>
-      <c r="X1" s="98" t="s">
+      <c r="X1" s="97" t="s">
         <v>592</v>
       </c>
-      <c r="Y1" s="98" t="s">
+      <c r="Y1" s="97" t="s">
         <v>593</v>
       </c>
-      <c r="Z1" s="98" t="s">
+      <c r="Z1" s="97" t="s">
         <v>592</v>
       </c>
-      <c r="AA1" s="98" t="s">
+      <c r="AA1" s="97" t="s">
         <v>593</v>
       </c>
-      <c r="AB1" s="98" t="s">
+      <c r="AB1" s="97" t="s">
         <v>592</v>
       </c>
-      <c r="AC1" s="98" t="s">
+      <c r="AC1" s="97" t="s">
         <v>593</v>
       </c>
-      <c r="AD1" s="98" t="s">
+      <c r="AD1" s="97" t="s">
         <v>592</v>
       </c>
-      <c r="AE1" s="98" t="s">
+      <c r="AE1" s="97" t="s">
         <v>593</v>
       </c>
     </row>
@@ -4282,60 +4290,60 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
-      <c r="T2" s="98" t="s">
+      <c r="T2" s="97" t="s">
         <v>135</v>
       </c>
-      <c r="U2" s="80">
+      <c r="U2" s="79">
         <v>23</v>
       </c>
-      <c r="V2" s="98" t="s">
+      <c r="V2" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="W2" s="80">
+      <c r="W2" s="79">
         <v>12</v>
       </c>
-      <c r="X2" s="98" t="s">
+      <c r="X2" s="97" t="s">
         <v>137</v>
       </c>
-      <c r="Y2" s="80">
+      <c r="Y2" s="79">
         <v>35</v>
       </c>
-      <c r="Z2" s="98" t="s">
+      <c r="Z2" s="97" t="s">
         <v>138</v>
       </c>
-      <c r="AA2" s="80">
+      <c r="AA2" s="79">
         <v>23</v>
       </c>
-      <c r="AB2" s="98" t="s">
+      <c r="AB2" s="97" t="s">
         <v>139</v>
       </c>
-      <c r="AC2" s="80">
+      <c r="AC2" s="79">
         <v>3</v>
       </c>
-      <c r="AD2" s="98" t="s">
+      <c r="AD2" s="97" t="s">
         <v>219</v>
       </c>
-      <c r="AE2" s="80">
+      <c r="AE2" s="79">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="28.8">
       <c r="A3" s="50"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="156" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="143"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="157"/>
       <c r="J3" s="40"/>
-      <c r="K3" s="142" t="s">
+      <c r="K3" s="156" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="143"/>
+      <c r="L3" s="157"/>
       <c r="M3" s="40"/>
       <c r="N3" s="38" t="s">
         <v>148</v>
@@ -4374,10 +4382,10 @@
         <v>219</v>
       </c>
       <c r="J4" s="19"/>
-      <c r="K4" s="140" t="s">
+      <c r="K4" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="L4" s="141"/>
+      <c r="L4" s="155"/>
       <c r="M4" s="5"/>
       <c r="N4" s="62" t="s">
         <v>135</v>
@@ -4420,10 +4428,10 @@
         <v>4</v>
       </c>
       <c r="J5" s="20"/>
-      <c r="K5" s="140" t="s">
+      <c r="K5" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="141"/>
+      <c r="L5" s="155"/>
       <c r="M5" s="5"/>
       <c r="N5" s="62" t="s">
         <v>136</v>
@@ -4466,10 +4474,10 @@
         <v>3</v>
       </c>
       <c r="J6" s="20"/>
-      <c r="K6" s="140" t="s">
+      <c r="K6" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="141"/>
+      <c r="L6" s="155"/>
       <c r="M6" s="5"/>
       <c r="N6" s="62" t="s">
         <v>137</v>
@@ -4512,10 +4520,10 @@
         <v>6</v>
       </c>
       <c r="J7" s="20"/>
-      <c r="K7" s="140" t="s">
+      <c r="K7" s="154" t="s">
         <v>143</v>
       </c>
-      <c r="L7" s="141"/>
+      <c r="L7" s="155"/>
       <c r="M7" s="5"/>
       <c r="N7" s="62" t="s">
         <v>138</v>
@@ -4532,8 +4540,8 @@
       </c>
       <c r="R7" s="5"/>
       <c r="S7" s="50"/>
-      <c r="T7" s="99"/>
-      <c r="U7" s="100"/>
+      <c r="T7" s="98"/>
+      <c r="U7" s="99"/>
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="50"/>
@@ -4560,10 +4568,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="20"/>
-      <c r="K8" s="140" t="s">
+      <c r="K8" s="154" t="s">
         <v>144</v>
       </c>
-      <c r="L8" s="141"/>
+      <c r="L8" s="155"/>
       <c r="M8" s="5"/>
       <c r="N8" s="62" t="s">
         <v>139</v>
@@ -4606,10 +4614,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="J9" s="20"/>
-      <c r="K9" s="140" t="s">
+      <c r="K9" s="154" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="141"/>
+      <c r="L9" s="155"/>
       <c r="M9" s="5"/>
       <c r="N9" s="62" t="s">
         <v>219</v>
@@ -4717,15 +4725,15 @@
     <row r="12" spans="1:31">
       <c r="A12" s="50"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="145"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="145"/>
-      <c r="F12" s="145"/>
-      <c r="G12" s="145"/>
-      <c r="H12" s="145"/>
-      <c r="I12" s="145"/>
-      <c r="J12" s="145"/>
-      <c r="K12" s="145"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="159"/>
+      <c r="H12" s="159"/>
+      <c r="I12" s="159"/>
+      <c r="J12" s="159"/>
+      <c r="K12" s="159"/>
       <c r="L12" s="5"/>
       <c r="M12" s="22"/>
       <c r="S12" s="50"/>
@@ -4733,37 +4741,37 @@
     <row r="13" spans="1:31" ht="14.55" customHeight="1">
       <c r="A13" s="50"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="160" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="148"/>
+      <c r="D13" s="161"/>
+      <c r="E13" s="161"/>
+      <c r="F13" s="161"/>
+      <c r="G13" s="161"/>
+      <c r="H13" s="161"/>
+      <c r="I13" s="161"/>
+      <c r="J13" s="161"/>
+      <c r="K13" s="161"/>
+      <c r="L13" s="162"/>
       <c r="M13" s="22"/>
       <c r="S13" s="50"/>
     </row>
     <row r="14" spans="1:31" ht="15.6">
       <c r="A14" s="50"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="137" t="s">
+      <c r="C14" s="151" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="139"/>
-      <c r="J14" s="137" t="s">
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="K14" s="139"/>
+      <c r="K14" s="153"/>
       <c r="L14" s="35" t="s">
         <v>217</v>
       </c>
@@ -5194,7 +5202,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27.21875" customWidth="1"/>
@@ -5206,14 +5214,15 @@
     <col min="8" max="9" width="48.77734375" customWidth="1"/>
     <col min="10" max="10" width="18.21875" customWidth="1"/>
     <col min="12" max="12" width="33" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" style="96" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="95" customWidth="1"/>
     <col min="14" max="14" width="41.88671875" customWidth="1"/>
     <col min="15" max="15" width="21.5546875" customWidth="1"/>
     <col min="16" max="17" width="27.77734375" customWidth="1"/>
     <col min="18" max="18" width="27.33203125" customWidth="1"/>
+    <col min="21" max="21" width="128" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="25.95" customHeight="1" thickBot="1">
+    <row r="1" spans="1:21" ht="25.95" customHeight="1" thickBot="1">
       <c r="A1" s="50"/>
       <c r="B1" s="6" t="s">
         <v>148</v>
@@ -5243,22 +5252,22 @@
         <v>272</v>
       </c>
       <c r="K1" s="50"/>
-      <c r="L1" s="95" t="s">
+      <c r="L1" s="146" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="94" t="s">
+      <c r="M1" s="135" t="s">
         <v>588</v>
       </c>
       <c r="N1" s="94" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="97.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:21" ht="97.5" customHeight="1" thickBot="1">
       <c r="A2" s="50"/>
-      <c r="B2" s="149" t="s">
+      <c r="B2" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="154" t="s">
+      <c r="C2" s="168" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -5279,40 +5288,48 @@
       <c r="I2" s="68" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>274</v>
+      <c r="J2" s="133" t="s">
+        <v>275</v>
       </c>
       <c r="K2" s="50"/>
-      <c r="L2" s="102">
+      <c r="L2" s="147">
         <f>N2/R2</f>
-        <v>0.875</v>
-      </c>
-      <c r="M2" s="95" t="s">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="M2" s="94" t="s">
         <v>275</v>
       </c>
-      <c r="N2" s="105">
+      <c r="N2" s="102">
         <f>COUNTIF(J2:J24,"Yes")</f>
         <v>14</v>
       </c>
-      <c r="O2" s="101" t="s">
+      <c r="O2" s="148" t="s">
         <v>279</v>
       </c>
-      <c r="P2" s="103">
+      <c r="P2" s="100">
         <f>COUNTA(H2:H24)</f>
         <v>17</v>
       </c>
-      <c r="Q2" s="94" t="s">
+      <c r="Q2" s="93" t="s">
         <v>591</v>
       </c>
-      <c r="R2" s="104">
+      <c r="R2" s="101">
         <f>P2-N4</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="81" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="T2" s="134" t="str">
+        <f>IF(J2="No",ROW(),"")</f>
+        <v/>
+      </c>
+      <c r="U2" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U2))-ROW($I$2)+1),"")</f>
+        <v>Is a formal incident logging register or ticketing system implemented to ensure proper tracking, documentation, and traceability of incidents?</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="81" customHeight="1">
       <c r="A3" s="50"/>
-      <c r="B3" s="150"/>
-      <c r="C3" s="154"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="168"/>
       <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
@@ -5336,19 +5353,27 @@
       </c>
       <c r="K3" s="50"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="108" t="s">
+      <c r="M3" s="105" t="s">
         <v>273</v>
       </c>
-      <c r="N3" s="106">
+      <c r="N3" s="103">
         <f>COUNTIF(J2:J24,"No")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" s="57"/>
       <c r="P3" s="57"/>
-    </row>
-    <row r="4" spans="1:22" ht="79.95" customHeight="1" thickBot="1">
+      <c r="T3" s="134">
+        <f t="shared" ref="T3:T24" si="0">IF(J3="No",ROW(),"")</f>
+        <v>3</v>
+      </c>
+      <c r="U3" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U3))-ROW($I$2)+1),"")</f>
+        <v xml:space="preserve">Les données reçues via les réseaux, supports de stockage ou pièces jointes des emails, sont-elles systématiquement analysées avant utilisation ? </v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="79.95" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="150"/>
+      <c r="B4" s="164"/>
       <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
@@ -5375,18 +5400,25 @@
       </c>
       <c r="K4" s="50"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="109" t="s">
+      <c r="M4" s="145" t="s">
         <v>274</v>
       </c>
-      <c r="N4" s="107">
+      <c r="N4" s="104">
         <f>COUNTIF(J2:J24,"N/A")</f>
-        <v>1</v>
-      </c>
-      <c r="V4" s="78"/>
-    </row>
-    <row r="5" spans="1:22" ht="87" thickBot="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U4" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U4))-ROW($I$2)+1),"")</f>
+        <v>Les configurations réseau sont-elles sauvegardées et versionnées pour assurer leur intégrité et leur restauration ?</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="87" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="150"/>
+      <c r="B5" s="164"/>
       <c r="C5" s="3" t="s">
         <v>283</v>
       </c>
@@ -5413,17 +5445,25 @@
       </c>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="91" t="s">
+      <c r="M5" s="149" t="s">
         <v>611</v>
       </c>
-      <c r="N5" s="125" t="s">
+      <c r="N5" s="121" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="91.05" customHeight="1">
+      <c r="T5" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U5" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U5))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="91.05" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="150"/>
-      <c r="C6" s="155" t="s">
+      <c r="B6" s="164"/>
+      <c r="C6" s="169" t="s">
         <v>293</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -5449,54 +5489,78 @@
       </c>
       <c r="K6" s="50"/>
       <c r="L6" s="50"/>
-    </row>
-    <row r="7" spans="1:22" ht="43.5" customHeight="1">
+      <c r="T6" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U6" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U6))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="43.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="149" t="s">
+      <c r="B7" s="164"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="163" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="152" t="s">
+      <c r="E7" s="166" t="s">
         <v>456</v>
       </c>
-      <c r="F7" s="152" t="s">
+      <c r="F7" s="166" t="s">
         <v>457</v>
       </c>
-      <c r="G7" s="152" t="s">
+      <c r="G7" s="166" t="s">
         <v>458</v>
       </c>
-      <c r="H7" s="152" t="s">
+      <c r="H7" s="166" t="s">
         <v>302</v>
       </c>
-      <c r="I7" s="81" t="s">
+      <c r="I7" s="80" t="s">
         <v>555</v>
       </c>
-      <c r="J7" s="149" t="s">
+      <c r="J7" s="163" t="s">
         <v>273</v>
       </c>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
-    </row>
-    <row r="8" spans="1:22" ht="43.5" customHeight="1">
+      <c r="T7" s="134">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U7" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U7))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="43.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="150"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="153"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="151"/>
+      <c r="B8" s="164"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="165"/>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
-    </row>
-    <row r="9" spans="1:22" ht="49.95" customHeight="1">
+      <c r="T8" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U8" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U8))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="49.95" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="150"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="151"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="170"/>
+      <c r="D9" s="165"/>
       <c r="E9" s="24" t="s">
         <v>459</v>
       </c>
@@ -5517,12 +5581,20 @@
       </c>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
-    </row>
-    <row r="10" spans="1:22" ht="43.5" customHeight="1">
+      <c r="T9" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U9" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U9))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="43.5" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="156"/>
-      <c r="D10" s="149" t="s">
+      <c r="B10" s="164"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="163" t="s">
         <v>288</v>
       </c>
       <c r="E10" s="24" t="s">
@@ -5545,52 +5617,76 @@
       </c>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
-    </row>
-    <row r="11" spans="1:22" ht="43.5" customHeight="1">
+      <c r="T10" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U10" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U10))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="43.5" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="150"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="152" t="s">
+      <c r="B11" s="164"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="164"/>
+      <c r="E11" s="166" t="s">
         <v>465</v>
       </c>
-      <c r="F11" s="152" t="s">
+      <c r="F11" s="166" t="s">
         <v>466</v>
       </c>
-      <c r="G11" s="152" t="s">
+      <c r="G11" s="166" t="s">
         <v>467</v>
       </c>
-      <c r="H11" s="152" t="s">
+      <c r="H11" s="166" t="s">
         <v>295</v>
       </c>
-      <c r="I11" s="81" t="s">
+      <c r="I11" s="80" t="s">
         <v>558</v>
       </c>
-      <c r="J11" s="149" t="s">
+      <c r="J11" s="163" t="s">
         <v>275</v>
       </c>
       <c r="K11" s="50"/>
       <c r="L11" s="50"/>
-    </row>
-    <row r="12" spans="1:22" ht="43.5" customHeight="1">
+      <c r="T11" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U11" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U11))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="43.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="150"/>
-      <c r="C12" s="156"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="151"/>
+      <c r="B12" s="164"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="165"/>
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
-    </row>
-    <row r="13" spans="1:22" ht="43.2">
+      <c r="T12" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U12" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U12))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="43.2">
       <c r="A13" s="50"/>
-      <c r="B13" s="150"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="149" t="s">
+      <c r="B13" s="164"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="163" t="s">
         <v>289</v>
       </c>
       <c r="E13" s="42" t="s">
@@ -5613,12 +5709,20 @@
       </c>
       <c r="K13" s="50"/>
       <c r="L13" s="50"/>
-    </row>
-    <row r="14" spans="1:22" ht="53.55" customHeight="1">
+      <c r="T13" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U13" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U13))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="150"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="150"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="170"/>
+      <c r="D14" s="164"/>
       <c r="E14" s="42" t="s">
         <v>469</v>
       </c>
@@ -5639,12 +5743,20 @@
       </c>
       <c r="K14" s="50"/>
       <c r="L14" s="50"/>
-    </row>
-    <row r="15" spans="1:22" ht="51" customHeight="1">
+      <c r="T14" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U14" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U14))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="51" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="150"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="151"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="170"/>
+      <c r="D15" s="165"/>
       <c r="E15" s="42" t="s">
         <v>470</v>
       </c>
@@ -5665,68 +5777,100 @@
       </c>
       <c r="K15" s="50"/>
       <c r="L15" s="50"/>
-    </row>
-    <row r="16" spans="1:22" ht="47.55" customHeight="1">
+      <c r="T15" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U15" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U15))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="47.55" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="150"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="149" t="s">
+      <c r="B16" s="164"/>
+      <c r="C16" s="170"/>
+      <c r="D16" s="163" t="s">
         <v>290</v>
       </c>
-      <c r="E16" s="152" t="s">
+      <c r="E16" s="166" t="s">
         <v>477</v>
       </c>
-      <c r="F16" s="152" t="s">
+      <c r="F16" s="166" t="s">
         <v>478</v>
       </c>
-      <c r="G16" s="152" t="s">
+      <c r="G16" s="166" t="s">
         <v>479</v>
       </c>
-      <c r="H16" s="152" t="s">
+      <c r="H16" s="166" t="s">
         <v>301</v>
       </c>
-      <c r="I16" s="81" t="s">
+      <c r="I16" s="80" t="s">
         <v>562</v>
       </c>
-      <c r="J16" s="149" t="s">
+      <c r="J16" s="163" t="s">
         <v>275</v>
       </c>
       <c r="K16" s="50"/>
       <c r="L16" s="50"/>
-    </row>
-    <row r="17" spans="1:12" ht="22.05" hidden="1" customHeight="1">
+      <c r="T16" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U16" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U16))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="22.05" hidden="1" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="150"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="159"/>
-      <c r="F17" s="159"/>
-      <c r="G17" s="159"/>
-      <c r="H17" s="159"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="150"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="170"/>
+      <c r="D17" s="164"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="164"/>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="T17" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U17" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U17))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="50"/>
-      <c r="B18" s="150"/>
-      <c r="C18" s="156"/>
-      <c r="D18" s="151"/>
-      <c r="E18" s="153"/>
-      <c r="F18" s="153"/>
-      <c r="G18" s="153"/>
-      <c r="H18" s="153"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="151"/>
+      <c r="B18" s="164"/>
+      <c r="C18" s="170"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="165"/>
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
-    </row>
-    <row r="19" spans="1:12" ht="61.95" customHeight="1">
+      <c r="T18" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U18" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U18))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="61.95" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="150"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="149" t="s">
+      <c r="B19" s="164"/>
+      <c r="C19" s="170"/>
+      <c r="D19" s="163" t="s">
         <v>291</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -5744,57 +5888,81 @@
       <c r="I19" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>275</v>
+      <c r="J19" s="133" t="s">
+        <v>273</v>
       </c>
       <c r="K19" s="50"/>
       <c r="L19" s="50"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="T19" s="134">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U19" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U19))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="50"/>
-      <c r="B20" s="150"/>
-      <c r="C20" s="156"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="152" t="s">
+      <c r="B20" s="164"/>
+      <c r="C20" s="170"/>
+      <c r="D20" s="164"/>
+      <c r="E20" s="166" t="s">
         <v>481</v>
       </c>
-      <c r="F20" s="152" t="s">
+      <c r="F20" s="166" t="s">
         <v>485</v>
       </c>
-      <c r="G20" s="160" t="s">
+      <c r="G20" s="174" t="s">
         <v>489</v>
       </c>
-      <c r="H20" s="152" t="s">
+      <c r="H20" s="166" t="s">
         <v>300</v>
       </c>
-      <c r="I20" s="81"/>
-      <c r="J20" s="149" t="s">
+      <c r="I20" s="80"/>
+      <c r="J20" s="163" t="s">
         <v>275</v>
       </c>
       <c r="K20" s="50"/>
       <c r="L20" s="50"/>
-    </row>
-    <row r="21" spans="1:12" ht="28.95" customHeight="1">
+      <c r="T20" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U20" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U20))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="28.95" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="150"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="153"/>
-      <c r="G21" s="161"/>
-      <c r="H21" s="153"/>
-      <c r="I21" s="82" t="s">
+      <c r="B21" s="164"/>
+      <c r="C21" s="170"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="81" t="s">
         <v>564</v>
       </c>
-      <c r="J21" s="151"/>
+      <c r="J21" s="165"/>
       <c r="K21" s="50"/>
       <c r="L21" s="50"/>
-    </row>
-    <row r="22" spans="1:12" ht="39.450000000000003" customHeight="1">
+      <c r="T21" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U21" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U21))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="39.450000000000003" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="150"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="150"/>
+      <c r="B22" s="164"/>
+      <c r="C22" s="170"/>
+      <c r="D22" s="164"/>
       <c r="E22" s="24" t="s">
         <v>482</v>
       </c>
@@ -5815,50 +5983,74 @@
       </c>
       <c r="K22" s="50"/>
       <c r="L22" s="50"/>
-    </row>
-    <row r="23" spans="1:12" ht="42" customHeight="1">
+      <c r="T22" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U22" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U22))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="42" customHeight="1">
       <c r="A23" s="50"/>
-      <c r="B23" s="150"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="154" t="s">
+      <c r="B23" s="164"/>
+      <c r="C23" s="170"/>
+      <c r="D23" s="168" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="152" t="s">
+      <c r="E23" s="166" t="s">
         <v>483</v>
       </c>
-      <c r="F23" s="158" t="s">
+      <c r="F23" s="172" t="s">
         <v>487</v>
       </c>
-      <c r="G23" s="152" t="s">
+      <c r="G23" s="166" t="s">
         <v>491</v>
       </c>
-      <c r="H23" s="152" t="s">
+      <c r="H23" s="166" t="s">
         <v>299</v>
       </c>
-      <c r="I23" s="81" t="s">
+      <c r="I23" s="80" t="s">
         <v>566</v>
       </c>
-      <c r="J23" s="149" t="s">
+      <c r="J23" s="163" t="s">
         <v>275</v>
       </c>
       <c r="K23" s="50"/>
       <c r="L23" s="50"/>
-    </row>
-    <row r="24" spans="1:12" ht="28.95" customHeight="1">
+      <c r="T23" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U23" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U23))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="28.95" customHeight="1">
       <c r="A24" s="50"/>
-      <c r="B24" s="151"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="82"/>
-      <c r="J24" s="151"/>
+      <c r="B24" s="165"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="165"/>
       <c r="K24" s="50"/>
       <c r="L24" s="50"/>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="T24" s="134" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U24" s="134" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U24))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="50"/>
       <c r="B25" s="50"/>
       <c r="C25" s="50"/>
@@ -5871,8 +6063,12 @@
       <c r="J25" s="50"/>
       <c r="K25" s="50"/>
       <c r="L25" s="50"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="U25" t="str">
+        <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U25))-ROW($I$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="50"/>
       <c r="B26" s="50"/>
       <c r="C26" s="50"/>
@@ -5924,34 +6120,34 @@
     <mergeCell ref="E11:E12"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:E1">
-    <cfRule type="expression" dxfId="52" priority="9">
+    <cfRule type="expression" dxfId="50" priority="9">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J1">
-    <cfRule type="expression" dxfId="51" priority="5">
+    <cfRule type="expression" dxfId="49" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="6">
+    <cfRule type="expression" dxfId="48" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J7 J9:J11 J13:J16 J19:J20 J22:J23">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J22:J23 J19:J20 J2:J7 J9:J11 J13:J16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J22:J23 J13:J16 J9:J11 J2:J7 J19:J20">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N5">
@@ -6011,21 +6207,21 @@
       <c r="S1" s="59"/>
     </row>
     <row r="2" spans="1:23" ht="21.45" customHeight="1" thickBot="1">
-      <c r="A2" s="168"/>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
+      <c r="A2" s="182"/>
+      <c r="B2" s="183"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
       <c r="I2" s="53"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="172" t="s">
+      <c r="J2" s="182"/>
+      <c r="K2" s="182"/>
+      <c r="L2" s="186" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="173"/>
+      <c r="M2" s="187"/>
       <c r="N2" s="58" t="s">
         <v>275</v>
       </c>
@@ -6044,7 +6240,7 @@
       <c r="S2" s="59"/>
     </row>
     <row r="3" spans="1:23" ht="28.05" customHeight="1">
-      <c r="A3" s="168"/>
+      <c r="A3" s="182"/>
       <c r="B3" s="43" t="s">
         <v>148</v>
       </c>
@@ -6063,131 +6259,132 @@
       <c r="G3" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="H3" s="115" t="s">
+      <c r="H3" s="111" t="s">
         <v>260</v>
       </c>
       <c r="I3" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
-      <c r="L3" s="162">
+      <c r="J3" s="182"/>
+      <c r="K3" s="182"/>
+      <c r="L3" s="176">
         <f>COUNTA(I4:I13)</f>
         <v>4</v>
       </c>
-      <c r="M3" s="174"/>
-      <c r="N3" s="177">
+      <c r="M3" s="188"/>
+      <c r="N3" s="191">
         <f>COUNTIF(I4:I12,"Yes")</f>
         <v>1</v>
       </c>
-      <c r="O3" s="180">
+      <c r="O3" s="194">
         <f>COUNTIF(I4:I12,"No")</f>
         <v>3</v>
       </c>
-      <c r="P3" s="183">
+      <c r="P3" s="197">
         <f>COUNTIF(I4:I12,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="162">
+      <c r="Q3" s="176">
         <f>L3-P3</f>
         <v>4</v>
       </c>
-      <c r="R3" s="165">
+      <c r="R3" s="179">
         <f>N3/Q3</f>
         <v>0.25</v>
       </c>
       <c r="S3" s="59"/>
-      <c r="V3" s="56" t="s">
-        <v>614</v>
-      </c>
+      <c r="U3" s="7"/>
+      <c r="V3" s="55"/>
     </row>
     <row r="4" spans="1:23" ht="93.6" customHeight="1">
-      <c r="A4" s="168"/>
-      <c r="B4" s="149" t="s">
+      <c r="A4" s="182"/>
+      <c r="B4" s="163" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="149" t="s">
+      <c r="C4" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="158" t="s">
+      <c r="D4" s="172" t="s">
         <v>228</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="172" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="152" t="s">
+      <c r="F4" s="166" t="s">
         <v>249</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="171" t="s">
+      <c r="H4" s="185" t="s">
         <v>262</v>
       </c>
-      <c r="I4" s="154" t="s">
+      <c r="I4" s="168" t="s">
         <v>273</v>
       </c>
-      <c r="J4" s="168"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="178"/>
-      <c r="O4" s="181"/>
-      <c r="P4" s="184"/>
-      <c r="Q4" s="163"/>
-      <c r="R4" s="166"/>
+      <c r="J4" s="182"/>
+      <c r="K4" s="182"/>
+      <c r="L4" s="177"/>
+      <c r="M4" s="189"/>
+      <c r="N4" s="192"/>
+      <c r="O4" s="195"/>
+      <c r="P4" s="198"/>
+      <c r="Q4" s="177"/>
+      <c r="R4" s="180"/>
       <c r="S4" s="59"/>
-      <c r="V4" s="212" t="str">
-        <f>IF(I4="No",H4,"")</f>
-        <v>Pouvez-vous fournir les rapports d’audit réalisés au cours des 12 derniers mois, ainsi que les preuves de leur dépôt auprès de l’ANSI ?</v>
-      </c>
-      <c r="W4" s="212"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="150"/>
+      <c r="W4" s="143"/>
     </row>
     <row r="5" spans="1:23" ht="78" customHeight="1" thickBot="1">
-      <c r="A5" s="168"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="159"/>
+      <c r="A5" s="182"/>
+      <c r="B5" s="164"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="173"/>
       <c r="G5" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="171"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="179"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="185"/>
-      <c r="Q5" s="164"/>
-      <c r="R5" s="167"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="182"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="178"/>
+      <c r="M5" s="190"/>
+      <c r="N5" s="193"/>
+      <c r="O5" s="196"/>
+      <c r="P5" s="199"/>
+      <c r="Q5" s="178"/>
+      <c r="R5" s="181"/>
       <c r="S5" s="59"/>
-      <c r="V5" s="212" t="str">
-        <f t="shared" ref="V5:V11" si="0">IF(I5="No",H5,"")</f>
-        <v/>
-      </c>
-      <c r="W5" s="212" t="str">
+      <c r="U5" s="7" t="str">
+        <f t="shared" ref="U5:U11" si="0">IF(I5="No",ROW(), "")</f>
+        <v/>
+      </c>
+      <c r="V5" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V5))-ROW($H$4)+1),"")</f>
+        <v>L’organisation possède-t-elle un niveau de sécurité délivré par l’ANSI ? Si oui, quel est ce niveau ?</v>
+      </c>
+      <c r="W5" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W5))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="105.6" thickBot="1">
-      <c r="A6" s="168"/>
-      <c r="B6" s="150"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
-      <c r="F6" s="153"/>
+    <row r="6" spans="1:23" ht="72.599999999999994" thickBot="1">
+      <c r="A6" s="182"/>
+      <c r="B6" s="164"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="167"/>
       <c r="G6" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="H6" s="171"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="168"/>
-      <c r="K6" s="168"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="168"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="182"/>
       <c r="L6" s="59"/>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -6196,19 +6393,23 @@
       <c r="Q6" s="59"/>
       <c r="R6" s="59"/>
       <c r="S6" s="59"/>
-      <c r="V6" s="212" t="str">
+      <c r="U6" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W6" s="212" t="str">
+      <c r="V6" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V6))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+      <c r="W6" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W6))),"")</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:23" ht="109.05" customHeight="1" thickBot="1">
-      <c r="A7" s="168"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
+      <c r="A7" s="182"/>
+      <c r="B7" s="164"/>
+      <c r="C7" s="164"/>
       <c r="D7" s="24" t="s">
         <v>234</v>
       </c>
@@ -6221,34 +6422,38 @@
       <c r="G7" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="171" t="s">
+      <c r="H7" s="185" t="s">
         <v>263</v>
       </c>
-      <c r="I7" s="154" t="s">
+      <c r="I7" s="168" t="s">
         <v>273</v>
       </c>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="91" t="s">
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="M7" s="125" t="s">
+      <c r="M7" s="121" t="s">
         <v>612</v>
       </c>
-      <c r="N7" s="113"/>
-      <c r="V7" s="212" t="str">
+      <c r="N7" s="109"/>
+      <c r="U7" s="7">
         <f t="shared" si="0"/>
-        <v>Est-ce que vos équipements électroniques et logiciels, ainsi que vos fournisseurs de services cloud, possèdent respectivement les labels « Sécurisé » et « G-Cloud / N-Cloud » valides délivrés par l’ANSI ?</v>
-      </c>
-      <c r="W7" s="212" t="str">
+        <v>7</v>
+      </c>
+      <c r="V7" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V7))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+      <c r="W7" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W7))),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:23" ht="102" customHeight="1">
-      <c r="A8" s="168"/>
-      <c r="B8" s="150"/>
-      <c r="C8" s="150"/>
+      <c r="A8" s="182"/>
+      <c r="B8" s="164"/>
+      <c r="C8" s="164"/>
       <c r="D8" s="24" t="s">
         <v>235</v>
       </c>
@@ -6261,25 +6466,29 @@
       <c r="G8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="H8" s="171"/>
-      <c r="I8" s="154"/>
-      <c r="J8" s="168"/>
-      <c r="K8" s="168"/>
-      <c r="N8" s="114"/>
-      <c r="Q8" s="211"/>
-      <c r="V8" s="212" t="str">
+      <c r="H8" s="185"/>
+      <c r="I8" s="168"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="N8" s="110"/>
+      <c r="Q8" s="142"/>
+      <c r="U8" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W8" s="212" t="str">
+      <c r="V8" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V8))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+      <c r="W8" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W8))),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:23" ht="252" customHeight="1">
-      <c r="A9" s="168"/>
-      <c r="B9" s="150"/>
-      <c r="C9" s="150"/>
+      <c r="A9" s="182"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="164"/>
       <c r="D9" s="24" t="s">
         <v>244</v>
       </c>
@@ -6292,27 +6501,31 @@
       <c r="G9" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H9" s="171" t="s">
+      <c r="H9" s="185" t="s">
         <v>265</v>
       </c>
-      <c r="I9" s="154" t="s">
+      <c r="I9" s="168" t="s">
         <v>275</v>
       </c>
-      <c r="J9" s="168"/>
-      <c r="K9" s="168"/>
-      <c r="V9" s="212" t="str">
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="U9" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W9" s="212" t="str">
+      <c r="V9" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V9))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+      <c r="W9" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W9))),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:23" ht="139.05000000000001" customHeight="1">
-      <c r="A10" s="168"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="150"/>
+      <c r="A10" s="182"/>
+      <c r="B10" s="164"/>
+      <c r="C10" s="164"/>
       <c r="D10" s="24" t="s">
         <v>248</v>
       </c>
@@ -6325,23 +6538,27 @@
       <c r="G10" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="171"/>
-      <c r="I10" s="154"/>
-      <c r="J10" s="168"/>
-      <c r="K10" s="168"/>
-      <c r="V10" s="212" t="str">
+      <c r="H10" s="185"/>
+      <c r="I10" s="168"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="U10" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W10" s="212" t="str">
+      <c r="V10" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V10))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+      <c r="W10" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W10))),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:23" ht="64.95" customHeight="1">
-      <c r="A11" s="168"/>
-      <c r="B11" s="151"/>
-      <c r="C11" s="151"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
       <c r="D11" s="24" t="s">
         <v>239</v>
       </c>
@@ -6357,53 +6574,54 @@
       <c r="H11" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="I11" s="136" t="s">
+      <c r="I11" s="132" t="s">
         <v>273</v>
       </c>
-      <c r="J11" s="168"/>
-      <c r="K11" s="168"/>
-      <c r="V11" s="212" t="str">
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="U11" s="7">
         <f t="shared" si="0"/>
-        <v>L’organisation possède-t-elle un niveau de sécurité délivré par l’ANSI ? Si oui, quel est ce niveau ?</v>
-      </c>
-      <c r="W11" s="212" t="str">
+        <v>11</v>
+      </c>
+      <c r="V11" s="150" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V11))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W11))),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:23" ht="21">
-      <c r="A12" s="168"/>
-      <c r="B12" s="170"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
-      <c r="E12" s="170"/>
-      <c r="F12" s="170"/>
-      <c r="G12" s="170"/>
-      <c r="H12" s="170"/>
+      <c r="A12" s="182"/>
+      <c r="B12" s="184"/>
+      <c r="C12" s="184"/>
+      <c r="D12" s="184"/>
+      <c r="E12" s="184"/>
+      <c r="F12" s="184"/>
+      <c r="G12" s="184"/>
+      <c r="H12" s="184"/>
       <c r="I12" s="53"/>
-      <c r="J12" s="168"/>
-      <c r="K12" s="168"/>
-      <c r="V12" s="212" t="str">
-        <f t="shared" ref="V8:V12" si="1">IF(I9="No",H9,"")</f>
-        <v/>
-      </c>
-      <c r="W12" s="212" t="str">
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="V12" s="143"/>
+      <c r="W12" s="143" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W12))),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="168"/>
-      <c r="B13" s="168"/>
-      <c r="C13" s="168"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="168"/>
-      <c r="G13" s="168"/>
-      <c r="H13" s="168"/>
+      <c r="A13" s="182"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="182"/>
       <c r="I13" s="53"/>
-      <c r="J13" s="168"/>
-      <c r="K13" s="168"/>
+      <c r="J13" s="182"/>
+      <c r="K13" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -6431,32 +6649,32 @@
     <mergeCell ref="I7:I8"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:I3">
-    <cfRule type="expression" dxfId="45" priority="7">
+    <cfRule type="expression" dxfId="43" priority="7">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="8">
+    <cfRule type="expression" dxfId="42" priority="8">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I7 I9 I11">
-    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="6" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V3">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="36" priority="2">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6478,7 +6696,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF38"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
@@ -6492,13 +6710,14 @@
     <col min="12" max="12" width="37.6640625" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="10.88671875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="25.33203125" style="90" customWidth="1"/>
-    <col min="16" max="16" width="24.21875" style="90" customWidth="1"/>
-    <col min="17" max="17" width="26.5546875" style="90" customWidth="1"/>
+    <col min="15" max="15" width="25.33203125" style="89" customWidth="1"/>
+    <col min="16" max="16" width="24.21875" style="89" customWidth="1"/>
+    <col min="17" max="17" width="26.5546875" style="89" customWidth="1"/>
     <col min="18" max="18" width="30.44140625" customWidth="1"/>
     <col min="19" max="19" width="26.21875" customWidth="1"/>
     <col min="20" max="20" width="45.77734375" customWidth="1"/>
     <col min="21" max="21" width="36.33203125" customWidth="1"/>
+    <col min="24" max="24" width="159.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="24" thickBot="1">
@@ -6528,22 +6747,22 @@
         <v>272</v>
       </c>
       <c r="J1" s="50"/>
-      <c r="L1" s="95" t="s">
+      <c r="L1" s="94" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="187" t="s">
+      <c r="M1" s="201" t="s">
         <v>588</v>
       </c>
-      <c r="N1" s="188"/>
-      <c r="O1" s="94" t="s">
+      <c r="N1" s="202"/>
+      <c r="O1" s="93" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="128.4" thickBot="1">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="168" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="172" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="24" t="s">
@@ -6562,58 +6781,64 @@
         <v>520</v>
       </c>
       <c r="H2" s="24"/>
-      <c r="I2" s="136" t="s">
+      <c r="I2" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J2" s="50"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="97">
+      <c r="K2" s="89"/>
+      <c r="L2" s="96">
         <f>O2/S2</f>
         <v>0.74285714285714288</v>
       </c>
-      <c r="M2" s="95" t="s">
+      <c r="M2" s="94" t="s">
         <v>275</v>
       </c>
-      <c r="N2" s="96"/>
-      <c r="O2" s="87">
+      <c r="N2" s="95"/>
+      <c r="O2" s="86">
         <f>COUNTIF(I2:I37,"Yes")</f>
         <v>26</v>
       </c>
-      <c r="P2" s="94" t="s">
+      <c r="P2" s="93" t="s">
         <v>279</v>
       </c>
-      <c r="Q2" s="86">
+      <c r="Q2" s="85">
         <f>COUNTA(I2:I200)</f>
         <v>35</v>
       </c>
-      <c r="R2" s="94" t="s">
+      <c r="R2" s="93" t="s">
         <v>591</v>
       </c>
-      <c r="S2" s="86">
+      <c r="S2" s="85">
         <f>Q2-O4</f>
         <v>35</v>
       </c>
-      <c r="T2" s="91" t="s">
+      <c r="T2" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="U2" s="125" t="s">
+      <c r="U2" s="121" t="s">
         <v>613</v>
       </c>
-      <c r="V2" s="90"/>
-      <c r="W2" s="90"/>
-      <c r="X2" s="90"/>
-      <c r="Y2" s="90"/>
-      <c r="Z2" s="90"/>
-      <c r="AA2" s="90"/>
-      <c r="AB2" s="90"/>
-      <c r="AC2" s="90"/>
-      <c r="AD2" s="90"/>
-      <c r="AE2" s="90"/>
-      <c r="AF2" s="90"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="129">
+        <f>IF(I4="No",ROW(), "")</f>
+        <v>2</v>
+      </c>
+      <c r="X2" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X2:X$2))-ROW($G$2)+1),"")</f>
+        <v>Les liens entre la gestion de crise, la gestion des incidents, la continuité d’activité et la sécurité sont-ils formalisés ?</v>
+      </c>
+      <c r="Y2" s="89"/>
+      <c r="Z2" s="89"/>
+      <c r="AA2" s="89"/>
+      <c r="AB2" s="89"/>
+      <c r="AC2" s="89"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="89"/>
+      <c r="AF2" s="89"/>
     </row>
     <row r="3" spans="1:32" ht="115.95" customHeight="1" thickBot="1">
-      <c r="A3" s="154"/>
-      <c r="B3" s="158"/>
+      <c r="A3" s="168"/>
+      <c r="B3" s="172"/>
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -6630,36 +6855,42 @@
         <v>519</v>
       </c>
       <c r="H3" s="24"/>
-      <c r="I3" s="136" t="s">
+      <c r="I3" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J3" s="50"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="95" t="s">
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="94" t="s">
         <v>273</v>
       </c>
-      <c r="N3" s="96"/>
-      <c r="O3" s="88">
+      <c r="N3" s="95"/>
+      <c r="O3" s="87">
         <f>COUNTIF(I2:I37,"No")</f>
         <v>9</v>
       </c>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="90"/>
-      <c r="V3" s="90"/>
-      <c r="W3" s="90"/>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
-      <c r="Z3" s="90"/>
-      <c r="AA3" s="90"/>
-      <c r="AB3" s="90"/>
-      <c r="AC3" s="90"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="129">
+        <f t="shared" ref="W3:W37" si="0">IF(I5="No",ROW(), "")</f>
+        <v>3</v>
+      </c>
+      <c r="X3" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X3))-ROW($G$2)+1),"")</f>
+        <v>Le cadre formel de gouvernance de la gestion de crise cyber est-il documenté, daté et approuvé par l’autorité compétente afin de garantir sa validité et son application ?</v>
+      </c>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="89"/>
+      <c r="AB3" s="89"/>
+      <c r="AC3" s="89"/>
     </row>
     <row r="4" spans="1:32" ht="87" customHeight="1" thickBot="1">
-      <c r="A4" s="154"/>
-      <c r="B4" s="158"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="172"/>
       <c r="C4" s="24" t="s">
         <v>72</v>
       </c>
@@ -6676,38 +6907,44 @@
         <v>495</v>
       </c>
       <c r="H4" s="24"/>
-      <c r="I4" s="136" t="s">
+      <c r="I4" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J4" s="50"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
       <c r="M4" s="58" t="s">
         <v>274</v>
       </c>
-      <c r="N4" s="90"/>
-      <c r="O4" s="89">
+      <c r="N4" s="89"/>
+      <c r="O4" s="88">
         <f>COUNTIF(I2:I37,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="90"/>
-      <c r="S4" s="90"/>
-      <c r="T4" s="90"/>
-      <c r="U4" s="90"/>
-      <c r="V4" s="90"/>
-      <c r="W4" s="90"/>
-      <c r="X4" s="90"/>
-      <c r="Y4" s="90"/>
-      <c r="Z4" s="90"/>
-      <c r="AA4" s="90"/>
-      <c r="AB4" s="90"/>
-      <c r="AC4" s="90"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="W4" s="129">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X4" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X4))-ROW($G$2)+1),"")</f>
+        <v xml:space="preserve">Exsite t-il des cas specifique ou de periode qui declanche la revision du cadre de gouvernance ? </v>
+      </c>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
+      <c r="AB4" s="89"/>
+      <c r="AC4" s="89"/>
     </row>
     <row r="5" spans="1:32" ht="126.45" customHeight="1">
-      <c r="A5" s="154"/>
-      <c r="B5" s="158"/>
+      <c r="A5" s="168"/>
+      <c r="B5" s="172"/>
       <c r="C5" s="68" t="s">
         <v>75</v>
       </c>
@@ -6724,32 +6961,38 @@
         <v>493</v>
       </c>
       <c r="H5" s="68"/>
-      <c r="I5" s="136" t="s">
+      <c r="I5" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J5" s="50"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="90"/>
-      <c r="X5" s="90"/>
-      <c r="Y5" s="90"/>
-      <c r="Z5" s="90"/>
-      <c r="AA5" s="90"/>
-      <c r="AB5" s="90"/>
-      <c r="AC5" s="90"/>
+      <c r="K5" s="89"/>
+      <c r="L5" s="89"/>
+      <c r="M5" s="89"/>
+      <c r="N5" s="89"/>
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
+      <c r="W5" s="129">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X5" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X5))-ROW($G$2)+1),"")</f>
+        <v>Existe-t-il une politique qui definie la modaliter et les ligne a suivre en terme de communication interne et externe dans le cas d'un crise cyber ?</v>
+      </c>
+      <c r="Y5" s="89"/>
+      <c r="Z5" s="89"/>
+      <c r="AA5" s="89"/>
+      <c r="AB5" s="89"/>
+      <c r="AC5" s="89"/>
     </row>
     <row r="6" spans="1:32" ht="86.4">
-      <c r="A6" s="154"/>
-      <c r="B6" s="158"/>
+      <c r="A6" s="168"/>
+      <c r="B6" s="172"/>
       <c r="C6" s="24" t="s">
         <v>78</v>
       </c>
@@ -6766,30 +7009,36 @@
         <v>492</v>
       </c>
       <c r="H6" s="24"/>
-      <c r="I6" s="136" t="s">
+      <c r="I6" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J6" s="50"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="90"/>
-      <c r="W6" s="90"/>
-      <c r="X6" s="90"/>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90"/>
-      <c r="AA6" s="90"/>
-      <c r="AB6" s="90"/>
-      <c r="AC6" s="90"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="89"/>
+      <c r="N6" s="89"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="89"/>
+      <c r="T6" s="89"/>
+      <c r="U6" s="89"/>
+      <c r="V6" s="89"/>
+      <c r="W6" s="129">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X6" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X6))-ROW($G$2)+1),"")</f>
+        <v>Existe-t-il une repartition des  responsabilite pour chaque acteur et procedure operationelles ?</v>
+      </c>
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="89"/>
+      <c r="AB6" s="89"/>
+      <c r="AC6" s="89"/>
     </row>
     <row r="7" spans="1:32" ht="86.4">
-      <c r="A7" s="154"/>
-      <c r="B7" s="158"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="172"/>
       <c r="C7" s="24" t="s">
         <v>81</v>
       </c>
@@ -6806,33 +7055,39 @@
         <v>494</v>
       </c>
       <c r="H7" s="24"/>
-      <c r="I7" s="136" t="s">
+      <c r="I7" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J7" s="50"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="90"/>
-      <c r="U7" s="90"/>
-      <c r="V7" s="90"/>
-      <c r="W7" s="90"/>
-      <c r="X7" s="90"/>
-      <c r="Y7" s="90"/>
-      <c r="Z7" s="90"/>
-      <c r="AA7" s="90"/>
-      <c r="AB7" s="90"/>
-      <c r="AC7" s="90"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
+      <c r="R7" s="89"/>
+      <c r="S7" s="89"/>
+      <c r="T7" s="89"/>
+      <c r="U7" s="89"/>
+      <c r="V7" s="89"/>
+      <c r="W7" s="129">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X7" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X7))-ROW($G$2)+1),"")</f>
+        <v>Qui a l'autorite de decision directionnelle en cas de crise cyber? Cette information est t-elle communiqué ?</v>
+      </c>
+      <c r="Y7" s="89"/>
+      <c r="Z7" s="89"/>
+      <c r="AA7" s="89"/>
+      <c r="AB7" s="89"/>
+      <c r="AC7" s="89"/>
     </row>
     <row r="8" spans="1:32" ht="96.6">
-      <c r="A8" s="154"/>
-      <c r="B8" s="154" t="s">
+      <c r="A8" s="168"/>
+      <c r="B8" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="154" t="s">
+      <c r="C8" s="168" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -6848,31 +7103,37 @@
         <v>496</v>
       </c>
       <c r="H8" s="24"/>
-      <c r="I8" s="136" t="s">
+      <c r="I8" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J8" s="50"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="89"/>
+      <c r="N8" s="89"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="89"/>
+      <c r="T8" s="89"/>
+      <c r="U8" s="89"/>
+      <c r="V8" s="89"/>
+      <c r="W8" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X8" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X8))-ROW($G$2)+1),"")</f>
+        <v>Les événements ou critères déclenchant l’activation de la cellule de crise sont-ils clairement définis afin d’assurer une réponse rapide et cohérente ?</v>
+      </c>
+      <c r="Y8" s="89"/>
+      <c r="Z8" s="89"/>
+      <c r="AA8" s="89"/>
+      <c r="AB8" s="89"/>
+      <c r="AC8" s="89"/>
     </row>
     <row r="9" spans="1:32" ht="69">
-      <c r="A9" s="154"/>
-      <c r="B9" s="154"/>
-      <c r="C9" s="154"/>
+      <c r="A9" s="168"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
       <c r="D9" s="31" t="s">
         <v>10</v>
       </c>
@@ -6886,31 +7147,37 @@
         <v>497</v>
       </c>
       <c r="H9" s="24"/>
-      <c r="I9" s="136" t="s">
+      <c r="I9" s="132" t="s">
         <v>273</v>
       </c>
       <c r="J9" s="50"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="U9" s="90"/>
-      <c r="V9" s="90"/>
-      <c r="W9" s="90"/>
-      <c r="X9" s="90"/>
-      <c r="Y9" s="90"/>
-      <c r="Z9" s="90"/>
-      <c r="AA9" s="90"/>
-      <c r="AB9" s="90"/>
-      <c r="AC9" s="90"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="89"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="89"/>
+      <c r="U9" s="89"/>
+      <c r="V9" s="89"/>
+      <c r="W9" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X9" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X9))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y9" s="89"/>
+      <c r="Z9" s="89"/>
+      <c r="AA9" s="89"/>
+      <c r="AB9" s="89"/>
+      <c r="AC9" s="89"/>
     </row>
     <row r="10" spans="1:32" ht="82.8">
-      <c r="A10" s="154"/>
-      <c r="B10" s="154"/>
-      <c r="C10" s="186"/>
+      <c r="A10" s="168"/>
+      <c r="B10" s="168"/>
+      <c r="C10" s="200"/>
       <c r="D10" s="31" t="s">
         <v>13</v>
       </c>
@@ -6924,31 +7191,37 @@
         <v>498</v>
       </c>
       <c r="H10" s="24"/>
-      <c r="I10" s="127" t="s">
+      <c r="I10" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J10" s="50"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="R10" s="90"/>
-      <c r="S10" s="90"/>
-      <c r="T10" s="90"/>
-      <c r="U10" s="90"/>
-      <c r="V10" s="90"/>
-      <c r="W10" s="90"/>
-      <c r="X10" s="90"/>
-      <c r="Y10" s="90"/>
-      <c r="Z10" s="90"/>
-      <c r="AA10" s="90"/>
-      <c r="AB10" s="90"/>
-      <c r="AC10" s="90"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="89"/>
+      <c r="R10" s="89"/>
+      <c r="S10" s="89"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="89"/>
+      <c r="W10" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X10" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X10))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y10" s="89"/>
+      <c r="Z10" s="89"/>
+      <c r="AA10" s="89"/>
+      <c r="AB10" s="89"/>
+      <c r="AC10" s="89"/>
     </row>
     <row r="11" spans="1:32" ht="72">
-      <c r="A11" s="154"/>
-      <c r="B11" s="154"/>
-      <c r="C11" s="186"/>
+      <c r="A11" s="168"/>
+      <c r="B11" s="168"/>
+      <c r="C11" s="200"/>
       <c r="D11" s="31" t="s">
         <v>15</v>
       </c>
@@ -6962,30 +7235,36 @@
         <v>499</v>
       </c>
       <c r="H11" s="24"/>
-      <c r="I11" s="127" t="s">
+      <c r="I11" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J11" s="50"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="90"/>
-      <c r="N11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="S11" s="90"/>
-      <c r="T11" s="90"/>
-      <c r="U11" s="90"/>
-      <c r="V11" s="90"/>
-      <c r="W11" s="90"/>
-      <c r="X11" s="90"/>
-      <c r="Y11" s="90"/>
-      <c r="Z11" s="90"/>
-      <c r="AA11" s="90"/>
-      <c r="AB11" s="90"/>
-      <c r="AC11" s="90"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="89"/>
+      <c r="N11" s="89"/>
+      <c r="R11" s="89"/>
+      <c r="S11" s="89"/>
+      <c r="T11" s="89"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="89"/>
+      <c r="W11" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X11" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X11))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y11" s="89"/>
+      <c r="Z11" s="89"/>
+      <c r="AA11" s="89"/>
+      <c r="AB11" s="89"/>
+      <c r="AC11" s="89"/>
     </row>
     <row r="12" spans="1:32" ht="72">
-      <c r="A12" s="154"/>
-      <c r="B12" s="154"/>
+      <c r="A12" s="168"/>
+      <c r="B12" s="168"/>
       <c r="C12" s="3"/>
       <c r="D12" s="31" t="s">
         <v>20</v>
@@ -7000,30 +7279,36 @@
         <v>500</v>
       </c>
       <c r="H12" s="24"/>
-      <c r="I12" s="127" t="s">
+      <c r="I12" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J12" s="50"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="S12" s="90"/>
-      <c r="T12" s="90"/>
-      <c r="U12" s="90"/>
-      <c r="V12" s="90"/>
-      <c r="W12" s="90"/>
-      <c r="X12" s="90"/>
-      <c r="Y12" s="90"/>
-      <c r="Z12" s="90"/>
-      <c r="AA12" s="90"/>
-      <c r="AB12" s="90"/>
-      <c r="AC12" s="90"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="89"/>
+      <c r="R12" s="89"/>
+      <c r="S12" s="89"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="89"/>
+      <c r="V12" s="89"/>
+      <c r="W12" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X12" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X12))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y12" s="89"/>
+      <c r="Z12" s="89"/>
+      <c r="AA12" s="89"/>
+      <c r="AB12" s="89"/>
+      <c r="AC12" s="89"/>
     </row>
     <row r="13" spans="1:32" ht="69">
-      <c r="A13" s="154"/>
-      <c r="B13" s="154"/>
+      <c r="A13" s="168"/>
+      <c r="B13" s="168"/>
       <c r="C13" s="3"/>
       <c r="D13" s="31" t="s">
         <v>22</v>
@@ -7038,30 +7323,36 @@
         <v>501</v>
       </c>
       <c r="H13" s="24"/>
-      <c r="I13" s="127" t="s">
+      <c r="I13" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J13" s="50"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
-      <c r="V13" s="90"/>
-      <c r="W13" s="90"/>
-      <c r="X13" s="90"/>
-      <c r="Y13" s="90"/>
-      <c r="Z13" s="90"/>
-      <c r="AA13" s="90"/>
-      <c r="AB13" s="90"/>
-      <c r="AC13" s="90"/>
+      <c r="K13" s="89"/>
+      <c r="L13" s="89"/>
+      <c r="M13" s="89"/>
+      <c r="N13" s="89"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="89"/>
+      <c r="T13" s="89"/>
+      <c r="U13" s="89"/>
+      <c r="V13" s="89"/>
+      <c r="W13" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X13" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X13))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y13" s="89"/>
+      <c r="Z13" s="89"/>
+      <c r="AA13" s="89"/>
+      <c r="AB13" s="89"/>
+      <c r="AC13" s="89"/>
     </row>
     <row r="14" spans="1:32" ht="86.4">
-      <c r="A14" s="154"/>
-      <c r="B14" s="154"/>
+      <c r="A14" s="168"/>
+      <c r="B14" s="168"/>
       <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
@@ -7078,31 +7369,37 @@
         <v>502</v>
       </c>
       <c r="H14" s="24"/>
-      <c r="I14" s="127" t="s">
+      <c r="I14" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J14" s="50"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
-      <c r="V14" s="90"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="90"/>
-      <c r="Y14" s="90"/>
-      <c r="Z14" s="90"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="90"/>
-      <c r="AC14" s="90"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="89"/>
+      <c r="N14" s="89"/>
+      <c r="R14" s="89"/>
+      <c r="S14" s="89"/>
+      <c r="T14" s="89"/>
+      <c r="U14" s="89"/>
+      <c r="V14" s="89"/>
+      <c r="W14" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X14" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X14))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="89"/>
+      <c r="Z14" s="89"/>
+      <c r="AA14" s="89"/>
+      <c r="AB14" s="89"/>
+      <c r="AC14" s="89"/>
     </row>
     <row r="15" spans="1:32" ht="82.8">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="186" t="s">
+      <c r="A15" s="168"/>
+      <c r="B15" s="168"/>
+      <c r="C15" s="200" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="31" t="s">
@@ -7118,31 +7415,37 @@
         <v>503</v>
       </c>
       <c r="H15" s="24"/>
-      <c r="I15" s="127" t="s">
+      <c r="I15" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J15" s="50"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
-      <c r="V15" s="90"/>
-      <c r="W15" s="90"/>
-      <c r="X15" s="90"/>
-      <c r="Y15" s="90"/>
-      <c r="Z15" s="90"/>
-      <c r="AA15" s="90"/>
-      <c r="AB15" s="90"/>
-      <c r="AC15" s="90"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="89"/>
+      <c r="U15" s="89"/>
+      <c r="V15" s="89"/>
+      <c r="W15" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X15" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X15))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="89"/>
+      <c r="Z15" s="89"/>
+      <c r="AA15" s="89"/>
+      <c r="AB15" s="89"/>
+      <c r="AC15" s="89"/>
     </row>
     <row r="16" spans="1:32" ht="72">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="186"/>
+      <c r="A16" s="168"/>
+      <c r="B16" s="168"/>
+      <c r="C16" s="200"/>
       <c r="D16" s="30" t="s">
         <v>52</v>
       </c>
@@ -7156,30 +7459,36 @@
         <v>504</v>
       </c>
       <c r="H16" s="24"/>
-      <c r="I16" s="127" t="s">
+      <c r="I16" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J16" s="50"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="90"/>
-      <c r="M16" s="90"/>
-      <c r="N16" s="90"/>
-      <c r="R16" s="90"/>
-      <c r="S16" s="90"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="90"/>
-      <c r="V16" s="90"/>
-      <c r="W16" s="90"/>
-      <c r="X16" s="90"/>
-      <c r="Y16" s="90"/>
-      <c r="Z16" s="90"/>
-      <c r="AA16" s="90"/>
-      <c r="AB16" s="90"/>
-      <c r="AC16" s="90"/>
+      <c r="K16" s="89"/>
+      <c r="L16" s="89"/>
+      <c r="M16" s="89"/>
+      <c r="N16" s="89"/>
+      <c r="R16" s="89"/>
+      <c r="S16" s="89"/>
+      <c r="T16" s="89"/>
+      <c r="U16" s="89"/>
+      <c r="V16" s="89"/>
+      <c r="W16" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X16" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X16))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y16" s="89"/>
+      <c r="Z16" s="89"/>
+      <c r="AA16" s="89"/>
+      <c r="AB16" s="89"/>
+      <c r="AC16" s="89"/>
     </row>
     <row r="17" spans="1:29" ht="100.8">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
+      <c r="A17" s="168"/>
+      <c r="B17" s="168"/>
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
@@ -7196,29 +7505,35 @@
         <v>505</v>
       </c>
       <c r="H17" s="24"/>
-      <c r="I17" s="127" t="s">
+      <c r="I17" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J17" s="50"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="90"/>
-      <c r="X17" s="90"/>
-      <c r="Y17" s="90"/>
-      <c r="Z17" s="90"/>
-      <c r="AA17" s="90"/>
-      <c r="AB17" s="90"/>
-      <c r="AC17" s="90"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X17" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X17))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
     </row>
     <row r="18" spans="1:29" ht="86.4">
-      <c r="A18" s="154"/>
+      <c r="A18" s="168"/>
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
@@ -7238,29 +7553,35 @@
         <v>506</v>
       </c>
       <c r="H18" s="24"/>
-      <c r="I18" s="127" t="s">
+      <c r="I18" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J18" s="50"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="R18" s="90"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="90"/>
-      <c r="W18" s="90"/>
-      <c r="X18" s="90"/>
-      <c r="Y18" s="90"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="90"/>
-      <c r="AB18" s="90"/>
-      <c r="AC18" s="90"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="89"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="89"/>
+      <c r="W18" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X18" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X18))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y18" s="89"/>
+      <c r="Z18" s="89"/>
+      <c r="AA18" s="89"/>
+      <c r="AB18" s="89"/>
+      <c r="AC18" s="89"/>
     </row>
     <row r="19" spans="1:29" ht="115.2">
-      <c r="A19" s="154"/>
+      <c r="A19" s="168"/>
       <c r="B19" s="4" t="s">
         <v>38</v>
       </c>
@@ -7280,30 +7601,36 @@
         <v>507</v>
       </c>
       <c r="H19" s="24"/>
-      <c r="I19" s="127" t="s">
+      <c r="I19" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J19" s="50"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="X19" s="90"/>
-      <c r="Y19" s="90"/>
-      <c r="Z19" s="90"/>
-      <c r="AA19" s="90"/>
-      <c r="AB19" s="90"/>
-      <c r="AC19" s="90"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="89"/>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89"/>
+      <c r="T19" s="89"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="89"/>
+      <c r="W19" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X19" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X19))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="89"/>
+      <c r="Z19" s="89"/>
+      <c r="AA19" s="89"/>
+      <c r="AB19" s="89"/>
+      <c r="AC19" s="89"/>
     </row>
     <row r="20" spans="1:29" ht="115.2">
-      <c r="A20" s="154"/>
-      <c r="B20" s="154" t="s">
+      <c r="A20" s="168"/>
+      <c r="B20" s="168" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -7322,30 +7649,36 @@
         <v>508</v>
       </c>
       <c r="H20" s="24"/>
-      <c r="I20" s="127" t="s">
+      <c r="I20" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J20" s="50"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="U20" s="90"/>
-      <c r="V20" s="90"/>
-      <c r="W20" s="90"/>
-      <c r="X20" s="90"/>
-      <c r="Y20" s="90"/>
-      <c r="Z20" s="90"/>
-      <c r="AA20" s="90"/>
-      <c r="AB20" s="90"/>
-      <c r="AC20" s="90"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="89"/>
+      <c r="R20" s="89"/>
+      <c r="S20" s="89"/>
+      <c r="T20" s="89"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="89"/>
+      <c r="W20" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X20" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X20))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="89"/>
+      <c r="Z20" s="89"/>
+      <c r="AA20" s="89"/>
+      <c r="AB20" s="89"/>
+      <c r="AC20" s="89"/>
     </row>
     <row r="21" spans="1:29" ht="86.4">
-      <c r="A21" s="154"/>
-      <c r="B21" s="154"/>
+      <c r="A21" s="168"/>
+      <c r="B21" s="168"/>
       <c r="C21" s="25" t="s">
         <v>51</v>
       </c>
@@ -7362,30 +7695,36 @@
         <v>509</v>
       </c>
       <c r="H21" s="24"/>
-      <c r="I21" s="127" t="s">
+      <c r="I21" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J21" s="50"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="R21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="T21" s="90"/>
-      <c r="U21" s="90"/>
-      <c r="V21" s="90"/>
-      <c r="W21" s="90"/>
-      <c r="X21" s="90"/>
-      <c r="Y21" s="90"/>
-      <c r="Z21" s="90"/>
-      <c r="AA21" s="90"/>
-      <c r="AB21" s="90"/>
-      <c r="AC21" s="90"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="89"/>
+      <c r="W21" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X21" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X21))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="89"/>
+      <c r="Z21" s="89"/>
+      <c r="AA21" s="89"/>
+      <c r="AB21" s="89"/>
+      <c r="AC21" s="89"/>
     </row>
     <row r="22" spans="1:29" ht="100.8">
-      <c r="A22" s="154"/>
-      <c r="B22" s="154"/>
+      <c r="A22" s="168"/>
+      <c r="B22" s="168"/>
       <c r="C22" s="25" t="s">
         <v>54</v>
       </c>
@@ -7402,30 +7741,36 @@
         <v>76</v>
       </c>
       <c r="H22" s="24"/>
-      <c r="I22" s="127" t="s">
+      <c r="I22" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J22" s="50"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="90"/>
-      <c r="U22" s="90"/>
-      <c r="V22" s="90"/>
-      <c r="W22" s="90"/>
-      <c r="X22" s="90"/>
-      <c r="Y22" s="90"/>
-      <c r="Z22" s="90"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="90"/>
-      <c r="AC22" s="90"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="89"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X22" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X22))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="89"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="89"/>
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="89"/>
     </row>
     <row r="23" spans="1:29" ht="115.2">
-      <c r="A23" s="154"/>
-      <c r="B23" s="154"/>
+      <c r="A23" s="168"/>
+      <c r="B23" s="168"/>
       <c r="C23" s="25" t="s">
         <v>56</v>
       </c>
@@ -7442,30 +7787,36 @@
         <v>510</v>
       </c>
       <c r="H23" s="24"/>
-      <c r="I23" s="127" t="s">
+      <c r="I23" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J23" s="50"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="90"/>
-      <c r="U23" s="90"/>
-      <c r="V23" s="90"/>
-      <c r="W23" s="90"/>
-      <c r="X23" s="90"/>
-      <c r="Y23" s="90"/>
-      <c r="Z23" s="90"/>
-      <c r="AA23" s="90"/>
-      <c r="AB23" s="90"/>
-      <c r="AC23" s="90"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="89"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="89"/>
+      <c r="T23" s="89"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="89"/>
+      <c r="W23" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X23" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X23))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="89"/>
+      <c r="Z23" s="89"/>
+      <c r="AA23" s="89"/>
+      <c r="AB23" s="89"/>
+      <c r="AC23" s="89"/>
     </row>
     <row r="24" spans="1:29" ht="69">
-      <c r="A24" s="154"/>
-      <c r="B24" s="154"/>
+      <c r="A24" s="168"/>
+      <c r="B24" s="168"/>
       <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
@@ -7482,30 +7833,36 @@
         <v>512</v>
       </c>
       <c r="H24" s="24"/>
-      <c r="I24" s="127" t="s">
+      <c r="I24" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J24" s="50"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="R24" s="90"/>
-      <c r="S24" s="90"/>
-      <c r="T24" s="90"/>
-      <c r="U24" s="90"/>
-      <c r="V24" s="90"/>
-      <c r="W24" s="90"/>
-      <c r="X24" s="90"/>
-      <c r="Y24" s="90"/>
-      <c r="Z24" s="90"/>
-      <c r="AA24" s="90"/>
-      <c r="AB24" s="90"/>
-      <c r="AC24" s="90"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="89"/>
+      <c r="N24" s="89"/>
+      <c r="R24" s="89"/>
+      <c r="S24" s="89"/>
+      <c r="T24" s="89"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="89"/>
+      <c r="W24" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X24" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X24))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="89"/>
+      <c r="Z24" s="89"/>
+      <c r="AA24" s="89"/>
+      <c r="AB24" s="89"/>
+      <c r="AC24" s="89"/>
     </row>
     <row r="25" spans="1:29" ht="86.4">
-      <c r="A25" s="154"/>
-      <c r="B25" s="154"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="168"/>
       <c r="C25" s="4" t="s">
         <v>69</v>
       </c>
@@ -7522,30 +7879,36 @@
         <v>511</v>
       </c>
       <c r="H25" s="24"/>
-      <c r="I25" s="127" t="s">
+      <c r="I25" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J25" s="50"/>
-      <c r="K25" s="90"/>
-      <c r="L25" s="90"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="R25" s="90"/>
-      <c r="S25" s="90"/>
-      <c r="T25" s="90"/>
-      <c r="U25" s="90"/>
-      <c r="V25" s="90"/>
-      <c r="W25" s="90"/>
-      <c r="X25" s="90"/>
-      <c r="Y25" s="90"/>
-      <c r="Z25" s="90"/>
-      <c r="AA25" s="90"/>
-      <c r="AB25" s="90"/>
-      <c r="AC25" s="90"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="89"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="89"/>
+      <c r="V25" s="89"/>
+      <c r="W25" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X25" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X25))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y25" s="89"/>
+      <c r="Z25" s="89"/>
+      <c r="AA25" s="89"/>
+      <c r="AB25" s="89"/>
+      <c r="AC25" s="89"/>
     </row>
     <row r="26" spans="1:29" ht="86.4">
-      <c r="A26" s="154"/>
-      <c r="B26" s="154"/>
+      <c r="A26" s="168"/>
+      <c r="B26" s="168"/>
       <c r="C26" s="4" t="s">
         <v>75</v>
       </c>
@@ -7562,31 +7925,37 @@
         <v>513</v>
       </c>
       <c r="H26" s="24"/>
-      <c r="I26" s="127" t="s">
+      <c r="I26" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J26" s="50"/>
-      <c r="K26" s="90"/>
-      <c r="L26" s="90"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="90"/>
-      <c r="R26" s="90"/>
-      <c r="S26" s="90"/>
-      <c r="T26" s="90"/>
-      <c r="U26" s="90"/>
-      <c r="V26" s="90"/>
-      <c r="W26" s="90"/>
-      <c r="X26" s="90"/>
-      <c r="Y26" s="90"/>
-      <c r="Z26" s="90"/>
-      <c r="AA26" s="90"/>
-      <c r="AB26" s="90"/>
-      <c r="AC26" s="90"/>
+      <c r="K26" s="89"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="89"/>
+      <c r="N26" s="89"/>
+      <c r="R26" s="89"/>
+      <c r="S26" s="89"/>
+      <c r="T26" s="89"/>
+      <c r="U26" s="89"/>
+      <c r="V26" s="89"/>
+      <c r="W26" s="129">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="X26" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X26))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y26" s="89"/>
+      <c r="Z26" s="89"/>
+      <c r="AA26" s="89"/>
+      <c r="AB26" s="89"/>
+      <c r="AC26" s="89"/>
     </row>
     <row r="27" spans="1:29" ht="86.4">
-      <c r="A27" s="154"/>
-      <c r="B27" s="154"/>
-      <c r="C27" s="154" t="s">
+      <c r="A27" s="168"/>
+      <c r="B27" s="168"/>
+      <c r="C27" s="168" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="31" t="s">
@@ -7602,31 +7971,37 @@
         <v>514</v>
       </c>
       <c r="H27" s="24"/>
-      <c r="I27" s="127" t="s">
+      <c r="I27" s="123" t="s">
         <v>275</v>
       </c>
       <c r="J27" s="50"/>
-      <c r="K27" s="90"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="90"/>
-      <c r="R27" s="90"/>
-      <c r="S27" s="90"/>
-      <c r="T27" s="90"/>
-      <c r="U27" s="90"/>
-      <c r="V27" s="90"/>
-      <c r="W27" s="90"/>
-      <c r="X27" s="90"/>
-      <c r="Y27" s="90"/>
-      <c r="Z27" s="90"/>
-      <c r="AA27" s="90"/>
-      <c r="AB27" s="90"/>
-      <c r="AC27" s="90"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="89"/>
+      <c r="R27" s="89"/>
+      <c r="S27" s="89"/>
+      <c r="T27" s="89"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="89"/>
+      <c r="W27" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X27" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X27))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y27" s="89"/>
+      <c r="Z27" s="89"/>
+      <c r="AA27" s="89"/>
+      <c r="AB27" s="89"/>
+      <c r="AC27" s="89"/>
     </row>
     <row r="28" spans="1:29" ht="86.4">
-      <c r="A28" s="154"/>
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
+      <c r="A28" s="168"/>
+      <c r="B28" s="168"/>
+      <c r="C28" s="168"/>
       <c r="D28" s="31" t="s">
         <v>127</v>
       </c>
@@ -7640,33 +8015,39 @@
         <v>515</v>
       </c>
       <c r="H28" s="24"/>
-      <c r="I28" s="123" t="s">
+      <c r="I28" s="119" t="s">
         <v>273</v>
       </c>
       <c r="J28" s="50"/>
-      <c r="K28" s="90"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="90"/>
-      <c r="R28" s="90"/>
-      <c r="S28" s="90"/>
-      <c r="T28" s="90"/>
-      <c r="U28" s="90"/>
-      <c r="V28" s="90"/>
-      <c r="W28" s="90"/>
-      <c r="X28" s="90"/>
-      <c r="Y28" s="90"/>
-      <c r="Z28" s="90"/>
-      <c r="AA28" s="90"/>
-      <c r="AB28" s="90"/>
-      <c r="AC28" s="90"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="89"/>
+      <c r="N28" s="89"/>
+      <c r="R28" s="89"/>
+      <c r="S28" s="89"/>
+      <c r="T28" s="89"/>
+      <c r="U28" s="89"/>
+      <c r="V28" s="89"/>
+      <c r="W28" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X28" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X28))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y28" s="89"/>
+      <c r="Z28" s="89"/>
+      <c r="AA28" s="89"/>
+      <c r="AB28" s="89"/>
+      <c r="AC28" s="89"/>
     </row>
     <row r="29" spans="1:29" ht="86.4">
-      <c r="A29" s="154"/>
-      <c r="B29" s="154" t="s">
+      <c r="A29" s="168"/>
+      <c r="B29" s="168" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="154" t="s">
+      <c r="C29" s="168" t="s">
         <v>92</v>
       </c>
       <c r="D29" s="31" t="s">
@@ -7686,27 +8067,33 @@
         <v>275</v>
       </c>
       <c r="J29" s="50"/>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="90"/>
-      <c r="R29" s="90"/>
-      <c r="S29" s="90"/>
-      <c r="T29" s="90"/>
-      <c r="U29" s="90"/>
-      <c r="V29" s="90"/>
-      <c r="W29" s="90"/>
-      <c r="X29" s="90"/>
-      <c r="Y29" s="90"/>
-      <c r="Z29" s="90"/>
-      <c r="AA29" s="90"/>
-      <c r="AB29" s="90"/>
-      <c r="AC29" s="90"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="89"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="89"/>
+      <c r="T29" s="89"/>
+      <c r="U29" s="89"/>
+      <c r="V29" s="89"/>
+      <c r="W29" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X29" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X29))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y29" s="89"/>
+      <c r="Z29" s="89"/>
+      <c r="AA29" s="89"/>
+      <c r="AB29" s="89"/>
+      <c r="AC29" s="89"/>
     </row>
     <row r="30" spans="1:29" ht="82.8">
-      <c r="A30" s="154"/>
-      <c r="B30" s="154"/>
-      <c r="C30" s="154"/>
+      <c r="A30" s="168"/>
+      <c r="B30" s="168"/>
+      <c r="C30" s="168"/>
       <c r="D30" s="31" t="s">
         <v>103</v>
       </c>
@@ -7724,24 +8111,30 @@
         <v>275</v>
       </c>
       <c r="J30" s="50"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="90"/>
-      <c r="R30" s="90"/>
-      <c r="S30" s="90"/>
-      <c r="T30" s="90"/>
-      <c r="U30" s="90"/>
-      <c r="V30" s="90"/>
-      <c r="W30" s="90"/>
-      <c r="X30" s="90"/>
-      <c r="Y30" s="90"/>
-      <c r="Z30" s="90"/>
-      <c r="AA30" s="90"/>
-      <c r="AB30" s="90"/>
-      <c r="AC30" s="90"/>
+      <c r="K30" s="89"/>
+      <c r="L30" s="89"/>
+      <c r="R30" s="89"/>
+      <c r="S30" s="89"/>
+      <c r="T30" s="89"/>
+      <c r="U30" s="89"/>
+      <c r="V30" s="89"/>
+      <c r="W30" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X30" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X30))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y30" s="89"/>
+      <c r="Z30" s="89"/>
+      <c r="AA30" s="89"/>
+      <c r="AB30" s="89"/>
+      <c r="AC30" s="89"/>
     </row>
     <row r="31" spans="1:29" ht="69">
-      <c r="A31" s="154"/>
-      <c r="B31" s="154"/>
+      <c r="A31" s="168"/>
+      <c r="B31" s="168"/>
       <c r="C31" s="4"/>
       <c r="D31" s="31" t="s">
         <v>114</v>
@@ -7752,7 +8145,7 @@
       <c r="F31" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="158" t="s">
+      <c r="G31" s="172" t="s">
         <v>517</v>
       </c>
       <c r="H31" s="24"/>
@@ -7760,24 +8153,30 @@
         <v>275</v>
       </c>
       <c r="J31" s="50"/>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
-      <c r="R31" s="90"/>
-      <c r="S31" s="90"/>
-      <c r="T31" s="90"/>
-      <c r="U31" s="90"/>
-      <c r="V31" s="90"/>
-      <c r="W31" s="90"/>
-      <c r="X31" s="90"/>
-      <c r="Y31" s="90"/>
-      <c r="Z31" s="90"/>
-      <c r="AA31" s="90"/>
-      <c r="AB31" s="90"/>
-      <c r="AC31" s="90"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
+      <c r="R31" s="89"/>
+      <c r="S31" s="89"/>
+      <c r="T31" s="89"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="89"/>
+      <c r="W31" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X31" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X31))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+      <c r="Y31" s="89"/>
+      <c r="Z31" s="89"/>
+      <c r="AA31" s="89"/>
+      <c r="AB31" s="89"/>
+      <c r="AC31" s="89"/>
     </row>
     <row r="32" spans="1:29" ht="69">
-      <c r="A32" s="154"/>
-      <c r="B32" s="154" t="s">
+      <c r="A32" s="168"/>
+      <c r="B32" s="168" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7792,16 +8191,24 @@
       <c r="F32" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G32" s="158"/>
+      <c r="G32" s="172"/>
       <c r="H32" s="24"/>
       <c r="I32" s="4" t="s">
         <v>275</v>
       </c>
       <c r="J32" s="50"/>
-    </row>
-    <row r="33" spans="1:10" ht="55.2">
-      <c r="A33" s="154"/>
-      <c r="B33" s="154"/>
+      <c r="W32" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X32" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X32))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="55.2">
+      <c r="A33" s="168"/>
+      <c r="B33" s="168"/>
       <c r="C33" s="4" t="s">
         <v>98</v>
       </c>
@@ -7814,19 +8221,27 @@
       <c r="F33" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="158"/>
+      <c r="G33" s="172"/>
       <c r="H33" s="24"/>
       <c r="I33" s="4" t="s">
         <v>275</v>
       </c>
       <c r="J33" s="50"/>
-    </row>
-    <row r="34" spans="1:10" ht="69">
-      <c r="A34" s="154"/>
-      <c r="B34" s="154" t="s">
+      <c r="W33" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X33" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X33))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="69">
+      <c r="A34" s="168"/>
+      <c r="B34" s="168" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="85"/>
+      <c r="C34" s="84"/>
       <c r="D34" s="31" t="s">
         <v>120</v>
       </c>
@@ -7844,11 +8259,19 @@
         <v>275</v>
       </c>
       <c r="J34" s="50"/>
-    </row>
-    <row r="35" spans="1:10" ht="69">
-      <c r="A35" s="154"/>
-      <c r="B35" s="154"/>
-      <c r="C35" s="154" t="s">
+      <c r="W34" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X34" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X34))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="69">
+      <c r="A35" s="168"/>
+      <c r="B35" s="168"/>
+      <c r="C35" s="168" t="s">
         <v>124</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -7868,42 +8291,76 @@
         <v>275</v>
       </c>
       <c r="J35" s="50"/>
-    </row>
-    <row r="36" spans="1:10" ht="232.05" customHeight="1">
-      <c r="A36" s="154"/>
-      <c r="B36" s="154"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="189" t="s">
+      <c r="W35" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X35" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X35))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="232.05" customHeight="1">
+      <c r="A36" s="168"/>
+      <c r="B36" s="168"/>
+      <c r="C36" s="168"/>
+      <c r="D36" s="203" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="154" t="s">
+      <c r="E36" s="168" t="s">
         <v>255</v>
       </c>
-      <c r="F36" s="154" t="s">
+      <c r="F36" s="168" t="s">
         <v>261</v>
       </c>
-      <c r="G36" s="154" t="s">
+      <c r="G36" s="168" t="s">
         <v>518</v>
       </c>
-      <c r="H36" s="154"/>
-      <c r="I36" s="154" t="s">
+      <c r="H36" s="168"/>
+      <c r="I36" s="168" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="154"/>
-      <c r="B37" s="154"/>
-      <c r="C37" s="154"/>
-      <c r="D37" s="189"/>
-      <c r="E37" s="154"/>
-      <c r="F37" s="154"/>
-      <c r="G37" s="154"/>
-      <c r="H37" s="154"/>
-      <c r="I37" s="154"/>
+      <c r="W36" s="129" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X36" s="129" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X36))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:24">
+      <c r="A37" s="168"/>
+      <c r="B37" s="168"/>
+      <c r="C37" s="168"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="168"/>
+      <c r="F37" s="168"/>
+      <c r="G37" s="168"/>
+      <c r="H37" s="168"/>
+      <c r="I37" s="168"/>
       <c r="J37" s="50"/>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="W37" s="89" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X37" s="89" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X37))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:24">
       <c r="J38" s="50"/>
+      <c r="X38" s="89" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X38))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:24">
+      <c r="X39" s="89" t="str">
+        <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X39))-ROW($G$2)+1),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -7933,29 +8390,29 @@
     <mergeCell ref="C29:C30"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:D1">
-    <cfRule type="expression" dxfId="39" priority="7">
+    <cfRule type="expression" dxfId="35" priority="7">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I1">
-    <cfRule type="expression" dxfId="38" priority="5">
+    <cfRule type="expression" dxfId="34" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="6">
+    <cfRule type="expression" dxfId="33" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I36">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7977,7 +8434,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="31.6640625" customWidth="1"/>
@@ -7995,9 +8452,10 @@
     <col min="16" max="16" width="22.44140625" customWidth="1"/>
     <col min="17" max="17" width="19.109375" customWidth="1"/>
     <col min="18" max="18" width="38.5546875" customWidth="1"/>
+    <col min="21" max="21" width="112.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1">
+    <row r="1" spans="1:21" ht="15" thickBot="1">
       <c r="J1" s="50"/>
       <c r="K1" s="50"/>
       <c r="L1" s="50"/>
@@ -8008,7 +8466,7 @@
       <c r="Q1" s="50"/>
       <c r="R1" s="50"/>
     </row>
-    <row r="2" spans="1:18" ht="40.950000000000003" customHeight="1" thickBot="1">
+    <row r="2" spans="1:21" ht="40.950000000000003" customHeight="1" thickBot="1">
       <c r="A2" s="50"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -8019,11 +8477,11 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="172" t="s">
+      <c r="L2" s="186" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="173"/>
-      <c r="N2" s="116" t="s">
+      <c r="M2" s="187"/>
+      <c r="N2" s="112" t="s">
         <v>600</v>
       </c>
       <c r="O2" s="58" t="s">
@@ -8039,7 +8497,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="14.55" customHeight="1">
+    <row r="3" spans="1:21" ht="14.55" customHeight="1">
       <c r="A3" s="50"/>
       <c r="B3" s="6" t="s">
         <v>148</v>
@@ -8067,44 +8525,46 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="162">
+      <c r="L3" s="176">
         <f>COUNTA(H4:H25)</f>
         <v>21</v>
       </c>
-      <c r="M3" s="174"/>
-      <c r="N3" s="190">
+      <c r="M3" s="188"/>
+      <c r="N3" s="204">
         <f>L3-Q3</f>
         <v>20</v>
       </c>
-      <c r="O3" s="177">
+      <c r="O3" s="191">
         <f>COUNTIF(J4:J21,"Yes")</f>
         <v>6</v>
       </c>
-      <c r="P3" s="180">
+      <c r="P3" s="194">
         <f>COUNTIF(J4:J21,"No")</f>
         <v>10</v>
       </c>
-      <c r="Q3" s="183">
+      <c r="Q3" s="197">
         <f>COUNTIF(J4:J21,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R3" s="165">
+      <c r="R3" s="179">
         <f>O3/N3</f>
         <v>0.3</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="94.5" customHeight="1">
+      <c r="T3" s="219"/>
+      <c r="U3" s="219"/>
+    </row>
+    <row r="4" spans="1:21" ht="94.5" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="155" t="s">
+      <c r="B4" s="169" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="149" t="s">
+      <c r="C4" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="154" t="s">
+      <c r="D4" s="168" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="193" t="s">
+      <c r="E4" s="207" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -8113,54 +8573,64 @@
       <c r="G4" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="158" t="s">
+      <c r="H4" s="172" t="s">
         <v>321</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="J4" s="154" t="s">
+      <c r="J4" s="168" t="s">
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="178"/>
-      <c r="P4" s="181"/>
-      <c r="Q4" s="184"/>
-      <c r="R4" s="166"/>
-    </row>
-    <row r="5" spans="1:18" ht="81" customHeight="1" thickBot="1">
+      <c r="L4" s="177"/>
+      <c r="M4" s="189"/>
+      <c r="N4" s="205"/>
+      <c r="O4" s="192"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="198"/>
+      <c r="R4" s="180"/>
+      <c r="T4" s="144"/>
+      <c r="U4" s="144"/>
+    </row>
+    <row r="5" spans="1:21" ht="81" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="156"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="193"/>
+      <c r="B5" s="170"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="12" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="H5" s="158"/>
+      <c r="H5" s="172"/>
       <c r="I5" s="24" t="s">
         <v>568</v>
       </c>
-      <c r="J5" s="154"/>
+      <c r="J5" s="168"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="192"/>
-      <c r="O5" s="179"/>
-      <c r="P5" s="182"/>
-      <c r="Q5" s="185"/>
-      <c r="R5" s="167"/>
-    </row>
-    <row r="6" spans="1:18" ht="111" customHeight="1" thickBot="1">
+      <c r="L5" s="178"/>
+      <c r="M5" s="190"/>
+      <c r="N5" s="206"/>
+      <c r="O5" s="193"/>
+      <c r="P5" s="196"/>
+      <c r="Q5" s="199"/>
+      <c r="R5" s="181"/>
+      <c r="T5" s="144" t="str">
+        <f t="shared" ref="T5:T25" si="0">IF(J5="No",ROW(), "")</f>
+        <v/>
+      </c>
+      <c r="U5" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U5))-ROW($H$4)+1),"")</f>
+        <v>Les membres de la cellule de crise sont-ils identifiés (IT, sécurité, juridique, communication, direction) ?</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="111" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="151"/>
+      <c r="B6" s="170"/>
+      <c r="C6" s="165"/>
       <c r="D6" s="2" t="s">
         <v>384</v>
       </c>
@@ -8179,7 +8649,7 @@
       <c r="I6" s="24" t="s">
         <v>569</v>
       </c>
-      <c r="J6" s="136" t="s">
+      <c r="J6" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K6" s="50"/>
@@ -8189,23 +8659,31 @@
       <c r="P6" s="67"/>
       <c r="Q6" s="67"/>
       <c r="R6" s="50"/>
-    </row>
-    <row r="7" spans="1:18" ht="61.95" customHeight="1" thickBot="1">
+      <c r="T6" s="144">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="U6" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U6))-ROW($H$4)+1),"")</f>
+        <v>Les rôles et responsabilités sont-ils clairement définis et compris ? Existe-t-il des remplaçants en cas d’indisponibilité ?</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="61.95" customHeight="1" thickBot="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="156"/>
-      <c r="C7" s="154" t="s">
+      <c r="B7" s="170"/>
+      <c r="C7" s="168" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="154" t="s">
+      <c r="D7" s="168" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="193" t="s">
+      <c r="E7" s="207" t="s">
         <v>546</v>
       </c>
-      <c r="F7" s="194" t="s">
+      <c r="F7" s="208" t="s">
         <v>547</v>
       </c>
-      <c r="G7" s="195" t="s">
+      <c r="G7" s="209" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -8214,45 +8692,61 @@
       <c r="I7" s="24" t="s">
         <v>570</v>
       </c>
-      <c r="J7" s="136" t="s">
+      <c r="J7" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K7" s="50"/>
-      <c r="L7" s="91" t="s">
+      <c r="L7" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="M7" s="125" t="s">
+      <c r="M7" s="121" t="s">
         <v>612</v>
       </c>
       <c r="N7" s="50"/>
-      <c r="O7" s="113"/>
-    </row>
-    <row r="8" spans="1:18" ht="53.55" customHeight="1">
+      <c r="O7" s="109"/>
+      <c r="T7" s="144">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U7" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U7))-ROW($H$4)+1),"")</f>
+        <v>Les outils de monitoring permettent-ils une détection en temps réel des incidents majeurs ?</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="53.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="156"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="193"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="195"/>
+      <c r="B8" s="170"/>
+      <c r="C8" s="168"/>
+      <c r="D8" s="168"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="209"/>
       <c r="H8" s="24" t="s">
         <v>320</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>570</v>
       </c>
-      <c r="J8" s="136" t="s">
+      <c r="J8" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="114"/>
-    </row>
-    <row r="9" spans="1:18" ht="57.6">
+      <c r="O8" s="110"/>
+      <c r="T8" s="144">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U8" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U8))-ROW($H$4)+1),"")</f>
+        <v>Combien de temps faut-il en moyenne pour isoler un système compromis ?</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="57.6">
       <c r="A9" s="50"/>
-      <c r="B9" s="156"/>
+      <c r="B9" s="170"/>
       <c r="C9" s="4" t="s">
         <v>306</v>
       </c>
@@ -8274,7 +8768,7 @@
       <c r="I9" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="J9" s="136" t="s">
+      <c r="J9" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K9" s="50"/>
@@ -8282,14 +8776,22 @@
       <c r="M9" s="50"/>
       <c r="N9" s="50"/>
       <c r="O9" s="50"/>
-    </row>
-    <row r="10" spans="1:18" ht="58.05" customHeight="1">
+      <c r="T9" s="144">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U9" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U9))-ROW($H$4)+1),"")</f>
+        <v>Des runbooks sont-ils disponibles pour les scénarios cyber majeurs</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="58.05" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="156"/>
-      <c r="C10" s="186" t="s">
+      <c r="B10" s="170"/>
+      <c r="C10" s="200" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="149" t="s">
+      <c r="D10" s="163" t="s">
         <v>439</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -8307,7 +8809,7 @@
       <c r="I10" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="J10" s="136" t="s">
+      <c r="J10" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K10" s="50"/>
@@ -8315,12 +8817,20 @@
       <c r="M10" s="50"/>
       <c r="N10" s="50"/>
       <c r="O10" s="50"/>
-    </row>
-    <row r="11" spans="1:18" ht="43.2">
+      <c r="T10" s="144">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="U10" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U10))-ROW($H$4)+1),"")</f>
+        <v>Un prestataire de réponse à incident (IR) est-il contractuellement prévu ?</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="43.2">
       <c r="A11" s="50"/>
-      <c r="B11" s="156"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="151"/>
+      <c r="B11" s="170"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="165"/>
       <c r="E11" s="2" t="s">
         <v>392</v>
       </c>
@@ -8336,7 +8846,7 @@
       <c r="I11" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="J11" s="136" t="s">
+      <c r="J11" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K11" s="50"/>
@@ -8344,14 +8854,22 @@
       <c r="M11" s="50"/>
       <c r="N11" s="50"/>
       <c r="O11" s="50"/>
-    </row>
-    <row r="12" spans="1:18" ht="52.05" customHeight="1">
+      <c r="T11" s="144">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="U11" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U11))-ROW($H$4)+1),"")</f>
+        <v>Existe-t-il un mécanisme de communication avec CERT/autorités ?</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="52.05" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="156"/>
-      <c r="C12" s="155" t="s">
+      <c r="B12" s="170"/>
+      <c r="C12" s="169" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="186" t="s">
+      <c r="D12" s="200" t="s">
         <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -8369,19 +8887,27 @@
       <c r="I12" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="J12" s="136" t="s">
+      <c r="J12" s="132" t="s">
         <v>273</v>
       </c>
       <c r="L12" s="50"/>
       <c r="M12" s="50"/>
       <c r="N12" s="50"/>
       <c r="O12" s="50"/>
-    </row>
-    <row r="13" spans="1:18" ht="58.5" customHeight="1">
+      <c r="T12" s="144">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="U12" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U12))-ROW($H$4)+1),"")</f>
+        <v>Comment La coordination avec fournisseurs, cloud providers et partenaires est-elle intégrée dans la gestion de crise ?</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="58.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="156"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="186"/>
+      <c r="B13" s="170"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="200"/>
       <c r="E13" s="2" t="s">
         <v>401</v>
       </c>
@@ -8397,18 +8923,26 @@
       <c r="I13" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="J13" s="136" t="s">
+      <c r="J13" s="132" t="s">
         <v>273</v>
       </c>
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
       <c r="N13" s="50"/>
       <c r="O13" s="50"/>
-    </row>
-    <row r="14" spans="1:18" ht="53.55" customHeight="1">
+      <c r="T13" s="144">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="U13" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U13))-ROW($H$4)+1),"")</f>
+        <v>Le temps de détection (MTTD) et de réponse (MTTR) est-il mesuré ?</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="156"/>
-      <c r="C14" s="157"/>
+      <c r="B14" s="170"/>
+      <c r="C14" s="171"/>
       <c r="D14" s="3" t="s">
         <v>441</v>
       </c>
@@ -8427,16 +8961,24 @@
       <c r="I14" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="J14" s="136" t="s">
+      <c r="J14" s="132" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="66" customHeight="1">
-      <c r="B15" s="156"/>
-      <c r="C15" s="154" t="s">
+      <c r="T14" s="144">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="U14" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U14))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="66" customHeight="1">
+      <c r="B15" s="170"/>
+      <c r="C15" s="168" t="s">
         <v>315</v>
       </c>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="169" t="s">
         <v>442</v>
       </c>
       <c r="E15" s="24" t="s">
@@ -8454,14 +8996,22 @@
       <c r="I15" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="J15" s="136" t="s">
+      <c r="J15" s="132" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="43.2">
-      <c r="B16" s="156"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="157"/>
+      <c r="T15" s="144">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="U15" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U15))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="43.2">
+      <c r="B16" s="170"/>
+      <c r="C16" s="168"/>
+      <c r="D16" s="171"/>
       <c r="E16" s="24" t="s">
         <v>407</v>
       </c>
@@ -8480,13 +9030,21 @@
       <c r="J16" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="77.55" customHeight="1">
-      <c r="B17" s="156"/>
-      <c r="C17" s="149" t="s">
+      <c r="T16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U16))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:21" ht="77.55" customHeight="1">
+      <c r="B17" s="170"/>
+      <c r="C17" s="163" t="s">
         <v>316</v>
       </c>
-      <c r="D17" s="155" t="s">
+      <c r="D17" s="169" t="s">
         <v>443</v>
       </c>
       <c r="E17" s="74" t="s">
@@ -8507,11 +9065,19 @@
       <c r="J17" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="57.6">
-      <c r="B18" s="156"/>
-      <c r="C18" s="151"/>
-      <c r="D18" s="157"/>
+      <c r="T17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U17))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="2:21" ht="57.6">
+      <c r="B18" s="170"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="171"/>
       <c r="E18" s="72" t="s">
         <v>413</v>
       </c>
@@ -8530,10 +9096,18 @@
       <c r="J18" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="42" customHeight="1">
-      <c r="B19" s="156"/>
-      <c r="C19" s="186" t="s">
+      <c r="T18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U18))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:21" ht="42" customHeight="1">
+      <c r="B19" s="170"/>
+      <c r="C19" s="200" t="s">
         <v>323</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -8557,10 +9131,18 @@
       <c r="J19" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="39" customHeight="1">
-      <c r="B20" s="156"/>
-      <c r="C20" s="186"/>
+      <c r="T19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U19))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:21" ht="39" customHeight="1">
+      <c r="B20" s="170"/>
+      <c r="C20" s="200"/>
       <c r="D20" s="3" t="s">
         <v>445</v>
       </c>
@@ -8582,13 +9164,21 @@
       <c r="J20" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="43.2">
-      <c r="B21" s="156"/>
-      <c r="C21" s="154" t="s">
+      <c r="T20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U20))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="43.2">
+      <c r="B21" s="170"/>
+      <c r="C21" s="168" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="155" t="s">
+      <c r="D21" s="169" t="s">
         <v>446</v>
       </c>
       <c r="E21" s="65" t="s">
@@ -8609,11 +9199,19 @@
       <c r="J21" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" ht="41.55" customHeight="1">
-      <c r="B22" s="156"/>
-      <c r="C22" s="154"/>
-      <c r="D22" s="157"/>
+      <c r="T21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U21))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:21" ht="41.55" customHeight="1">
+      <c r="B22" s="170"/>
+      <c r="C22" s="168"/>
+      <c r="D22" s="171"/>
       <c r="E22" s="24" t="s">
         <v>427</v>
       </c>
@@ -8632,9 +9230,17 @@
       <c r="J22" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" ht="57.6">
-      <c r="B23" s="156"/>
+      <c r="T22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U22))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:21" ht="57.6">
+      <c r="B23" s="170"/>
       <c r="C23" s="4" t="s">
         <v>330</v>
       </c>
@@ -8659,10 +9265,18 @@
       <c r="J23" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" ht="43.2">
-      <c r="B24" s="156"/>
-      <c r="C24" s="186" t="s">
+      <c r="T23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U23))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="43.2">
+      <c r="B24" s="170"/>
+      <c r="C24" s="200" t="s">
         <v>333</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -8680,16 +9294,24 @@
       <c r="H24" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="I24" s="84" t="s">
+      <c r="I24" s="83" t="s">
         <v>586</v>
       </c>
       <c r="J24" s="61" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" ht="43.2">
-      <c r="B25" s="157"/>
-      <c r="C25" s="186"/>
+      <c r="T24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U24))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="2:21" ht="43.2">
+      <c r="B25" s="171"/>
+      <c r="C25" s="200"/>
       <c r="D25" s="3" t="s">
         <v>447</v>
       </c>
@@ -8711,8 +9333,16 @@
       <c r="J25" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="26" spans="2:10">
+      <c r="T25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U25))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:21">
       <c r="J26" s="66"/>
     </row>
   </sheetData>
@@ -8749,29 +9379,29 @@
     <mergeCell ref="Q3:Q5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="32" priority="11">
+    <cfRule type="expression" dxfId="28" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="31" priority="5">
+    <cfRule type="expression" dxfId="27" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="6">
+    <cfRule type="expression" dxfId="26" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6:J26">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8792,7 +9422,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -8811,10 +9441,11 @@
     <col min="18" max="18" width="47.44140625" customWidth="1"/>
     <col min="19" max="19" width="25.44140625" customWidth="1"/>
     <col min="20" max="20" width="30.77734375" customWidth="1"/>
+    <col min="23" max="23" width="159" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1"/>
-    <row r="2" spans="1:20" ht="24" thickBot="1">
+    <row r="1" spans="1:23" ht="15" thickBot="1"/>
+    <row r="2" spans="1:23" ht="24" thickBot="1">
       <c r="A2" s="50"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -8826,11 +9457,11 @@
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="172" t="s">
+      <c r="L2" s="186" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="173"/>
-      <c r="N2" s="116" t="s">
+      <c r="M2" s="187"/>
+      <c r="N2" s="112" t="s">
         <v>601</v>
       </c>
       <c r="O2" s="58" t="s">
@@ -8846,7 +9477,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="33.450000000000003" customHeight="1" thickBot="1">
+    <row r="3" spans="1:23" ht="33.450000000000003" customHeight="1" thickBot="1">
       <c r="A3" s="50"/>
       <c r="B3" s="6" t="s">
         <v>148</v>
@@ -8876,41 +9507,43 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="162">
+      <c r="L3" s="176">
         <f>COUNTA(H4:H25)</f>
         <v>11</v>
       </c>
-      <c r="M3" s="174"/>
-      <c r="N3" s="190">
+      <c r="M3" s="188"/>
+      <c r="N3" s="204">
         <f>L3-Q3</f>
         <v>9</v>
       </c>
-      <c r="O3" s="177">
+      <c r="O3" s="191">
         <f>COUNTIF(J4:J25,"Yes")</f>
         <v>4</v>
       </c>
-      <c r="P3" s="180">
+      <c r="P3" s="194">
         <f>COUNTIF(J4:J25,"No")</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="183">
+      <c r="Q3" s="197">
         <f>COUNTIF(J4:J25,"N/A")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="165">
+      <c r="R3" s="179">
         <f>O3/N3</f>
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="120" customHeight="1" thickBot="1">
+      <c r="V3" s="219"/>
+      <c r="W3" s="219"/>
+    </row>
+    <row r="4" spans="1:23" ht="120" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="154" t="s">
+      <c r="B4" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="154" t="s">
+      <c r="C4" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="199" t="s">
+      <c r="D4" s="213" t="s">
         <v>343</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -8922,35 +9555,43 @@
       <c r="G4" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="199" t="s">
+      <c r="H4" s="213" t="s">
         <v>346</v>
       </c>
-      <c r="I4" s="196" t="s">
+      <c r="I4" s="210" t="s">
         <v>525</v>
       </c>
-      <c r="J4" s="154" t="s">
+      <c r="J4" s="168" t="s">
         <v>273</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="178"/>
-      <c r="P4" s="181"/>
-      <c r="Q4" s="184"/>
-      <c r="R4" s="166"/>
-      <c r="S4" s="91" t="s">
+      <c r="L4" s="177"/>
+      <c r="M4" s="189"/>
+      <c r="N4" s="205"/>
+      <c r="O4" s="192"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="198"/>
+      <c r="R4" s="180"/>
+      <c r="S4" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="T4" s="125" t="s">
+      <c r="T4" s="121" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="169.05" customHeight="1" thickBot="1">
+      <c r="V4" s="144">
+        <f>IF(J4="No",ROW(), "")</f>
+        <v>4</v>
+      </c>
+      <c r="W4" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W4:W$4))-ROW($H$4)+1),"")</f>
+        <v>Comment les processus métiers sont-ils identifiés, priorisés et classifiés ?</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="169.05" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="154"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="199"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="8" t="s">
         <v>347</v>
       </c>
@@ -8960,23 +9601,31 @@
       <c r="G5" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="199"/>
-      <c r="I5" s="197"/>
-      <c r="J5" s="154"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="168"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="192"/>
-      <c r="O5" s="179"/>
-      <c r="P5" s="182"/>
-      <c r="Q5" s="185"/>
-      <c r="R5" s="167"/>
-    </row>
-    <row r="6" spans="1:20" ht="141" customHeight="1">
+      <c r="L5" s="178"/>
+      <c r="M5" s="190"/>
+      <c r="N5" s="206"/>
+      <c r="O5" s="193"/>
+      <c r="P5" s="196"/>
+      <c r="Q5" s="199"/>
+      <c r="R5" s="181"/>
+      <c r="V5" s="144" t="str">
+        <f t="shared" ref="V5:V25" si="0">IF(J5="No",ROW(), "")</f>
+        <v/>
+      </c>
+      <c r="W5" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W5))-ROW($H$4)+1),"")</f>
+        <v>Toutes les dépendances internes et externes, y compris les fournisseurs, partenaires, systèmes informatiques et le personnel, ont-elles été identifiées et intégrées dans le BIA ?</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="141" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="154"/>
-      <c r="C6" s="154"/>
-      <c r="D6" s="199"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="213"/>
       <c r="E6" s="8" t="s">
         <v>349</v>
       </c>
@@ -8986,13 +9635,13 @@
       <c r="G6" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="199" t="s">
+      <c r="H6" s="213" t="s">
         <v>351</v>
       </c>
-      <c r="I6" s="196" t="s">
+      <c r="I6" s="210" t="s">
         <v>526</v>
       </c>
-      <c r="J6" s="154" t="s">
+      <c r="J6" s="168" t="s">
         <v>273</v>
       </c>
       <c r="K6" s="50"/>
@@ -9000,12 +9649,20 @@
       <c r="M6" s="57"/>
       <c r="N6" s="57"/>
       <c r="O6" s="50"/>
-    </row>
-    <row r="7" spans="1:20" ht="151.94999999999999" customHeight="1">
+      <c r="V6" s="144">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="W6" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W6))-ROW($H$4)+1),"")</f>
+        <v>Comment l’entreprise s’assure-t-elle que les équipes connaissent leurs rôles en cas de crise ?</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="151.94999999999999" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="154"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="199"/>
+      <c r="B7" s="168"/>
+      <c r="C7" s="168"/>
+      <c r="D7" s="213"/>
       <c r="E7" s="27" t="s">
         <v>352</v>
       </c>
@@ -9015,20 +9672,28 @@
       <c r="G7" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="199"/>
-      <c r="I7" s="197"/>
-      <c r="J7" s="154"/>
+      <c r="H7" s="213"/>
+      <c r="I7" s="211"/>
+      <c r="J7" s="168"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
-      <c r="O7" s="113"/>
-    </row>
-    <row r="8" spans="1:20" ht="109.5" customHeight="1">
+      <c r="O7" s="109"/>
+      <c r="V7" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W7" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W7))-ROW($H$4)+1),"")</f>
+        <v>Le personnel critique a-t-il été identifié et formé de manière appropriée pour faire face aux perturbations ?</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="109.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="158" t="s">
+      <c r="B8" s="168"/>
+      <c r="C8" s="168"/>
+      <c r="D8" s="172" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="27" t="s">
@@ -9040,23 +9705,31 @@
       <c r="G8" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="158" t="s">
+      <c r="H8" s="172" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="149" t="s">
+      <c r="I8" s="163" t="s">
         <v>527</v>
       </c>
-      <c r="J8" s="154" t="s">
+      <c r="J8" s="168" t="s">
         <v>274</v>
       </c>
       <c r="K8" s="50"/>
-      <c r="O8" s="114"/>
-    </row>
-    <row r="9" spans="1:20" ht="136.05000000000001" customHeight="1">
+      <c r="O8" s="110"/>
+      <c r="V8" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W8" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W8))-ROW($H$4)+1),"")</f>
+        <v>Quand les scénarios du BIA ont-ils été testés pour la dernière fois et quels types de tests ont été réalisés ?</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="136.05000000000001" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="154"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="158"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="172"/>
       <c r="E9" s="27" t="s">
         <v>356</v>
       </c>
@@ -9066,18 +9739,26 @@
       <c r="G9" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="H9" s="158"/>
-      <c r="I9" s="151"/>
-      <c r="J9" s="154"/>
+      <c r="H9" s="172"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="168"/>
       <c r="K9" s="50"/>
-    </row>
-    <row r="10" spans="1:20" ht="132.44999999999999" customHeight="1">
+      <c r="V9" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W9" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W9))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="132.44999999999999" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="154"/>
-      <c r="C10" s="154" t="s">
+      <c r="B10" s="168"/>
+      <c r="C10" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="158" t="s">
+      <c r="D10" s="172" t="s">
         <v>358</v>
       </c>
       <c r="E10" s="27" t="s">
@@ -9089,22 +9770,30 @@
       <c r="G10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="199" t="s">
+      <c r="H10" s="213" t="s">
         <v>528</v>
       </c>
-      <c r="I10" s="196" t="s">
+      <c r="I10" s="210" t="s">
         <v>529</v>
       </c>
-      <c r="J10" s="154" t="s">
+      <c r="J10" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K10" s="50"/>
-    </row>
-    <row r="11" spans="1:20" ht="138.44999999999999" customHeight="1">
+      <c r="V10" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W10" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W10))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="138.44999999999999" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="154"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="158"/>
+      <c r="B11" s="168"/>
+      <c r="C11" s="168"/>
+      <c r="D11" s="172"/>
       <c r="E11" s="31" t="s">
         <v>361</v>
       </c>
@@ -9114,16 +9803,24 @@
       <c r="G11" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="199"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="154"/>
+      <c r="H11" s="213"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="168"/>
       <c r="K11" s="50"/>
-    </row>
-    <row r="12" spans="1:20" ht="121.5" customHeight="1">
+      <c r="V11" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W11" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W11))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="121.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="158" t="s">
+      <c r="B12" s="168"/>
+      <c r="C12" s="168"/>
+      <c r="D12" s="172" t="s">
         <v>307</v>
       </c>
       <c r="E12" s="31" t="s">
@@ -9135,22 +9832,30 @@
       <c r="G12" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="199" t="s">
+      <c r="H12" s="213" t="s">
         <v>342</v>
       </c>
-      <c r="I12" s="196" t="s">
+      <c r="I12" s="210" t="s">
         <v>530</v>
       </c>
-      <c r="J12" s="154" t="s">
+      <c r="J12" s="168" t="s">
         <v>274</v>
       </c>
       <c r="K12" s="50"/>
-    </row>
-    <row r="13" spans="1:20" ht="154.5" customHeight="1">
+      <c r="V12" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W12" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W12))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="154.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="154"/>
-      <c r="C13" s="154"/>
-      <c r="D13" s="158"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="168"/>
+      <c r="D13" s="172"/>
       <c r="E13" s="31" t="s">
         <v>364</v>
       </c>
@@ -9160,15 +9865,23 @@
       <c r="G13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="199"/>
-      <c r="I13" s="201"/>
-      <c r="J13" s="154"/>
+      <c r="H13" s="213"/>
+      <c r="I13" s="215"/>
+      <c r="J13" s="168"/>
       <c r="K13" s="50"/>
-    </row>
-    <row r="14" spans="1:20" ht="144.44999999999999" customHeight="1">
+      <c r="V13" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W13" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W13))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="144.44999999999999" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
+      <c r="B14" s="168"/>
+      <c r="C14" s="168"/>
       <c r="D14" s="24" t="s">
         <v>18</v>
       </c>
@@ -9181,25 +9894,33 @@
       <c r="G14" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="199"/>
-      <c r="I14" s="197"/>
-      <c r="J14" s="154"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="211"/>
+      <c r="J14" s="168"/>
       <c r="K14" s="50"/>
-    </row>
-    <row r="15" spans="1:20" ht="52.95" customHeight="1">
+      <c r="V14" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W14" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W14))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="52.95" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154" t="s">
+      <c r="B15" s="168"/>
+      <c r="C15" s="168"/>
+      <c r="D15" s="168" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="202" t="s">
+      <c r="E15" s="216" t="s">
         <v>369</v>
       </c>
-      <c r="F15" s="200" t="s">
+      <c r="F15" s="214" t="s">
         <v>370</v>
       </c>
-      <c r="G15" s="203" t="s">
+      <c r="G15" s="217" t="s">
         <v>169</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -9208,34 +9929,50 @@
       <c r="I15" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="J15" s="136" t="s">
+      <c r="J15" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K15" s="50"/>
-    </row>
-    <row r="16" spans="1:20" ht="91.05" customHeight="1">
+      <c r="V15" s="144">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="W15" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W15))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="91.05" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="202"/>
-      <c r="F16" s="200"/>
-      <c r="G16" s="203"/>
+      <c r="B16" s="168"/>
+      <c r="C16" s="168"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="214"/>
+      <c r="G16" s="217"/>
       <c r="H16" s="70" t="s">
         <v>532</v>
       </c>
       <c r="I16" s="70" t="s">
         <v>533</v>
       </c>
-      <c r="J16" s="136" t="s">
+      <c r="J16" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K16" s="50"/>
-    </row>
-    <row r="17" spans="1:15" ht="124.05" customHeight="1">
+      <c r="V16" s="144">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="W16" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W16))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="124.05" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
+      <c r="B17" s="168"/>
+      <c r="C17" s="168"/>
       <c r="D17" s="60" t="s">
         <v>368</v>
       </c>
@@ -9248,21 +9985,29 @@
       <c r="G17" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H17" s="199" t="s">
+      <c r="H17" s="213" t="s">
         <v>371</v>
       </c>
-      <c r="I17" s="196" t="s">
+      <c r="I17" s="210" t="s">
         <v>534</v>
       </c>
-      <c r="J17" s="154" t="s">
+      <c r="J17" s="168" t="s">
         <v>273</v>
       </c>
       <c r="K17" s="50"/>
-    </row>
-    <row r="18" spans="1:15" ht="123" customHeight="1">
+      <c r="V17" s="144">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W17" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W17))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="123" customHeight="1">
       <c r="A18" s="50"/>
-      <c r="B18" s="154"/>
-      <c r="C18" s="154"/>
+      <c r="B18" s="168"/>
+      <c r="C18" s="168"/>
       <c r="D18" s="24" t="s">
         <v>19</v>
       </c>
@@ -9275,16 +10020,24 @@
       <c r="G18" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="199"/>
-      <c r="I18" s="197"/>
-      <c r="J18" s="154"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="211"/>
+      <c r="J18" s="168"/>
       <c r="K18" s="50"/>
-    </row>
-    <row r="19" spans="1:15" ht="118.05" customHeight="1">
+      <c r="V18" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W18" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W18))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="118.05" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="154"/>
-      <c r="C19" s="154"/>
-      <c r="D19" s="158" t="s">
+      <c r="B19" s="168"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="172" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="31" t="s">
@@ -9296,24 +10049,32 @@
       <c r="G19" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="198" t="s">
+      <c r="H19" s="212" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="196" t="s">
+      <c r="I19" s="210" t="s">
         <v>535</v>
       </c>
-      <c r="J19" s="154" t="s">
+      <c r="J19" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K19" s="50"/>
       <c r="M19" s="47"/>
       <c r="N19" s="47"/>
-    </row>
-    <row r="20" spans="1:15" ht="123" customHeight="1">
+      <c r="V19" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W19" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W19))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="123" customHeight="1">
       <c r="A20" s="50"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="158"/>
+      <c r="B20" s="168"/>
+      <c r="C20" s="168"/>
+      <c r="D20" s="172"/>
       <c r="E20" s="31" t="s">
         <v>30</v>
       </c>
@@ -9323,20 +10084,28 @@
       <c r="G20" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="198"/>
-      <c r="I20" s="201"/>
-      <c r="J20" s="154"/>
+      <c r="H20" s="212"/>
+      <c r="I20" s="215"/>
+      <c r="J20" s="168"/>
       <c r="K20" s="51"/>
       <c r="L20" s="45"/>
       <c r="M20" s="45"/>
       <c r="N20" s="45"/>
       <c r="O20" s="46"/>
-    </row>
-    <row r="21" spans="1:15" ht="106.05" customHeight="1">
+      <c r="V20" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W20" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W20))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="106.05" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="154"/>
-      <c r="C21" s="154"/>
-      <c r="D21" s="158"/>
+      <c r="B21" s="168"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="172"/>
       <c r="E21" s="31" t="s">
         <v>26</v>
       </c>
@@ -9346,59 +10115,83 @@
       <c r="G21" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="198"/>
-      <c r="I21" s="197"/>
-      <c r="J21" s="154"/>
+      <c r="H21" s="212"/>
+      <c r="I21" s="211"/>
+      <c r="J21" s="168"/>
       <c r="K21" s="50"/>
-    </row>
-    <row r="22" spans="1:15" ht="78" customHeight="1">
+      <c r="V21" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W21" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W21))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="78" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="154"/>
-      <c r="C22" s="154" t="s">
+      <c r="B22" s="168"/>
+      <c r="C22" s="168" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="154" t="s">
+      <c r="D22" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="202" t="s">
+      <c r="E22" s="216" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="200" t="s">
+      <c r="F22" s="214" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="H22" s="199" t="s">
+      <c r="H22" s="213" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="196" t="s">
+      <c r="I22" s="210" t="s">
         <v>536</v>
       </c>
-      <c r="J22" s="154" t="s">
+      <c r="J22" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K22" s="50"/>
-    </row>
-    <row r="23" spans="1:15" ht="72">
+      <c r="V22" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W22" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W22))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="72">
       <c r="A23" s="50"/>
-      <c r="B23" s="154"/>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="202"/>
-      <c r="F23" s="200"/>
+      <c r="B23" s="168"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="168"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="214"/>
       <c r="G23" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="H23" s="199"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="154"/>
+      <c r="H23" s="213"/>
+      <c r="I23" s="215"/>
+      <c r="J23" s="168"/>
       <c r="K23" s="50"/>
-    </row>
-    <row r="24" spans="1:15" ht="72">
+      <c r="V23" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W23" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W23))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="72">
       <c r="A24" s="50"/>
-      <c r="B24" s="154"/>
-      <c r="C24" s="154"/>
+      <c r="B24" s="168"/>
+      <c r="C24" s="168"/>
       <c r="D24" s="24" t="s">
         <v>12</v>
       </c>
@@ -9411,15 +10204,23 @@
       <c r="G24" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="199"/>
-      <c r="I24" s="197"/>
-      <c r="J24" s="154"/>
+      <c r="H24" s="213"/>
+      <c r="I24" s="211"/>
+      <c r="J24" s="168"/>
       <c r="K24" s="50"/>
-    </row>
-    <row r="25" spans="1:15" ht="100.8">
+      <c r="V24" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W24" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W24))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="100.8">
       <c r="A25" s="50"/>
-      <c r="B25" s="154"/>
-      <c r="C25" s="154"/>
+      <c r="B25" s="168"/>
+      <c r="C25" s="168"/>
       <c r="D25" s="2" t="s">
         <v>17</v>
       </c>
@@ -9438,22 +10239,30 @@
       <c r="I25" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="J25" s="127" t="s">
+      <c r="J25" s="123" t="s">
         <v>275</v>
       </c>
       <c r="K25" s="50"/>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="V25" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W25" s="144" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W25))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26" s="50"/>
       <c r="B26" s="49"/>
       <c r="D26" s="49"/>
       <c r="K26" s="50"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:23">
       <c r="A27" s="50"/>
       <c r="B27" s="49"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:23">
       <c r="B28" s="49"/>
     </row>
   </sheetData>
@@ -9507,59 +10316,59 @@
     <mergeCell ref="I10:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:D3 E3:E4">
-    <cfRule type="expression" dxfId="25" priority="11">
+    <cfRule type="expression" dxfId="21" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="24" priority="5">
+    <cfRule type="expression" dxfId="20" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="6">
+    <cfRule type="expression" dxfId="19" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="16" priority="20">
       <formula>$A6="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="19" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="13" priority="17">
       <formula>$A5="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F4">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>$A4="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="10">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J8 J10 J12 J19 J22 J25 J6 J15:J17">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9580,7 +10389,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -9600,13 +10409,14 @@
     <col min="18" max="18" width="20.21875" customWidth="1"/>
     <col min="19" max="19" width="19.88671875" customWidth="1"/>
     <col min="20" max="20" width="42.21875" customWidth="1"/>
+    <col min="23" max="23" width="108.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1">
+    <row r="1" spans="1:23" ht="15" thickBot="1">
       <c r="K1" s="50"/>
       <c r="L1" s="50"/>
     </row>
-    <row r="2" spans="1:20" ht="24" thickBot="1">
+    <row r="2" spans="1:23" ht="24" thickBot="1">
       <c r="A2" s="50"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -9617,14 +10427,14 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
-      <c r="K2" s="205"/>
+      <c r="K2" s="136"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-      <c r="N2" s="172" t="s">
+      <c r="N2" s="186" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="173"/>
-      <c r="P2" s="116" t="s">
+      <c r="O2" s="187"/>
+      <c r="P2" s="112" t="s">
         <v>601</v>
       </c>
       <c r="Q2" s="58" t="s">
@@ -9640,7 +10450,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="14.55" customHeight="1">
+    <row r="3" spans="1:23" ht="14.55" customHeight="1">
       <c r="A3" s="50"/>
       <c r="B3" s="6" t="s">
         <v>148</v>
@@ -9669,44 +10479,46 @@
       <c r="J3" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="K3" s="206"/>
+      <c r="K3" s="137"/>
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="162">
+      <c r="N3" s="176">
         <f>COUNTA(H4:H13)</f>
         <v>4</v>
       </c>
-      <c r="O3" s="174"/>
-      <c r="P3" s="190">
+      <c r="O3" s="188"/>
+      <c r="P3" s="204">
         <f>N3-S3</f>
         <v>4</v>
       </c>
-      <c r="Q3" s="177">
+      <c r="Q3" s="191">
         <f>COUNTIF(J4:J10,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="180">
+      <c r="R3" s="194">
         <f>COUNTIF(J4:J11,"No")</f>
         <v>2</v>
       </c>
-      <c r="S3" s="183">
+      <c r="S3" s="197">
         <f>COUNTIF(J4:J10,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="T3" s="177">
+      <c r="T3" s="191">
         <f>Q3/P3</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="78" customHeight="1">
+      <c r="V3" s="219"/>
+      <c r="W3" s="219"/>
+    </row>
+    <row r="4" spans="1:23" ht="78" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="154" t="s">
+      <c r="B4" s="168" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="154" t="s">
+      <c r="C4" s="168" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="154" t="s">
+      <c r="D4" s="168" t="s">
         <v>102</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -9718,31 +10530,39 @@
       <c r="G4" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="H4" s="158" t="s">
+      <c r="H4" s="172" t="s">
         <v>268</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>544</v>
       </c>
-      <c r="J4" s="154" t="s">
+      <c r="J4" s="168" t="s">
         <v>275</v>
       </c>
-      <c r="K4" s="205"/>
+      <c r="K4" s="136"/>
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="191"/>
-      <c r="Q4" s="178"/>
-      <c r="R4" s="181"/>
-      <c r="S4" s="184"/>
-      <c r="T4" s="178"/>
-    </row>
-    <row r="5" spans="1:20" ht="82.95" customHeight="1" thickBot="1">
+      <c r="N4" s="177"/>
+      <c r="O4" s="189"/>
+      <c r="P4" s="205"/>
+      <c r="Q4" s="192"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="198"/>
+      <c r="T4" s="192"/>
+      <c r="V4" s="7" t="str">
+        <f>IF(J4="No",ROW(), "")</f>
+        <v/>
+      </c>
+      <c r="W4" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W4:W$4))-ROW($H$4)+1),"")</f>
+        <v>Où sont stockées les preuves et qui peut y accéder ?</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="82.95" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="154"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
       <c r="E5" s="12" t="s">
         <v>107</v>
       </c>
@@ -9752,27 +10572,35 @@
       <c r="G5" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="158"/>
+      <c r="H5" s="172"/>
       <c r="I5" s="24" t="s">
         <v>545</v>
       </c>
-      <c r="J5" s="154"/>
+      <c r="J5" s="168"/>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
-      <c r="N5" s="204"/>
-      <c r="O5" s="176"/>
-      <c r="P5" s="192"/>
-      <c r="Q5" s="179"/>
-      <c r="R5" s="182"/>
-      <c r="S5" s="185"/>
-      <c r="T5" s="179"/>
-    </row>
-    <row r="6" spans="1:20" ht="88.5" customHeight="1" thickBot="1">
+      <c r="N5" s="218"/>
+      <c r="O5" s="190"/>
+      <c r="P5" s="206"/>
+      <c r="Q5" s="193"/>
+      <c r="R5" s="196"/>
+      <c r="S5" s="199"/>
+      <c r="T5" s="193"/>
+      <c r="V5" s="7" t="str">
+        <f t="shared" ref="V5:V11" si="0">IF(J5="No",ROW(), "")</f>
+        <v/>
+      </c>
+      <c r="W5" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W5))-ROW($H$4)+1),"")</f>
+        <v>Comment l’entreprise s’assure-t-elle que les enregistrements sont complets et n’ont fait l’objet d’aucune altération ?</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="88.5" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="154"/>
-      <c r="C6" s="154"/>
-      <c r="D6" s="154" t="s">
+      <c r="B6" s="168"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -9784,31 +10612,39 @@
       <c r="G6" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H6" s="152" t="s">
+      <c r="H6" s="166" t="s">
         <v>267</v>
       </c>
       <c r="I6" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="J6" s="154" t="s">
+      <c r="J6" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K6" s="50"/>
       <c r="L6" s="50"/>
       <c r="M6" s="50"/>
-      <c r="N6" s="135" t="s">
+      <c r="N6" s="131" t="s">
         <v>611</v>
       </c>
-      <c r="O6" s="134" t="s">
+      <c r="O6" s="130" t="s">
         <v>612</v>
       </c>
       <c r="P6" s="57"/>
-    </row>
-    <row r="7" spans="1:20" ht="76.5" customHeight="1">
+      <c r="V6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W6" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W6))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="76.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="154"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
+      <c r="B7" s="168"/>
+      <c r="C7" s="168"/>
+      <c r="D7" s="168"/>
       <c r="E7" s="12" t="s">
         <v>109</v>
       </c>
@@ -9818,24 +10654,32 @@
       <c r="G7" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="H7" s="153"/>
+      <c r="H7" s="167"/>
       <c r="I7" s="24" t="s">
         <v>539</v>
       </c>
-      <c r="J7" s="154"/>
+      <c r="J7" s="168"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
       <c r="O7" s="50"/>
       <c r="P7" s="50"/>
-      <c r="Q7" s="113"/>
-    </row>
-    <row r="8" spans="1:20" ht="98.55" customHeight="1">
+      <c r="Q7" s="109"/>
+      <c r="V7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W7" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W7))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="98.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154" t="s">
+      <c r="B8" s="168"/>
+      <c r="C8" s="168"/>
+      <c r="D8" s="168" t="s">
         <v>110</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -9847,26 +10691,34 @@
       <c r="G8" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="H8" s="158" t="s">
+      <c r="H8" s="172" t="s">
         <v>266</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>540</v>
       </c>
-      <c r="J8" s="149" t="s">
+      <c r="J8" s="163" t="s">
         <v>273</v>
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
-      <c r="Q8" s="117"/>
+      <c r="Q8" s="113"/>
       <c r="R8" s="50"/>
-    </row>
-    <row r="9" spans="1:20" ht="75.45" customHeight="1">
+      <c r="V8" s="7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="W8" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W8))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="75.45" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="154"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
       <c r="E9" s="12" t="s">
         <v>112</v>
       </c>
@@ -9876,62 +10728,86 @@
       <c r="G9" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H9" s="158"/>
+      <c r="H9" s="172"/>
       <c r="I9" s="24" t="s">
         <v>541</v>
       </c>
-      <c r="J9" s="150"/>
+      <c r="J9" s="164"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
-      <c r="Q9" s="79"/>
-    </row>
-    <row r="10" spans="1:20" ht="109.95" customHeight="1">
+      <c r="Q9" s="78"/>
+      <c r="V9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W9" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W9))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="109.95" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="154"/>
-      <c r="C10" s="154"/>
-      <c r="D10" s="154"/>
-      <c r="E10" s="194" t="s">
+      <c r="B10" s="168"/>
+      <c r="C10" s="168"/>
+      <c r="D10" s="168"/>
+      <c r="E10" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="194" t="s">
+      <c r="F10" s="208" t="s">
         <v>227</v>
       </c>
-      <c r="G10" s="195" t="s">
+      <c r="G10" s="209" t="s">
         <v>206</v>
       </c>
-      <c r="H10" s="158"/>
+      <c r="H10" s="172"/>
       <c r="I10" s="24" t="s">
         <v>542</v>
       </c>
-      <c r="J10" s="151"/>
+      <c r="J10" s="165"/>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
-      <c r="Q10" s="79"/>
-    </row>
-    <row r="11" spans="1:20" ht="63" customHeight="1">
+      <c r="Q10" s="78"/>
+      <c r="V10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W10" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W10))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="63" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="154"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="154"/>
-      <c r="E11" s="194"/>
-      <c r="F11" s="194"/>
-      <c r="G11" s="195"/>
+      <c r="B11" s="168"/>
+      <c r="C11" s="168"/>
+      <c r="D11" s="168"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="208"/>
+      <c r="G11" s="209"/>
       <c r="H11" s="2" t="s">
         <v>280</v>
       </c>
       <c r="I11" s="24" t="s">
         <v>543</v>
       </c>
-      <c r="J11" s="136" t="s">
+      <c r="J11" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K11" s="50"/>
       <c r="L11" s="50"/>
       <c r="M11" s="50"/>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="V11" s="7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="W11" s="7" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W11))-ROW($H$4)+1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="50"/>
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
@@ -9962,29 +10838,29 @@
     <mergeCell ref="R3:R5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:K3">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J11">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10017,258 +10893,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="115" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="115" t="s">
         <v>608</v>
       </c>
-      <c r="C1" s="119" t="s">
+      <c r="C1" s="115" t="s">
         <v>609</v>
       </c>
-      <c r="D1" s="119" t="s">
+      <c r="D1" s="115" t="s">
         <v>275</v>
       </c>
-      <c r="E1" s="119" t="s">
+      <c r="E1" s="115" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="119" t="s">
+      <c r="F1" s="115" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="119" t="s">
+      <c r="G1" s="115" t="s">
         <v>610</v>
       </c>
-      <c r="H1" s="119" t="s">
+      <c r="H1" s="115" t="s">
         <v>602</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="115" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="115" t="s">
         <v>595</v>
       </c>
-      <c r="B2" s="110">
+      <c r="B2" s="106">
         <f>'Questionnaire Domain Forensics'!$N$3</f>
         <v>4</v>
       </c>
-      <c r="C2" s="110">
+      <c r="C2" s="106">
         <f>'Questionnaire Domain Forensics'!$P$3</f>
         <v>4</v>
       </c>
-      <c r="D2" s="110">
+      <c r="D2" s="106">
         <f>'Questionnaire Domain Forensics'!$Q$3</f>
         <v>2</v>
       </c>
-      <c r="E2" s="110">
+      <c r="E2" s="106">
         <f>'Questionnaire Domain Forensics'!$R$3</f>
         <v>2</v>
       </c>
-      <c r="F2" s="110">
+      <c r="F2" s="106">
         <f>'Questionnaire Domain Forensics'!$S$3</f>
         <v>0</v>
       </c>
-      <c r="G2" s="121">
+      <c r="G2" s="117">
         <f>'Questionnaire Domain Forensics'!$T$3</f>
         <v>0.5</v>
       </c>
-      <c r="H2" s="124">
+      <c r="H2" s="120">
         <f>PONDERATION!$L$20</f>
         <v>6</v>
       </c>
-      <c r="I2" s="126" t="str">
+      <c r="I2" s="122" t="str">
         <f>'Questionnaire Domain Forensics'!$O$6</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="115" t="s">
         <v>596</v>
       </c>
-      <c r="B3" s="110">
+      <c r="B3" s="106">
         <f>'Question Continuité d’activité'!$L$3</f>
         <v>11</v>
       </c>
-      <c r="C3" s="110">
+      <c r="C3" s="106">
         <f>'Question Continuité d’activité'!$N$3</f>
         <v>9</v>
       </c>
-      <c r="D3" s="110">
+      <c r="D3" s="106">
         <f>'Question Continuité d’activité'!$O$3</f>
         <v>4</v>
       </c>
-      <c r="E3" s="110">
+      <c r="E3" s="106">
         <f>'Question Continuité d’activité'!$P$3</f>
         <v>5</v>
       </c>
-      <c r="F3" s="110">
+      <c r="F3" s="106">
         <f>'Question Continuité d’activité'!$Q$3</f>
         <v>2</v>
       </c>
-      <c r="G3" s="121">
+      <c r="G3" s="117">
         <f>'Question Continuité d’activité'!$R$3</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="H3" s="124">
+      <c r="H3" s="120">
         <f>PONDERATION!$L$19</f>
         <v>23</v>
       </c>
-      <c r="I3" s="126" t="str">
+      <c r="I3" s="122" t="str">
         <f>'Question Continuité d’activité'!$T$4</f>
         <v>Dhia</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="115" t="s">
         <v>597</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="106">
         <f>'Questionnaire Gestion de crise'!$L$3</f>
         <v>21</v>
       </c>
-      <c r="C4" s="110">
+      <c r="C4" s="106">
         <f>'Questionnaire Gestion de crise'!$N$3</f>
         <v>20</v>
       </c>
-      <c r="D4" s="110">
+      <c r="D4" s="106">
         <f>'Questionnaire Gestion de crise'!$O$3</f>
         <v>6</v>
       </c>
-      <c r="E4" s="110">
+      <c r="E4" s="106">
         <f>'Questionnaire Gestion de crise'!$P$3</f>
         <v>10</v>
       </c>
-      <c r="F4" s="110">
+      <c r="F4" s="106">
         <f>'Questionnaire Gestion de crise'!$Q$3</f>
         <v>1</v>
       </c>
-      <c r="G4" s="121">
+      <c r="G4" s="117">
         <f>'Questionnaire Gestion de crise'!$R$3</f>
         <v>0.3</v>
       </c>
-      <c r="H4" s="124">
+      <c r="H4" s="120">
         <f>PONDERATION!$L$18</f>
         <v>20</v>
       </c>
-      <c r="I4" s="126" t="str">
+      <c r="I4" s="122" t="str">
         <f>'Questionnaire Gestion de crise'!$M$7</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="115" t="s">
         <v>598</v>
       </c>
-      <c r="B5" s="122">
+      <c r="B5" s="118">
         <f>'Questionnaire Gestion Incidents'!$P$2</f>
         <v>17</v>
       </c>
-      <c r="C5" s="110">
+      <c r="C5" s="106">
         <f>'Questionnaire Gestion Incidents'!$R$2</f>
-        <v>16</v>
-      </c>
-      <c r="D5" s="122">
+        <v>17</v>
+      </c>
+      <c r="D5" s="118">
         <f>'Questionnaire Gestion Incidents'!$N$2</f>
         <v>14</v>
       </c>
-      <c r="E5" s="122">
+      <c r="E5" s="118">
         <f>'Questionnaire Gestion Incidents'!$N$3</f>
-        <v>2</v>
-      </c>
-      <c r="F5" s="122">
+        <v>3</v>
+      </c>
+      <c r="F5" s="118">
         <f>'Questionnaire Gestion Incidents'!$N$4</f>
-        <v>1</v>
-      </c>
-      <c r="G5" s="121">
+        <v>0</v>
+      </c>
+      <c r="G5" s="117">
         <f>'Questionnaire Gestion Incidents'!$L$2</f>
-        <v>0.875</v>
-      </c>
-      <c r="H5" s="124">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="H5" s="120">
         <f>PONDERATION!$L$17</f>
         <v>18.5</v>
       </c>
-      <c r="I5" s="126" t="str">
+      <c r="I5" s="122" t="str">
         <f>'Questionnaire Gestion Incidents'!$N$5</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="115" t="s">
         <v>599</v>
       </c>
-      <c r="B6" s="110">
+      <c r="B6" s="106">
         <f>'Questionnaire Confirmitee'!$L$3</f>
         <v>4</v>
       </c>
-      <c r="C6" s="110">
+      <c r="C6" s="106">
         <f>'Questionnaire Confirmitee'!$Q$3</f>
         <v>4</v>
       </c>
-      <c r="D6" s="110">
+      <c r="D6" s="106">
         <f>'Questionnaire Confirmitee'!$N$3</f>
         <v>1</v>
       </c>
-      <c r="E6" s="110">
+      <c r="E6" s="106">
         <f>'Questionnaire Confirmitee'!$O$3</f>
         <v>3</v>
       </c>
-      <c r="F6" s="110">
+      <c r="F6" s="106">
         <f>'Questionnaire Confirmitee'!$P$3</f>
         <v>0</v>
       </c>
-      <c r="G6" s="121">
+      <c r="G6" s="117">
         <f>'Questionnaire Confirmitee'!$R$3</f>
         <v>0.25</v>
       </c>
-      <c r="H6" s="124">
+      <c r="H6" s="120">
         <f>PONDERATION!$L$21</f>
         <v>6</v>
       </c>
-      <c r="I6" s="126" t="str">
+      <c r="I6" s="122" t="str">
         <f>'Questionnaire Confirmitee'!$M$7</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="124" t="s">
         <v>594</v>
       </c>
-      <c r="B7" s="129">
+      <c r="B7" s="125">
         <f>'Questionnaire Gouvernance '!$Q$2</f>
         <v>35</v>
       </c>
-      <c r="C7" s="129">
+      <c r="C7" s="125">
         <f>'Questionnaire Gouvernance '!$S$2</f>
         <v>35</v>
       </c>
-      <c r="D7" s="129">
+      <c r="D7" s="125">
         <f>'Questionnaire Gouvernance '!$O$2</f>
         <v>26</v>
       </c>
-      <c r="E7" s="129">
+      <c r="E7" s="125">
         <f>'Questionnaire Gouvernance '!$O$3</f>
         <v>9</v>
       </c>
-      <c r="F7" s="129">
+      <c r="F7" s="125">
         <f>'Questionnaire Gouvernance '!$O$4</f>
         <v>0</v>
       </c>
-      <c r="G7" s="130">
+      <c r="G7" s="126">
         <f>'Questionnaire Gouvernance '!$L$2</f>
         <v>0.74285714285714288</v>
       </c>
-      <c r="H7" s="131">
+      <c r="H7" s="127">
         <f>PONDERATION!$L$16</f>
         <v>26.5</v>
       </c>
-      <c r="I7" s="126" t="str">
+      <c r="I7" s="122" t="str">
         <f>'Questionnaire Gouvernance '!$U$2</f>
         <v>Dhia</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="132" t="s">
+      <c r="A8" s="128" t="s">
         <v>272</v>
       </c>
       <c r="B8" s="18">
@@ -10277,7 +11153,7 @@
       </c>
       <c r="C8" s="18">
         <f>SUM(C2:C7)</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" s="18">
         <f t="shared" ref="D8:F8" si="0">SUM(D2:D7)</f>
@@ -10285,15 +11161,15 @@
       </c>
       <c r="E8" s="18">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G8" s="133">
+        <v>3</v>
+      </c>
+      <c r="G8" s="129">
         <f>G2*H2+G3*H3+G4*H4+G5*H5+G6*H6+G7*H7</f>
-        <v>56.595436507936512</v>
+        <v>55.64323062558357</v>
       </c>
       <c r="H8" s="18">
         <f>SUM(H2:H7)</f>
@@ -10309,157 +11185,157 @@
       <c r="F10" s="47"/>
     </row>
     <row r="11" spans="1:9" ht="21">
-      <c r="A11" s="112" t="s">
+      <c r="A11" s="108" t="s">
         <v>603</v>
       </c>
-      <c r="B11" s="112" t="s">
+      <c r="B11" s="108" t="s">
         <v>607</v>
       </c>
-      <c r="C11" s="112" t="s">
+      <c r="C11" s="108" t="s">
         <v>604</v>
       </c>
-      <c r="D11" s="112" t="s">
+      <c r="D11" s="108" t="s">
         <v>605</v>
       </c>
-      <c r="E11" s="112" t="s">
+      <c r="E11" s="108" t="s">
         <v>606</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="114"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="120">
+      <c r="A12" s="116">
         <v>1</v>
       </c>
       <c r="B12" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="C12" s="111">
+      <c r="C12" s="107">
         <v>0</v>
       </c>
-      <c r="D12" s="111">
+      <c r="D12" s="107">
         <v>16</v>
       </c>
-      <c r="E12" s="111">
+      <c r="E12" s="107">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="120">
+      <c r="A13" s="116">
         <v>2</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="C13" s="111">
+      <c r="C13" s="107">
         <v>17</v>
       </c>
-      <c r="D13" s="111">
+      <c r="D13" s="107">
         <v>33</v>
       </c>
-      <c r="E13" s="111">
+      <c r="E13" s="107">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="120">
+      <c r="A14" s="116">
         <v>3</v>
       </c>
       <c r="B14" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="C14" s="111">
+      <c r="C14" s="107">
         <v>34</v>
       </c>
-      <c r="D14" s="111">
+      <c r="D14" s="107">
         <v>51</v>
       </c>
-      <c r="E14" s="111">
+      <c r="E14" s="107">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="120">
+      <c r="A15" s="116">
         <v>4</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="C15" s="111">
+      <c r="C15" s="107">
         <v>52</v>
       </c>
-      <c r="D15" s="111">
+      <c r="D15" s="107">
         <v>68</v>
       </c>
-      <c r="E15" s="111">
+      <c r="E15" s="107">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="120">
+      <c r="A16" s="116">
         <v>5</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="C16" s="111">
+      <c r="C16" s="107">
         <v>69</v>
       </c>
-      <c r="D16" s="111">
+      <c r="D16" s="107">
         <v>85</v>
       </c>
-      <c r="E16" s="111">
+      <c r="E16" s="107">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="120">
+      <c r="A17" s="116">
         <v>6</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="C17" s="111">
+      <c r="C17" s="107">
         <v>86</v>
       </c>
-      <c r="D17" s="111">
+      <c r="D17" s="107">
         <v>100</v>
       </c>
-      <c r="E17" s="111">
+      <c r="E17" s="107">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="210" t="s">
+      <c r="A20" s="141" t="s">
         <v>595</v>
       </c>
-      <c r="B20" s="210" t="s">
+      <c r="B20" s="141" t="s">
         <v>596</v>
       </c>
-      <c r="C20" s="210" t="s">
+      <c r="C20" s="141" t="s">
         <v>597</v>
       </c>
-      <c r="D20" s="210" t="s">
+      <c r="D20" s="141" t="s">
         <v>598</v>
       </c>
-      <c r="E20" s="210" t="s">
+      <c r="E20" s="141" t="s">
         <v>599</v>
       </c>
-      <c r="F20" s="210" t="s">
+      <c r="F20" s="141" t="s">
         <v>594</v>
       </c>
-      <c r="G20" s="209"/>
+      <c r="G20" s="140"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="207"/>
+      <c r="A24" s="138"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="208"/>
+      <c r="A25" s="139"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="207"/>
+      <c r="A26" s="138"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="207"/>
+      <c r="A27" s="138"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Default_Template.xlsx
+++ b/Data/Default_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="PONDERATION" sheetId="10" r:id="rId1"/>
@@ -2600,7 +2600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2934,9 +2934,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2982,12 +2979,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3015,6 +3007,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3219,12 +3236,62 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <u val="double"/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -4330,20 +4397,20 @@
     <row r="3" spans="1:31" ht="28.8">
       <c r="A3" s="50"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="161" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="157"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="40"/>
-      <c r="K3" s="156" t="s">
+      <c r="K3" s="161" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="157"/>
+      <c r="L3" s="162"/>
       <c r="M3" s="40"/>
       <c r="N3" s="38" t="s">
         <v>148</v>
@@ -4382,10 +4449,10 @@
         <v>219</v>
       </c>
       <c r="J4" s="19"/>
-      <c r="K4" s="154" t="s">
+      <c r="K4" s="159" t="s">
         <v>140</v>
       </c>
-      <c r="L4" s="155"/>
+      <c r="L4" s="160"/>
       <c r="M4" s="5"/>
       <c r="N4" s="62" t="s">
         <v>135</v>
@@ -4428,10 +4495,10 @@
         <v>4</v>
       </c>
       <c r="J5" s="20"/>
-      <c r="K5" s="154" t="s">
+      <c r="K5" s="159" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="155"/>
+      <c r="L5" s="160"/>
       <c r="M5" s="5"/>
       <c r="N5" s="62" t="s">
         <v>136</v>
@@ -4474,10 +4541,10 @@
         <v>3</v>
       </c>
       <c r="J6" s="20"/>
-      <c r="K6" s="154" t="s">
+      <c r="K6" s="159" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="155"/>
+      <c r="L6" s="160"/>
       <c r="M6" s="5"/>
       <c r="N6" s="62" t="s">
         <v>137</v>
@@ -4520,10 +4587,10 @@
         <v>6</v>
       </c>
       <c r="J7" s="20"/>
-      <c r="K7" s="154" t="s">
+      <c r="K7" s="159" t="s">
         <v>143</v>
       </c>
-      <c r="L7" s="155"/>
+      <c r="L7" s="160"/>
       <c r="M7" s="5"/>
       <c r="N7" s="62" t="s">
         <v>138</v>
@@ -4568,10 +4635,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="20"/>
-      <c r="K8" s="154" t="s">
+      <c r="K8" s="159" t="s">
         <v>144</v>
       </c>
-      <c r="L8" s="155"/>
+      <c r="L8" s="160"/>
       <c r="M8" s="5"/>
       <c r="N8" s="62" t="s">
         <v>139</v>
@@ -4614,10 +4681,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="J9" s="20"/>
-      <c r="K9" s="154" t="s">
+      <c r="K9" s="159" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="155"/>
+      <c r="L9" s="160"/>
       <c r="M9" s="5"/>
       <c r="N9" s="62" t="s">
         <v>219</v>
@@ -4725,15 +4792,15 @@
     <row r="12" spans="1:31">
       <c r="A12" s="50"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="159"/>
-      <c r="D12" s="159"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="159"/>
-      <c r="H12" s="159"/>
-      <c r="I12" s="159"/>
-      <c r="J12" s="159"/>
-      <c r="K12" s="159"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="164"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="164"/>
+      <c r="G12" s="164"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="164"/>
+      <c r="K12" s="164"/>
       <c r="L12" s="5"/>
       <c r="M12" s="22"/>
       <c r="S12" s="50"/>
@@ -4741,37 +4808,37 @@
     <row r="13" spans="1:31" ht="14.55" customHeight="1">
       <c r="A13" s="50"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="160" t="s">
+      <c r="C13" s="165" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="161"/>
-      <c r="E13" s="161"/>
-      <c r="F13" s="161"/>
-      <c r="G13" s="161"/>
-      <c r="H13" s="161"/>
-      <c r="I13" s="161"/>
-      <c r="J13" s="161"/>
-      <c r="K13" s="161"/>
-      <c r="L13" s="162"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="166"/>
+      <c r="K13" s="166"/>
+      <c r="L13" s="167"/>
       <c r="M13" s="22"/>
       <c r="S13" s="50"/>
     </row>
     <row r="14" spans="1:31" ht="15.6">
       <c r="A14" s="50"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="151" t="s">
+      <c r="C14" s="156" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="153"/>
-      <c r="J14" s="151" t="s">
+      <c r="D14" s="157"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="157"/>
+      <c r="H14" s="157"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="156" t="s">
         <v>149</v>
       </c>
-      <c r="K14" s="153"/>
+      <c r="K14" s="158"/>
       <c r="L14" s="35" t="s">
         <v>217</v>
       </c>
@@ -5252,10 +5319,10 @@
         <v>272</v>
       </c>
       <c r="K1" s="50"/>
-      <c r="L1" s="146" t="s">
+      <c r="L1" s="142" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="135" t="s">
+      <c r="M1" s="134" t="s">
         <v>588</v>
       </c>
       <c r="N1" s="94" t="s">
@@ -5264,10 +5331,10 @@
     </row>
     <row r="2" spans="1:21" ht="97.5" customHeight="1" thickBot="1">
       <c r="A2" s="50"/>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="168" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="168" t="s">
+      <c r="C2" s="173" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -5288,22 +5355,22 @@
       <c r="I2" s="68" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="133" t="s">
+      <c r="J2" s="132" t="s">
         <v>275</v>
       </c>
       <c r="K2" s="50"/>
-      <c r="L2" s="147">
+      <c r="L2" s="143">
         <f>N2/R2</f>
-        <v>0.82352941176470584</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="M2" s="94" t="s">
         <v>275</v>
       </c>
       <c r="N2" s="102">
         <f>COUNTIF(J2:J24,"Yes")</f>
-        <v>14</v>
-      </c>
-      <c r="O2" s="148" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="144" t="s">
         <v>279</v>
       </c>
       <c r="P2" s="100">
@@ -5317,19 +5384,19 @@
         <f>P2-N4</f>
         <v>17</v>
       </c>
-      <c r="T2" s="134" t="str">
+      <c r="T2" s="133" t="str">
         <f>IF(J2="No",ROW(),"")</f>
         <v/>
       </c>
-      <c r="U2" s="134" t="str">
+      <c r="U2" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U2))-ROW($I$2)+1),"")</f>
         <v>Is a formal incident logging register or ticketing system implemented to ensure proper tracking, documentation, and traceability of incidents?</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="81" customHeight="1">
       <c r="A3" s="50"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="168"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="173"/>
       <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
@@ -5358,22 +5425,22 @@
       </c>
       <c r="N3" s="103">
         <f>COUNTIF(J2:J24,"No")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3" s="57"/>
       <c r="P3" s="57"/>
-      <c r="T3" s="134">
+      <c r="T3" s="133">
         <f t="shared" ref="T3:T24" si="0">IF(J3="No",ROW(),"")</f>
         <v>3</v>
       </c>
-      <c r="U3" s="134" t="str">
+      <c r="U3" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U3))-ROW($I$2)+1),"")</f>
-        <v xml:space="preserve">Les données reçues via les réseaux, supports de stockage ou pièces jointes des emails, sont-elles systématiquement analysées avant utilisation ? </v>
+        <v>Comment l’entreprise s’assure-t-elle que les bâtiments hébergeant des systèmes d’information sont physiquement sécurisés, que l’accès physique est contrôlé et limité aux personnes autorisées, et que des systèmes d’alarme et de surveillance sont installés et opérationnels ?</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="79.95" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="164"/>
+      <c r="B4" s="169"/>
       <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
@@ -5400,25 +5467,25 @@
       </c>
       <c r="K4" s="50"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="145" t="s">
+      <c r="M4" s="141" t="s">
         <v>274</v>
       </c>
       <c r="N4" s="104">
         <f>COUNTIF(J2:J24,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="T4" s="134" t="str">
+      <c r="T4" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U4" s="134" t="str">
+      <c r="U4" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U4))-ROW($I$2)+1),"")</f>
-        <v>Les configurations réseau sont-elles sauvegardées et versionnées pour assurer leur intégrité et leur restauration ?</v>
+        <v xml:space="preserve">Les données reçues via les réseaux, supports de stockage ou pièces jointes des emails, sont-elles systématiquement analysées avant utilisation ? </v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="87" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="164"/>
+      <c r="B5" s="169"/>
       <c r="C5" s="3" t="s">
         <v>283</v>
       </c>
@@ -5440,30 +5507,30 @@
       <c r="I5" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>275</v>
+      <c r="J5" s="148" t="s">
+        <v>273</v>
       </c>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="149" t="s">
+      <c r="M5" s="145" t="s">
         <v>611</v>
       </c>
-      <c r="N5" s="121" t="s">
+      <c r="N5" s="120" t="s">
         <v>612</v>
       </c>
-      <c r="T5" s="134" t="str">
+      <c r="T5" s="133">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="U5" s="134" t="str">
+        <v>5</v>
+      </c>
+      <c r="U5" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U5))-ROW($I$2)+1),"")</f>
-        <v/>
+        <v>Les configurations réseau sont-elles sauvegardées et versionnées pour assurer leur intégrité et leur restauration ?</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="91.05" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="169" t="s">
+      <c r="B6" s="169"/>
+      <c r="C6" s="174" t="s">
         <v>293</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -5489,78 +5556,78 @@
       </c>
       <c r="K6" s="50"/>
       <c r="L6" s="50"/>
-      <c r="T6" s="134" t="str">
+      <c r="T6" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U6" s="134" t="str">
+      <c r="U6" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U6))-ROW($I$2)+1),"")</f>
-        <v/>
+        <v>Des contrôles d’accès réseau (firewalls, ACL) sont-ils configurés ?</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="43.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="164"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="163" t="s">
+      <c r="B7" s="169"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="168" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="166" t="s">
+      <c r="E7" s="171" t="s">
         <v>456</v>
       </c>
-      <c r="F7" s="166" t="s">
+      <c r="F7" s="171" t="s">
         <v>457</v>
       </c>
-      <c r="G7" s="166" t="s">
+      <c r="G7" s="171" t="s">
         <v>458</v>
       </c>
-      <c r="H7" s="166" t="s">
+      <c r="H7" s="171" t="s">
         <v>302</v>
       </c>
       <c r="I7" s="80" t="s">
         <v>555</v>
       </c>
-      <c r="J7" s="163" t="s">
+      <c r="J7" s="168" t="s">
         <v>273</v>
       </c>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
-      <c r="T7" s="134">
+      <c r="T7" s="133">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="U7" s="134" t="str">
+      <c r="U7" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U7))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:21" ht="43.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="164"/>
-      <c r="C8" s="170"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
+      <c r="B8" s="169"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="169"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="172"/>
+      <c r="G8" s="172"/>
+      <c r="H8" s="172"/>
       <c r="I8" s="81"/>
-      <c r="J8" s="165"/>
+      <c r="J8" s="170"/>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
-      <c r="T8" s="134" t="str">
+      <c r="T8" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U8" s="134" t="str">
+      <c r="U8" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U8))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:21" ht="49.95" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="164"/>
-      <c r="C9" s="170"/>
-      <c r="D9" s="165"/>
+      <c r="B9" s="169"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="170"/>
       <c r="E9" s="24" t="s">
         <v>459</v>
       </c>
@@ -5581,20 +5648,20 @@
       </c>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
-      <c r="T9" s="134" t="str">
+      <c r="T9" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U9" s="134" t="str">
+      <c r="U9" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U9))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:21" ht="43.5" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="170"/>
-      <c r="D10" s="163" t="s">
+      <c r="B10" s="169"/>
+      <c r="C10" s="175"/>
+      <c r="D10" s="168" t="s">
         <v>288</v>
       </c>
       <c r="E10" s="24" t="s">
@@ -5617,76 +5684,76 @@
       </c>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
-      <c r="T10" s="134" t="str">
+      <c r="T10" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U10" s="134" t="str">
+      <c r="U10" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U10))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:21" ht="43.5" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="166" t="s">
+      <c r="B11" s="169"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="171" t="s">
         <v>465</v>
       </c>
-      <c r="F11" s="166" t="s">
+      <c r="F11" s="171" t="s">
         <v>466</v>
       </c>
-      <c r="G11" s="166" t="s">
+      <c r="G11" s="171" t="s">
         <v>467</v>
       </c>
-      <c r="H11" s="166" t="s">
+      <c r="H11" s="171" t="s">
         <v>295</v>
       </c>
       <c r="I11" s="80" t="s">
         <v>558</v>
       </c>
-      <c r="J11" s="163" t="s">
+      <c r="J11" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K11" s="50"/>
       <c r="L11" s="50"/>
-      <c r="T11" s="134" t="str">
+      <c r="T11" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U11" s="134" t="str">
+      <c r="U11" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U11))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:21" ht="43.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="164"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="167"/>
+      <c r="B12" s="169"/>
+      <c r="C12" s="175"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="172"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="172"/>
+      <c r="H12" s="172"/>
       <c r="I12" s="81"/>
-      <c r="J12" s="165"/>
+      <c r="J12" s="170"/>
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
-      <c r="T12" s="134" t="str">
+      <c r="T12" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U12" s="134" t="str">
+      <c r="U12" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U12))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:21" ht="43.2">
       <c r="A13" s="50"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="163" t="s">
+      <c r="B13" s="169"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="168" t="s">
         <v>289</v>
       </c>
       <c r="E13" s="42" t="s">
@@ -5709,20 +5776,20 @@
       </c>
       <c r="K13" s="50"/>
       <c r="L13" s="50"/>
-      <c r="T13" s="134" t="str">
+      <c r="T13" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U13" s="134" t="str">
+      <c r="U13" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U13))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:21" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="164"/>
-      <c r="C14" s="170"/>
-      <c r="D14" s="164"/>
+      <c r="B14" s="169"/>
+      <c r="C14" s="175"/>
+      <c r="D14" s="169"/>
       <c r="E14" s="42" t="s">
         <v>469</v>
       </c>
@@ -5743,20 +5810,20 @@
       </c>
       <c r="K14" s="50"/>
       <c r="L14" s="50"/>
-      <c r="T14" s="134" t="str">
+      <c r="T14" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U14" s="134" t="str">
+      <c r="U14" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U14))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:21" ht="51" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="165"/>
+      <c r="B15" s="169"/>
+      <c r="C15" s="175"/>
+      <c r="D15" s="170"/>
       <c r="E15" s="42" t="s">
         <v>470</v>
       </c>
@@ -5777,100 +5844,100 @@
       </c>
       <c r="K15" s="50"/>
       <c r="L15" s="50"/>
-      <c r="T15" s="134" t="str">
+      <c r="T15" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U15" s="134" t="str">
+      <c r="U15" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U15))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:21" ht="47.55" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="163" t="s">
+      <c r="B16" s="169"/>
+      <c r="C16" s="175"/>
+      <c r="D16" s="168" t="s">
         <v>290</v>
       </c>
-      <c r="E16" s="166" t="s">
+      <c r="E16" s="171" t="s">
         <v>477</v>
       </c>
-      <c r="F16" s="166" t="s">
+      <c r="F16" s="171" t="s">
         <v>478</v>
       </c>
-      <c r="G16" s="166" t="s">
+      <c r="G16" s="171" t="s">
         <v>479</v>
       </c>
-      <c r="H16" s="166" t="s">
+      <c r="H16" s="171" t="s">
         <v>301</v>
       </c>
       <c r="I16" s="80" t="s">
         <v>562</v>
       </c>
-      <c r="J16" s="163" t="s">
+      <c r="J16" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K16" s="50"/>
       <c r="L16" s="50"/>
-      <c r="T16" s="134" t="str">
+      <c r="T16" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U16" s="134" t="str">
+      <c r="U16" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U16))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:21" ht="22.05" hidden="1" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="164"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="173"/>
+      <c r="B17" s="169"/>
+      <c r="C17" s="175"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="178"/>
+      <c r="H17" s="178"/>
       <c r="I17" s="82"/>
-      <c r="J17" s="164"/>
+      <c r="J17" s="169"/>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
-      <c r="T17" s="134" t="str">
+      <c r="T17" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U17" s="134" t="str">
+      <c r="U17" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U17))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="50"/>
-      <c r="B18" s="164"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="165"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="167"/>
-      <c r="H18" s="167"/>
+      <c r="B18" s="169"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="170"/>
+      <c r="E18" s="172"/>
+      <c r="F18" s="172"/>
+      <c r="G18" s="172"/>
+      <c r="H18" s="172"/>
       <c r="I18" s="81"/>
-      <c r="J18" s="165"/>
+      <c r="J18" s="170"/>
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
-      <c r="T18" s="134" t="str">
+      <c r="T18" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U18" s="134" t="str">
+      <c r="U18" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U18))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:21" ht="61.95" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="163" t="s">
+      <c r="B19" s="169"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="168" t="s">
         <v>291</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -5888,81 +5955,81 @@
       <c r="I19" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="J19" s="133" t="s">
+      <c r="J19" s="132" t="s">
         <v>273</v>
       </c>
       <c r="K19" s="50"/>
       <c r="L19" s="50"/>
-      <c r="T19" s="134">
+      <c r="T19" s="133">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U19" s="134" t="str">
+      <c r="U19" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U19))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="50"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="170"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="166" t="s">
+      <c r="B20" s="169"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="169"/>
+      <c r="E20" s="171" t="s">
         <v>481</v>
       </c>
-      <c r="F20" s="166" t="s">
+      <c r="F20" s="171" t="s">
         <v>485</v>
       </c>
-      <c r="G20" s="174" t="s">
+      <c r="G20" s="179" t="s">
         <v>489</v>
       </c>
-      <c r="H20" s="166" t="s">
+      <c r="H20" s="171" t="s">
         <v>300</v>
       </c>
       <c r="I20" s="80"/>
-      <c r="J20" s="163" t="s">
+      <c r="J20" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K20" s="50"/>
       <c r="L20" s="50"/>
-      <c r="T20" s="134" t="str">
+      <c r="T20" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U20" s="134" t="str">
+      <c r="U20" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U20))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:21" ht="28.95" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="170"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="167"/>
-      <c r="F21" s="167"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="167"/>
+      <c r="B21" s="169"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="180"/>
+      <c r="H21" s="172"/>
       <c r="I21" s="81" t="s">
         <v>564</v>
       </c>
-      <c r="J21" s="165"/>
+      <c r="J21" s="170"/>
       <c r="K21" s="50"/>
       <c r="L21" s="50"/>
-      <c r="T21" s="134" t="str">
+      <c r="T21" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U21" s="134" t="str">
+      <c r="U21" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U21))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:21" ht="39.450000000000003" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="164"/>
-      <c r="C22" s="170"/>
-      <c r="D22" s="164"/>
+      <c r="B22" s="169"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="169"/>
       <c r="E22" s="24" t="s">
         <v>482</v>
       </c>
@@ -5978,74 +6045,74 @@
       <c r="I22" s="65" t="s">
         <v>565</v>
       </c>
-      <c r="J22" s="61" t="s">
-        <v>275</v>
+      <c r="J22" s="147" t="s">
+        <v>273</v>
       </c>
       <c r="K22" s="50"/>
       <c r="L22" s="50"/>
-      <c r="T22" s="134" t="str">
+      <c r="T22" s="133">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="U22" s="134" t="str">
+        <v>22</v>
+      </c>
+      <c r="U22" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U22))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:21" ht="42" customHeight="1">
       <c r="A23" s="50"/>
-      <c r="B23" s="164"/>
-      <c r="C23" s="170"/>
-      <c r="D23" s="168" t="s">
+      <c r="B23" s="169"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="173" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="166" t="s">
+      <c r="E23" s="171" t="s">
         <v>483</v>
       </c>
-      <c r="F23" s="172" t="s">
+      <c r="F23" s="177" t="s">
         <v>487</v>
       </c>
-      <c r="G23" s="166" t="s">
+      <c r="G23" s="171" t="s">
         <v>491</v>
       </c>
-      <c r="H23" s="166" t="s">
+      <c r="H23" s="171" t="s">
         <v>299</v>
       </c>
       <c r="I23" s="80" t="s">
         <v>566</v>
       </c>
-      <c r="J23" s="163" t="s">
+      <c r="J23" s="168" t="s">
         <v>275</v>
       </c>
       <c r="K23" s="50"/>
       <c r="L23" s="50"/>
-      <c r="T23" s="134" t="str">
+      <c r="T23" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U23" s="134" t="str">
+      <c r="U23" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U23))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:21" ht="28.95" customHeight="1">
       <c r="A24" s="50"/>
-      <c r="B24" s="165"/>
-      <c r="C24" s="171"/>
-      <c r="D24" s="168"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="167"/>
-      <c r="H24" s="167"/>
+      <c r="B24" s="170"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="177"/>
+      <c r="G24" s="172"/>
+      <c r="H24" s="172"/>
       <c r="I24" s="81"/>
-      <c r="J24" s="165"/>
+      <c r="J24" s="170"/>
       <c r="K24" s="50"/>
       <c r="L24" s="50"/>
-      <c r="T24" s="134" t="str">
+      <c r="T24" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="U24" s="134" t="str">
+      <c r="U24" s="133" t="str">
         <f>IFERROR(INDEX($H$2:$H$100,SMALL($T$2:$T$100,ROWS($U$2:U24))-ROW($I$2)+1),"")</f>
         <v/>
       </c>
@@ -6120,29 +6187,29 @@
     <mergeCell ref="E11:E12"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:E1">
-    <cfRule type="expression" dxfId="50" priority="9">
+    <cfRule type="expression" dxfId="54" priority="9">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J1">
-    <cfRule type="expression" dxfId="49" priority="5">
+    <cfRule type="expression" dxfId="53" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="6">
+    <cfRule type="expression" dxfId="52" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J7 J9:J11 J13:J16 J19:J20 J22:J23">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6207,21 +6274,21 @@
       <c r="S1" s="59"/>
     </row>
     <row r="2" spans="1:23" ht="21.45" customHeight="1" thickBot="1">
-      <c r="A2" s="182"/>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
+      <c r="A2" s="187"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
       <c r="I2" s="53"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
-      <c r="L2" s="186" t="s">
+      <c r="J2" s="187"/>
+      <c r="K2" s="187"/>
+      <c r="L2" s="191" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="187"/>
+      <c r="M2" s="192"/>
       <c r="N2" s="58" t="s">
         <v>275</v>
       </c>
@@ -6240,7 +6307,7 @@
       <c r="S2" s="59"/>
     </row>
     <row r="3" spans="1:23" ht="28.05" customHeight="1">
-      <c r="A3" s="182"/>
+      <c r="A3" s="187"/>
       <c r="B3" s="43" t="s">
         <v>148</v>
       </c>
@@ -6265,30 +6332,30 @@
       <c r="I3" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="176">
+      <c r="J3" s="187"/>
+      <c r="K3" s="187"/>
+      <c r="L3" s="181">
         <f>COUNTA(I4:I13)</f>
         <v>4</v>
       </c>
-      <c r="M3" s="188"/>
-      <c r="N3" s="191">
+      <c r="M3" s="193"/>
+      <c r="N3" s="196">
         <f>COUNTIF(I4:I12,"Yes")</f>
         <v>1</v>
       </c>
-      <c r="O3" s="194">
+      <c r="O3" s="199">
         <f>COUNTIF(I4:I12,"No")</f>
         <v>3</v>
       </c>
-      <c r="P3" s="197">
+      <c r="P3" s="202">
         <f>COUNTIF(I4:I12,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="176">
+      <c r="Q3" s="181">
         <f>L3-P3</f>
         <v>4</v>
       </c>
-      <c r="R3" s="179">
+      <c r="R3" s="184">
         <f>N3/Q3</f>
         <v>0.25</v>
       </c>
@@ -6296,95 +6363,101 @@
       <c r="U3" s="7"/>
       <c r="V3" s="55"/>
     </row>
-    <row r="4" spans="1:23" ht="93.6" customHeight="1">
-      <c r="A4" s="182"/>
-      <c r="B4" s="163" t="s">
+    <row r="4" spans="1:23" ht="133.19999999999999" customHeight="1">
+      <c r="A4" s="187"/>
+      <c r="B4" s="168" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="163" t="s">
+      <c r="C4" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="172" t="s">
+      <c r="D4" s="177" t="s">
         <v>228</v>
       </c>
-      <c r="E4" s="172" t="s">
+      <c r="E4" s="177" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="166" t="s">
+      <c r="F4" s="171" t="s">
         <v>249</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="185" t="s">
+      <c r="H4" s="190" t="s">
         <v>262</v>
       </c>
-      <c r="I4" s="168" t="s">
+      <c r="I4" s="173" t="s">
         <v>273</v>
       </c>
-      <c r="J4" s="182"/>
-      <c r="K4" s="182"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="189"/>
-      <c r="N4" s="192"/>
-      <c r="O4" s="195"/>
-      <c r="P4" s="198"/>
-      <c r="Q4" s="177"/>
-      <c r="R4" s="180"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="187"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="194"/>
+      <c r="N4" s="197"/>
+      <c r="O4" s="200"/>
+      <c r="P4" s="203"/>
+      <c r="Q4" s="182"/>
+      <c r="R4" s="185"/>
       <c r="S4" s="59"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="150"/>
-      <c r="W4" s="143"/>
-    </row>
-    <row r="5" spans="1:23" ht="78" customHeight="1" thickBot="1">
-      <c r="A5" s="182"/>
-      <c r="B5" s="164"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="172"/>
-      <c r="F5" s="173"/>
+      <c r="U4" s="7">
+        <f t="shared" ref="U4:U11" si="0">IF(I4="No",ROW(), "")</f>
+        <v>4</v>
+      </c>
+      <c r="V4" s="146" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$4:$U$100,ROWS($V$4:V4))-ROW($H$4)+1),"")</f>
+        <v>Pouvez-vous fournir les rapports d’audit réalisés au cours des 12 derniers mois, ainsi que les preuves de leur dépôt auprès de l’ANSI ?</v>
+      </c>
+      <c r="W4" s="139"/>
+    </row>
+    <row r="5" spans="1:23" ht="102.6" customHeight="1" thickBot="1">
+      <c r="A5" s="187"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="178"/>
       <c r="G5" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="185"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="193"/>
-      <c r="O5" s="196"/>
-      <c r="P5" s="199"/>
-      <c r="Q5" s="178"/>
-      <c r="R5" s="181"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="187"/>
+      <c r="K5" s="187"/>
+      <c r="L5" s="183"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="198"/>
+      <c r="O5" s="201"/>
+      <c r="P5" s="204"/>
+      <c r="Q5" s="183"/>
+      <c r="R5" s="186"/>
       <c r="S5" s="59"/>
       <c r="U5" s="7" t="str">
-        <f t="shared" ref="U5:U11" si="0">IF(I5="No",ROW(), "")</f>
-        <v/>
-      </c>
-      <c r="V5" s="150" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V5" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V5))-ROW($H$4)+1),"")</f>
-        <v>L’organisation possède-t-elle un niveau de sécurité délivré par l’ANSI ? Si oui, quel est ce niveau ?</v>
-      </c>
-      <c r="W5" s="143" t="str">
+        <v>Est-ce que vos équipements électroniques et logiciels, ainsi que vos fournisseurs de services cloud, possèdent respectivement les labels « Sécurisé » et « G-Cloud / N-Cloud » valides délivrés par l’ANSI ?</v>
+      </c>
+      <c r="W5" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W5))),"")</f>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:23" ht="72.599999999999994" thickBot="1">
-      <c r="A6" s="182"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="167"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="172"/>
       <c r="G6" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="H6" s="185"/>
-      <c r="I6" s="168"/>
-      <c r="J6" s="182"/>
-      <c r="K6" s="182"/>
+      <c r="H6" s="190"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="187"/>
+      <c r="K6" s="187"/>
       <c r="L6" s="59"/>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -6397,19 +6470,19 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="V6" s="150" t="str">
+      <c r="V6" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V6))-ROW($H$4)+1),"")</f>
-        <v/>
-      </c>
-      <c r="W6" s="143" t="str">
+        <v>L’organisme dispose-t-il d’un centre de réponse aux urgences (propre ou adhérent) et prend-il les mesures de sécurité requises pour la gestion des infrastructures numériques d’importance vitale ?</v>
+      </c>
+      <c r="W6" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W6))),"")</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:23" ht="109.05" customHeight="1" thickBot="1">
-      <c r="A7" s="182"/>
-      <c r="B7" s="164"/>
-      <c r="C7" s="164"/>
+      <c r="A7" s="187"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
       <c r="D7" s="24" t="s">
         <v>234</v>
       </c>
@@ -6422,18 +6495,18 @@
       <c r="G7" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="185" t="s">
+      <c r="H7" s="190" t="s">
         <v>263</v>
       </c>
-      <c r="I7" s="168" t="s">
+      <c r="I7" s="173" t="s">
         <v>273</v>
       </c>
-      <c r="J7" s="182"/>
-      <c r="K7" s="182"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
       <c r="L7" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="M7" s="121" t="s">
+      <c r="M7" s="120" t="s">
         <v>612</v>
       </c>
       <c r="N7" s="109"/>
@@ -6441,19 +6514,19 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="V7" s="150" t="str">
+      <c r="V7" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V7))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
-      <c r="W7" s="143" t="str">
+      <c r="W7" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W7))),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:23" ht="102" customHeight="1">
-      <c r="A8" s="182"/>
-      <c r="B8" s="164"/>
-      <c r="C8" s="164"/>
+      <c r="A8" s="187"/>
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
       <c r="D8" s="24" t="s">
         <v>235</v>
       </c>
@@ -6466,29 +6539,29 @@
       <c r="G8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="H8" s="185"/>
-      <c r="I8" s="168"/>
-      <c r="J8" s="182"/>
-      <c r="K8" s="182"/>
+      <c r="H8" s="190"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="187"/>
+      <c r="K8" s="187"/>
       <c r="N8" s="110"/>
-      <c r="Q8" s="142"/>
+      <c r="Q8" s="138"/>
       <c r="U8" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="V8" s="150" t="str">
+      <c r="V8" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V8))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
-      <c r="W8" s="143" t="str">
+      <c r="W8" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W8))),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:23" ht="252" customHeight="1">
-      <c r="A9" s="182"/>
-      <c r="B9" s="164"/>
-      <c r="C9" s="164"/>
+      <c r="A9" s="187"/>
+      <c r="B9" s="169"/>
+      <c r="C9" s="169"/>
       <c r="D9" s="24" t="s">
         <v>244</v>
       </c>
@@ -6501,31 +6574,31 @@
       <c r="G9" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H9" s="185" t="s">
+      <c r="H9" s="190" t="s">
         <v>265</v>
       </c>
-      <c r="I9" s="168" t="s">
-        <v>275</v>
-      </c>
-      <c r="J9" s="182"/>
-      <c r="K9" s="182"/>
-      <c r="U9" s="7" t="str">
+      <c r="I9" s="173" t="s">
+        <v>273</v>
+      </c>
+      <c r="J9" s="187"/>
+      <c r="K9" s="187"/>
+      <c r="U9" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="V9" s="150" t="str">
+        <v>9</v>
+      </c>
+      <c r="V9" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V9))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
-      <c r="W9" s="143" t="str">
+      <c r="W9" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W9))),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:23" ht="139.05000000000001" customHeight="1">
-      <c r="A10" s="182"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="164"/>
+      <c r="A10" s="187"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
       <c r="D10" s="24" t="s">
         <v>248</v>
       </c>
@@ -6538,27 +6611,27 @@
       <c r="G10" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="185"/>
-      <c r="I10" s="168"/>
-      <c r="J10" s="182"/>
-      <c r="K10" s="182"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="173"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
       <c r="U10" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="V10" s="150" t="str">
+      <c r="V10" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V10))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
-      <c r="W10" s="143" t="str">
+      <c r="W10" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W10))),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:23" ht="64.95" customHeight="1">
-      <c r="A11" s="182"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
+      <c r="A11" s="187"/>
+      <c r="B11" s="170"/>
+      <c r="C11" s="170"/>
       <c r="D11" s="24" t="s">
         <v>239</v>
       </c>
@@ -6574,54 +6647,54 @@
       <c r="H11" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="I11" s="132" t="s">
-        <v>273</v>
-      </c>
-      <c r="J11" s="182"/>
-      <c r="K11" s="182"/>
-      <c r="U11" s="7">
+      <c r="I11" s="148" t="s">
+        <v>275</v>
+      </c>
+      <c r="J11" s="187"/>
+      <c r="K11" s="187"/>
+      <c r="U11" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="V11" s="150" t="str">
+        <v/>
+      </c>
+      <c r="V11" s="146" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($U$2:$U$100,ROWS($V$4:V11))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
-      <c r="W11" s="143" t="str">
+      <c r="W11" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W11))),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:23" ht="21">
-      <c r="A12" s="182"/>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
+      <c r="A12" s="187"/>
+      <c r="B12" s="189"/>
+      <c r="C12" s="189"/>
+      <c r="D12" s="189"/>
+      <c r="E12" s="189"/>
+      <c r="F12" s="189"/>
+      <c r="G12" s="189"/>
+      <c r="H12" s="189"/>
       <c r="I12" s="53"/>
-      <c r="J12" s="182"/>
-      <c r="K12" s="182"/>
-      <c r="V12" s="143"/>
-      <c r="W12" s="143" t="str">
+      <c r="J12" s="187"/>
+      <c r="K12" s="187"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="139" t="str">
         <f>IFERROR(INDEX($V$4:$V$11,SMALL(IF($V$4:$V$11&lt;&gt;"",ROW($V$4:$V$11)-ROW($V$4)+1),ROWS($W$4:W12))),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="182"/>
-      <c r="B13" s="182"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="182"/>
-      <c r="F13" s="182"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="182"/>
+      <c r="A13" s="187"/>
+      <c r="B13" s="187"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="187"/>
+      <c r="F13" s="187"/>
+      <c r="G13" s="187"/>
+      <c r="H13" s="187"/>
       <c r="I13" s="53"/>
-      <c r="J13" s="182"/>
-      <c r="K13" s="182"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -6649,32 +6722,32 @@
     <mergeCell ref="I7:I8"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:I3">
-    <cfRule type="expression" dxfId="43" priority="7">
+    <cfRule type="expression" dxfId="47" priority="7">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="8">
+    <cfRule type="expression" dxfId="46" priority="8">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I7 I9 I11">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="6" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V3">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="2">
+    <cfRule type="expression" dxfId="40" priority="2">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6750,19 +6823,19 @@
       <c r="L1" s="94" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="201" t="s">
+      <c r="M1" s="206" t="s">
         <v>588</v>
       </c>
-      <c r="N1" s="202"/>
+      <c r="N1" s="207"/>
       <c r="O1" s="93" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="128.4" thickBot="1">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="173" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="177" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="24" t="s">
@@ -6781,14 +6854,14 @@
         <v>520</v>
       </c>
       <c r="H2" s="24"/>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="152" t="s">
         <v>273</v>
       </c>
       <c r="J2" s="50"/>
       <c r="K2" s="89"/>
       <c r="L2" s="96">
         <f>O2/S2</f>
-        <v>0.74285714285714288</v>
+        <v>0.54285714285714282</v>
       </c>
       <c r="M2" s="94" t="s">
         <v>275</v>
@@ -6796,7 +6869,7 @@
       <c r="N2" s="95"/>
       <c r="O2" s="86">
         <f>COUNTIF(I2:I37,"Yes")</f>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="P2" s="93" t="s">
         <v>279</v>
@@ -6815,15 +6888,15 @@
       <c r="T2" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="U2" s="121" t="s">
+      <c r="U2" s="120" t="s">
         <v>613</v>
       </c>
       <c r="V2" s="89"/>
-      <c r="W2" s="129">
-        <f>IF(I4="No",ROW(), "")</f>
+      <c r="W2" s="128">
+        <f>IF(I2="No",ROW(), "")</f>
         <v>2</v>
       </c>
-      <c r="X2" s="129" t="str">
+      <c r="X2" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X2:X$2))-ROW($G$2)+1),"")</f>
         <v>Les liens entre la gestion de crise, la gestion des incidents, la continuité d’activité et la sécurité sont-ils formalisés ?</v>
       </c>
@@ -6837,8 +6910,8 @@
       <c r="AF2" s="89"/>
     </row>
     <row r="3" spans="1:32" ht="115.95" customHeight="1" thickBot="1">
-      <c r="A3" s="168"/>
-      <c r="B3" s="172"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="177"/>
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -6855,7 +6928,7 @@
         <v>519</v>
       </c>
       <c r="H3" s="24"/>
-      <c r="I3" s="132" t="s">
+      <c r="I3" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J3" s="50"/>
@@ -6867,18 +6940,18 @@
       <c r="N3" s="95"/>
       <c r="O3" s="87">
         <f>COUNTIF(I2:I37,"No")</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R3" s="89"/>
       <c r="S3" s="89"/>
       <c r="T3" s="89"/>
       <c r="U3" s="89"/>
       <c r="V3" s="89"/>
-      <c r="W3" s="129">
-        <f t="shared" ref="W3:W37" si="0">IF(I5="No",ROW(), "")</f>
+      <c r="W3" s="128">
+        <f t="shared" ref="W3:W36" si="0">IF(I3="No",ROW(), "")</f>
         <v>3</v>
       </c>
-      <c r="X3" s="129" t="str">
+      <c r="X3" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X3))-ROW($G$2)+1),"")</f>
         <v>Le cadre formel de gouvernance de la gestion de crise cyber est-il documenté, daté et approuvé par l’autorité compétente afin de garantir sa validité et son application ?</v>
       </c>
@@ -6889,8 +6962,8 @@
       <c r="AC3" s="89"/>
     </row>
     <row r="4" spans="1:32" ht="87" customHeight="1" thickBot="1">
-      <c r="A4" s="168"/>
-      <c r="B4" s="172"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="177"/>
       <c r="C4" s="24" t="s">
         <v>72</v>
       </c>
@@ -6907,7 +6980,7 @@
         <v>495</v>
       </c>
       <c r="H4" s="24"/>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J4" s="50"/>
@@ -6928,11 +7001,11 @@
       <c r="T4" s="89"/>
       <c r="U4" s="89"/>
       <c r="V4" s="89"/>
-      <c r="W4" s="129">
+      <c r="W4" s="128">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="X4" s="129" t="str">
+      <c r="X4" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X4))-ROW($G$2)+1),"")</f>
         <v xml:space="preserve">Exsite t-il des cas specifique ou de periode qui declanche la revision du cadre de gouvernance ? </v>
       </c>
@@ -6943,8 +7016,8 @@
       <c r="AC4" s="89"/>
     </row>
     <row r="5" spans="1:32" ht="126.45" customHeight="1">
-      <c r="A5" s="168"/>
-      <c r="B5" s="172"/>
+      <c r="A5" s="173"/>
+      <c r="B5" s="177"/>
       <c r="C5" s="68" t="s">
         <v>75</v>
       </c>
@@ -6961,7 +7034,7 @@
         <v>493</v>
       </c>
       <c r="H5" s="68"/>
-      <c r="I5" s="132" t="s">
+      <c r="I5" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J5" s="50"/>
@@ -6976,11 +7049,11 @@
       <c r="T5" s="89"/>
       <c r="U5" s="89"/>
       <c r="V5" s="89"/>
-      <c r="W5" s="129">
+      <c r="W5" s="128">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="X5" s="129" t="str">
+      <c r="X5" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X5))-ROW($G$2)+1),"")</f>
         <v>Existe-t-il une politique qui definie la modaliter et les ligne a suivre en terme de communication interne et externe dans le cas d'un crise cyber ?</v>
       </c>
@@ -6991,8 +7064,8 @@
       <c r="AC5" s="89"/>
     </row>
     <row r="6" spans="1:32" ht="86.4">
-      <c r="A6" s="168"/>
-      <c r="B6" s="172"/>
+      <c r="A6" s="173"/>
+      <c r="B6" s="177"/>
       <c r="C6" s="24" t="s">
         <v>78</v>
       </c>
@@ -7009,7 +7082,7 @@
         <v>492</v>
       </c>
       <c r="H6" s="24"/>
-      <c r="I6" s="132" t="s">
+      <c r="I6" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J6" s="50"/>
@@ -7022,11 +7095,11 @@
       <c r="T6" s="89"/>
       <c r="U6" s="89"/>
       <c r="V6" s="89"/>
-      <c r="W6" s="129">
+      <c r="W6" s="128">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="X6" s="129" t="str">
+      <c r="X6" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X6))-ROW($G$2)+1),"")</f>
         <v>Existe-t-il une repartition des  responsabilite pour chaque acteur et procedure operationelles ?</v>
       </c>
@@ -7037,8 +7110,8 @@
       <c r="AC6" s="89"/>
     </row>
     <row r="7" spans="1:32" ht="86.4">
-      <c r="A7" s="168"/>
-      <c r="B7" s="172"/>
+      <c r="A7" s="173"/>
+      <c r="B7" s="177"/>
       <c r="C7" s="24" t="s">
         <v>81</v>
       </c>
@@ -7055,7 +7128,7 @@
         <v>494</v>
       </c>
       <c r="H7" s="24"/>
-      <c r="I7" s="132" t="s">
+      <c r="I7" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J7" s="50"/>
@@ -7068,11 +7141,11 @@
       <c r="T7" s="89"/>
       <c r="U7" s="89"/>
       <c r="V7" s="89"/>
-      <c r="W7" s="129">
+      <c r="W7" s="128">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="X7" s="129" t="str">
+      <c r="X7" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X7))-ROW($G$2)+1),"")</f>
         <v>Qui a l'autorite de decision directionnelle en cas de crise cyber? Cette information est t-elle communiqué ?</v>
       </c>
@@ -7083,11 +7156,11 @@
       <c r="AC7" s="89"/>
     </row>
     <row r="8" spans="1:32" ht="96.6">
-      <c r="A8" s="168"/>
-      <c r="B8" s="168" t="s">
+      <c r="A8" s="173"/>
+      <c r="B8" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="168" t="s">
+      <c r="C8" s="173" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -7103,7 +7176,7 @@
         <v>496</v>
       </c>
       <c r="H8" s="24"/>
-      <c r="I8" s="132" t="s">
+      <c r="I8" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J8" s="50"/>
@@ -7116,13 +7189,13 @@
       <c r="T8" s="89"/>
       <c r="U8" s="89"/>
       <c r="V8" s="89"/>
-      <c r="W8" s="129" t="str">
+      <c r="W8" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X8" s="129" t="str">
+        <v>8</v>
+      </c>
+      <c r="X8" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X8))-ROW($G$2)+1),"")</f>
-        <v>Les événements ou critères déclenchant l’activation de la cellule de crise sont-ils clairement définis afin d’assurer une réponse rapide et cohérente ?</v>
+        <v>Exsite t-il un document formel de plan de contunite d'activite ?</v>
       </c>
       <c r="Y8" s="89"/>
       <c r="Z8" s="89"/>
@@ -7131,9 +7204,9 @@
       <c r="AC8" s="89"/>
     </row>
     <row r="9" spans="1:32" ht="69">
-      <c r="A9" s="168"/>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
+      <c r="A9" s="173"/>
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
       <c r="D9" s="31" t="s">
         <v>10</v>
       </c>
@@ -7147,7 +7220,7 @@
         <v>497</v>
       </c>
       <c r="H9" s="24"/>
-      <c r="I9" s="132" t="s">
+      <c r="I9" s="131" t="s">
         <v>273</v>
       </c>
       <c r="J9" s="50"/>
@@ -7160,13 +7233,13 @@
       <c r="T9" s="89"/>
       <c r="U9" s="89"/>
       <c r="V9" s="89"/>
-      <c r="W9" s="129" t="str">
+      <c r="W9" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X9" s="129" t="str">
+        <v>9</v>
+      </c>
+      <c r="X9" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X9))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Les versions des documents sont-elles contrôlées et régulièrement mises à jour ?</v>
       </c>
       <c r="Y9" s="89"/>
       <c r="Z9" s="89"/>
@@ -7175,9 +7248,9 @@
       <c r="AC9" s="89"/>
     </row>
     <row r="10" spans="1:32" ht="82.8">
-      <c r="A10" s="168"/>
-      <c r="B10" s="168"/>
-      <c r="C10" s="200"/>
+      <c r="A10" s="173"/>
+      <c r="B10" s="173"/>
+      <c r="C10" s="205"/>
       <c r="D10" s="31" t="s">
         <v>13</v>
       </c>
@@ -7191,8 +7264,8 @@
         <v>498</v>
       </c>
       <c r="H10" s="24"/>
-      <c r="I10" s="123" t="s">
-        <v>275</v>
+      <c r="I10" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J10" s="50"/>
       <c r="K10" s="89"/>
@@ -7204,13 +7277,13 @@
       <c r="T10" s="89"/>
       <c r="U10" s="89"/>
       <c r="V10" s="89"/>
-      <c r="W10" s="129" t="str">
+      <c r="W10" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X10" s="129" t="str">
+        <v>10</v>
+      </c>
+      <c r="X10" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X10))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Les procédures de sauvegarde et de restauration des données sont-elles formellement documentées</v>
       </c>
       <c r="Y10" s="89"/>
       <c r="Z10" s="89"/>
@@ -7219,9 +7292,9 @@
       <c r="AC10" s="89"/>
     </row>
     <row r="11" spans="1:32" ht="72">
-      <c r="A11" s="168"/>
-      <c r="B11" s="168"/>
-      <c r="C11" s="200"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="173"/>
+      <c r="C11" s="205"/>
       <c r="D11" s="31" t="s">
         <v>15</v>
       </c>
@@ -7235,8 +7308,8 @@
         <v>499</v>
       </c>
       <c r="H11" s="24"/>
-      <c r="I11" s="123" t="s">
-        <v>275</v>
+      <c r="I11" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J11" s="50"/>
       <c r="K11" s="89"/>
@@ -7248,13 +7321,13 @@
       <c r="T11" s="89"/>
       <c r="U11" s="89"/>
       <c r="V11" s="89"/>
-      <c r="W11" s="129" t="str">
+      <c r="W11" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X11" s="129" t="str">
+        <v>11</v>
+      </c>
+      <c r="X11" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X11))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Des stratégies de reprise sont-elles définies pour chaque processus critique</v>
       </c>
       <c r="Y11" s="89"/>
       <c r="Z11" s="89"/>
@@ -7263,8 +7336,8 @@
       <c r="AC11" s="89"/>
     </row>
     <row r="12" spans="1:32" ht="72">
-      <c r="A12" s="168"/>
-      <c r="B12" s="168"/>
+      <c r="A12" s="173"/>
+      <c r="B12" s="173"/>
       <c r="C12" s="3"/>
       <c r="D12" s="31" t="s">
         <v>20</v>
@@ -7279,8 +7352,8 @@
         <v>500</v>
       </c>
       <c r="H12" s="24"/>
-      <c r="I12" s="123" t="s">
-        <v>275</v>
+      <c r="I12" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J12" s="50"/>
       <c r="K12" s="89"/>
@@ -7292,13 +7365,13 @@
       <c r="T12" s="89"/>
       <c r="U12" s="89"/>
       <c r="V12" s="89"/>
-      <c r="W12" s="129" t="str">
+      <c r="W12" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X12" s="129" t="str">
+        <v>12</v>
+      </c>
+      <c r="X12" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X12))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Les résultats des tests sont-ils formellement documentés et analysés afin d’identifier les écarts et axes d’amélioration ?</v>
       </c>
       <c r="Y12" s="89"/>
       <c r="Z12" s="89"/>
@@ -7307,8 +7380,8 @@
       <c r="AC12" s="89"/>
     </row>
     <row r="13" spans="1:32" ht="69">
-      <c r="A13" s="168"/>
-      <c r="B13" s="168"/>
+      <c r="A13" s="173"/>
+      <c r="B13" s="173"/>
       <c r="C13" s="3"/>
       <c r="D13" s="31" t="s">
         <v>22</v>
@@ -7323,8 +7396,8 @@
         <v>501</v>
       </c>
       <c r="H13" s="24"/>
-      <c r="I13" s="123" t="s">
-        <v>275</v>
+      <c r="I13" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J13" s="50"/>
       <c r="K13" s="89"/>
@@ -7336,13 +7409,13 @@
       <c r="T13" s="89"/>
       <c r="U13" s="89"/>
       <c r="V13" s="89"/>
-      <c r="W13" s="129" t="str">
+      <c r="W13" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X13" s="129" t="str">
+        <v>13</v>
+      </c>
+      <c r="X13" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X13))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Les employés sont-ils sensibilisés au PCA et à leurs rôles</v>
       </c>
       <c r="Y13" s="89"/>
       <c r="Z13" s="89"/>
@@ -7351,8 +7424,8 @@
       <c r="AC13" s="89"/>
     </row>
     <row r="14" spans="1:32" ht="86.4">
-      <c r="A14" s="168"/>
-      <c r="B14" s="168"/>
+      <c r="A14" s="173"/>
+      <c r="B14" s="173"/>
       <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
@@ -7369,8 +7442,8 @@
         <v>502</v>
       </c>
       <c r="H14" s="24"/>
-      <c r="I14" s="123" t="s">
-        <v>275</v>
+      <c r="I14" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J14" s="50"/>
       <c r="K14" s="89"/>
@@ -7382,13 +7455,13 @@
       <c r="T14" s="89"/>
       <c r="U14" s="89"/>
       <c r="V14" s="89"/>
-      <c r="W14" s="129" t="str">
+      <c r="W14" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X14" s="129" t="str">
+        <v>14</v>
+      </c>
+      <c r="X14" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X14))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Les choix de stratégies de continuité sont-ils formellement justifiés (coût, efficacité, risques) afin de garantir des décisions adaptées et optimisées ?</v>
       </c>
       <c r="Y14" s="89"/>
       <c r="Z14" s="89"/>
@@ -7397,9 +7470,9 @@
       <c r="AC14" s="89"/>
     </row>
     <row r="15" spans="1:32" ht="82.8">
-      <c r="A15" s="168"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="200" t="s">
+      <c r="A15" s="173"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="205" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="31" t="s">
@@ -7415,8 +7488,8 @@
         <v>503</v>
       </c>
       <c r="H15" s="24"/>
-      <c r="I15" s="123" t="s">
-        <v>275</v>
+      <c r="I15" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J15" s="50"/>
       <c r="K15" s="89"/>
@@ -7428,13 +7501,13 @@
       <c r="T15" s="89"/>
       <c r="U15" s="89"/>
       <c r="V15" s="89"/>
-      <c r="W15" s="129" t="str">
+      <c r="W15" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X15" s="129" t="str">
+        <v>15</v>
+      </c>
+      <c r="X15" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X15))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Existe-t-il une grille formelle de qualification des incidents?</v>
       </c>
       <c r="Y15" s="89"/>
       <c r="Z15" s="89"/>
@@ -7443,9 +7516,9 @@
       <c r="AC15" s="89"/>
     </row>
     <row r="16" spans="1:32" ht="72">
-      <c r="A16" s="168"/>
-      <c r="B16" s="168"/>
-      <c r="C16" s="200"/>
+      <c r="A16" s="173"/>
+      <c r="B16" s="173"/>
+      <c r="C16" s="205"/>
       <c r="D16" s="30" t="s">
         <v>52</v>
       </c>
@@ -7459,8 +7532,8 @@
         <v>504</v>
       </c>
       <c r="H16" s="24"/>
-      <c r="I16" s="123" t="s">
-        <v>275</v>
+      <c r="I16" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J16" s="50"/>
       <c r="K16" s="89"/>
@@ -7472,13 +7545,13 @@
       <c r="T16" s="89"/>
       <c r="U16" s="89"/>
       <c r="V16" s="89"/>
-      <c r="W16" s="129" t="str">
+      <c r="W16" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X16" s="129" t="str">
+        <v>16</v>
+      </c>
+      <c r="X16" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X16))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Des seuils d’escalade vers la gestion de crise sont-ils définis afin de déclencher rapidement les actions appropriées ?</v>
       </c>
       <c r="Y16" s="89"/>
       <c r="Z16" s="89"/>
@@ -7487,8 +7560,8 @@
       <c r="AC16" s="89"/>
     </row>
     <row r="17" spans="1:29" ht="100.8">
-      <c r="A17" s="168"/>
-      <c r="B17" s="168"/>
+      <c r="A17" s="173"/>
+      <c r="B17" s="173"/>
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
@@ -7505,8 +7578,8 @@
         <v>505</v>
       </c>
       <c r="H17" s="24"/>
-      <c r="I17" s="123" t="s">
-        <v>275</v>
+      <c r="I17" s="152" t="s">
+        <v>273</v>
       </c>
       <c r="J17" s="50"/>
       <c r="K17" s="89"/>
@@ -7518,13 +7591,13 @@
       <c r="T17" s="89"/>
       <c r="U17" s="89"/>
       <c r="V17" s="89"/>
-      <c r="W17" s="129" t="str">
+      <c r="W17" s="128">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="X17" s="129" t="str">
+        <v>17</v>
+      </c>
+      <c r="X17" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X17))-ROW($G$2)+1),"")</f>
-        <v/>
+        <v>Existe-t-il des playbooks formels de confinement et de réponse pour les scénarios d’incidents majeurs afin de guider les actions et réduire les erreurs opérationnelles ?</v>
       </c>
       <c r="Y17" s="89"/>
       <c r="Z17" s="89"/>
@@ -7533,7 +7606,7 @@
       <c r="AC17" s="89"/>
     </row>
     <row r="18" spans="1:29" ht="86.4">
-      <c r="A18" s="168"/>
+      <c r="A18" s="173"/>
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
@@ -7553,7 +7626,7 @@
         <v>506</v>
       </c>
       <c r="H18" s="24"/>
-      <c r="I18" s="123" t="s">
+      <c r="I18" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J18" s="50"/>
@@ -7566,11 +7639,11 @@
       <c r="T18" s="89"/>
       <c r="U18" s="89"/>
       <c r="V18" s="89"/>
-      <c r="W18" s="129" t="str">
+      <c r="W18" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X18" s="129" t="str">
+      <c r="X18" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X18))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7581,7 +7654,7 @@
       <c r="AC18" s="89"/>
     </row>
     <row r="19" spans="1:29" ht="115.2">
-      <c r="A19" s="168"/>
+      <c r="A19" s="173"/>
       <c r="B19" s="4" t="s">
         <v>38</v>
       </c>
@@ -7601,7 +7674,7 @@
         <v>507</v>
       </c>
       <c r="H19" s="24"/>
-      <c r="I19" s="123" t="s">
+      <c r="I19" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J19" s="50"/>
@@ -7614,11 +7687,11 @@
       <c r="T19" s="89"/>
       <c r="U19" s="89"/>
       <c r="V19" s="89"/>
-      <c r="W19" s="129" t="str">
+      <c r="W19" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X19" s="129" t="str">
+      <c r="X19" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X19))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7629,8 +7702,8 @@
       <c r="AC19" s="89"/>
     </row>
     <row r="20" spans="1:29" ht="115.2">
-      <c r="A20" s="168"/>
-      <c r="B20" s="168" t="s">
+      <c r="A20" s="173"/>
+      <c r="B20" s="173" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -7649,7 +7722,7 @@
         <v>508</v>
       </c>
       <c r="H20" s="24"/>
-      <c r="I20" s="123" t="s">
+      <c r="I20" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J20" s="50"/>
@@ -7662,11 +7735,11 @@
       <c r="T20" s="89"/>
       <c r="U20" s="89"/>
       <c r="V20" s="89"/>
-      <c r="W20" s="129" t="str">
+      <c r="W20" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X20" s="129" t="str">
+      <c r="X20" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X20))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7677,8 +7750,8 @@
       <c r="AC20" s="89"/>
     </row>
     <row r="21" spans="1:29" ht="86.4">
-      <c r="A21" s="168"/>
-      <c r="B21" s="168"/>
+      <c r="A21" s="173"/>
+      <c r="B21" s="173"/>
       <c r="C21" s="25" t="s">
         <v>51</v>
       </c>
@@ -7695,7 +7768,7 @@
         <v>509</v>
       </c>
       <c r="H21" s="24"/>
-      <c r="I21" s="123" t="s">
+      <c r="I21" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J21" s="50"/>
@@ -7708,11 +7781,11 @@
       <c r="T21" s="89"/>
       <c r="U21" s="89"/>
       <c r="V21" s="89"/>
-      <c r="W21" s="129" t="str">
+      <c r="W21" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X21" s="129" t="str">
+      <c r="X21" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X21))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7723,8 +7796,8 @@
       <c r="AC21" s="89"/>
     </row>
     <row r="22" spans="1:29" ht="100.8">
-      <c r="A22" s="168"/>
-      <c r="B22" s="168"/>
+      <c r="A22" s="173"/>
+      <c r="B22" s="173"/>
       <c r="C22" s="25" t="s">
         <v>54</v>
       </c>
@@ -7741,7 +7814,7 @@
         <v>76</v>
       </c>
       <c r="H22" s="24"/>
-      <c r="I22" s="123" t="s">
+      <c r="I22" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J22" s="50"/>
@@ -7754,11 +7827,11 @@
       <c r="T22" s="89"/>
       <c r="U22" s="89"/>
       <c r="V22" s="89"/>
-      <c r="W22" s="129" t="str">
+      <c r="W22" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X22" s="129" t="str">
+      <c r="X22" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X22))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7769,8 +7842,8 @@
       <c r="AC22" s="89"/>
     </row>
     <row r="23" spans="1:29" ht="115.2">
-      <c r="A23" s="168"/>
-      <c r="B23" s="168"/>
+      <c r="A23" s="173"/>
+      <c r="B23" s="173"/>
       <c r="C23" s="25" t="s">
         <v>56</v>
       </c>
@@ -7787,7 +7860,7 @@
         <v>510</v>
       </c>
       <c r="H23" s="24"/>
-      <c r="I23" s="123" t="s">
+      <c r="I23" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J23" s="50"/>
@@ -7800,11 +7873,11 @@
       <c r="T23" s="89"/>
       <c r="U23" s="89"/>
       <c r="V23" s="89"/>
-      <c r="W23" s="129" t="str">
+      <c r="W23" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X23" s="129" t="str">
+      <c r="X23" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X23))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7815,8 +7888,8 @@
       <c r="AC23" s="89"/>
     </row>
     <row r="24" spans="1:29" ht="69">
-      <c r="A24" s="168"/>
-      <c r="B24" s="168"/>
+      <c r="A24" s="173"/>
+      <c r="B24" s="173"/>
       <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
@@ -7833,7 +7906,7 @@
         <v>512</v>
       </c>
       <c r="H24" s="24"/>
-      <c r="I24" s="123" t="s">
+      <c r="I24" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J24" s="50"/>
@@ -7846,11 +7919,11 @@
       <c r="T24" s="89"/>
       <c r="U24" s="89"/>
       <c r="V24" s="89"/>
-      <c r="W24" s="129" t="str">
+      <c r="W24" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X24" s="129" t="str">
+      <c r="X24" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X24))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7861,8 +7934,8 @@
       <c r="AC24" s="89"/>
     </row>
     <row r="25" spans="1:29" ht="86.4">
-      <c r="A25" s="168"/>
-      <c r="B25" s="168"/>
+      <c r="A25" s="173"/>
+      <c r="B25" s="173"/>
       <c r="C25" s="4" t="s">
         <v>69</v>
       </c>
@@ -7879,7 +7952,7 @@
         <v>511</v>
       </c>
       <c r="H25" s="24"/>
-      <c r="I25" s="123" t="s">
+      <c r="I25" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J25" s="50"/>
@@ -7892,11 +7965,11 @@
       <c r="T25" s="89"/>
       <c r="U25" s="89"/>
       <c r="V25" s="89"/>
-      <c r="W25" s="129" t="str">
+      <c r="W25" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X25" s="129" t="str">
+      <c r="X25" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X25))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7907,8 +7980,8 @@
       <c r="AC25" s="89"/>
     </row>
     <row r="26" spans="1:29" ht="86.4">
-      <c r="A26" s="168"/>
-      <c r="B26" s="168"/>
+      <c r="A26" s="173"/>
+      <c r="B26" s="173"/>
       <c r="C26" s="4" t="s">
         <v>75</v>
       </c>
@@ -7925,7 +7998,7 @@
         <v>513</v>
       </c>
       <c r="H26" s="24"/>
-      <c r="I26" s="123" t="s">
+      <c r="I26" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J26" s="50"/>
@@ -7938,11 +8011,11 @@
       <c r="T26" s="89"/>
       <c r="U26" s="89"/>
       <c r="V26" s="89"/>
-      <c r="W26" s="129">
+      <c r="W26" s="128" t="str">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="X26" s="129" t="str">
+        <v/>
+      </c>
+      <c r="X26" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X26))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7953,9 +8026,9 @@
       <c r="AC26" s="89"/>
     </row>
     <row r="27" spans="1:29" ht="86.4">
-      <c r="A27" s="168"/>
-      <c r="B27" s="168"/>
-      <c r="C27" s="168" t="s">
+      <c r="A27" s="173"/>
+      <c r="B27" s="173"/>
+      <c r="C27" s="173" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="31" t="s">
@@ -7971,7 +8044,7 @@
         <v>514</v>
       </c>
       <c r="H27" s="24"/>
-      <c r="I27" s="123" t="s">
+      <c r="I27" s="122" t="s">
         <v>275</v>
       </c>
       <c r="J27" s="50"/>
@@ -7984,11 +8057,11 @@
       <c r="T27" s="89"/>
       <c r="U27" s="89"/>
       <c r="V27" s="89"/>
-      <c r="W27" s="129" t="str">
+      <c r="W27" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X27" s="129" t="str">
+      <c r="X27" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X27))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -7999,9 +8072,9 @@
       <c r="AC27" s="89"/>
     </row>
     <row r="28" spans="1:29" ht="86.4">
-      <c r="A28" s="168"/>
-      <c r="B28" s="168"/>
-      <c r="C28" s="168"/>
+      <c r="A28" s="173"/>
+      <c r="B28" s="173"/>
+      <c r="C28" s="173"/>
       <c r="D28" s="31" t="s">
         <v>127</v>
       </c>
@@ -8015,8 +8088,8 @@
         <v>515</v>
       </c>
       <c r="H28" s="24"/>
-      <c r="I28" s="119" t="s">
-        <v>273</v>
+      <c r="I28" s="152" t="s">
+        <v>275</v>
       </c>
       <c r="J28" s="50"/>
       <c r="K28" s="89"/>
@@ -8028,11 +8101,11 @@
       <c r="T28" s="89"/>
       <c r="U28" s="89"/>
       <c r="V28" s="89"/>
-      <c r="W28" s="129" t="str">
+      <c r="W28" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X28" s="129" t="str">
+      <c r="X28" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X28))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -8043,11 +8116,11 @@
       <c r="AC28" s="89"/>
     </row>
     <row r="29" spans="1:29" ht="86.4">
-      <c r="A29" s="168"/>
-      <c r="B29" s="168" t="s">
+      <c r="A29" s="173"/>
+      <c r="B29" s="173" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="168" t="s">
+      <c r="C29" s="173" t="s">
         <v>92</v>
       </c>
       <c r="D29" s="31" t="s">
@@ -8076,11 +8149,11 @@
       <c r="T29" s="89"/>
       <c r="U29" s="89"/>
       <c r="V29" s="89"/>
-      <c r="W29" s="129" t="str">
+      <c r="W29" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X29" s="129" t="str">
+      <c r="X29" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X29))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -8091,9 +8164,9 @@
       <c r="AC29" s="89"/>
     </row>
     <row r="30" spans="1:29" ht="82.8">
-      <c r="A30" s="168"/>
-      <c r="B30" s="168"/>
-      <c r="C30" s="168"/>
+      <c r="A30" s="173"/>
+      <c r="B30" s="173"/>
+      <c r="C30" s="173"/>
       <c r="D30" s="31" t="s">
         <v>103</v>
       </c>
@@ -8118,11 +8191,11 @@
       <c r="T30" s="89"/>
       <c r="U30" s="89"/>
       <c r="V30" s="89"/>
-      <c r="W30" s="129" t="str">
+      <c r="W30" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X30" s="129" t="str">
+      <c r="X30" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X30))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -8133,8 +8206,8 @@
       <c r="AC30" s="89"/>
     </row>
     <row r="31" spans="1:29" ht="69">
-      <c r="A31" s="168"/>
-      <c r="B31" s="168"/>
+      <c r="A31" s="173"/>
+      <c r="B31" s="173"/>
       <c r="C31" s="4"/>
       <c r="D31" s="31" t="s">
         <v>114</v>
@@ -8145,7 +8218,7 @@
       <c r="F31" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="172" t="s">
+      <c r="G31" s="177" t="s">
         <v>517</v>
       </c>
       <c r="H31" s="24"/>
@@ -8160,11 +8233,11 @@
       <c r="T31" s="89"/>
       <c r="U31" s="89"/>
       <c r="V31" s="89"/>
-      <c r="W31" s="129" t="str">
+      <c r="W31" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X31" s="129" t="str">
+      <c r="X31" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X31))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
@@ -8175,8 +8248,8 @@
       <c r="AC31" s="89"/>
     </row>
     <row r="32" spans="1:29" ht="69">
-      <c r="A32" s="168"/>
-      <c r="B32" s="168" t="s">
+      <c r="A32" s="173"/>
+      <c r="B32" s="173" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -8191,24 +8264,24 @@
       <c r="F32" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G32" s="172"/>
+      <c r="G32" s="177"/>
       <c r="H32" s="24"/>
       <c r="I32" s="4" t="s">
         <v>275</v>
       </c>
       <c r="J32" s="50"/>
-      <c r="W32" s="129" t="str">
+      <c r="W32" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X32" s="129" t="str">
+      <c r="X32" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X32))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:24" ht="55.2">
-      <c r="A33" s="168"/>
-      <c r="B33" s="168"/>
+      <c r="A33" s="173"/>
+      <c r="B33" s="173"/>
       <c r="C33" s="4" t="s">
         <v>98</v>
       </c>
@@ -8221,24 +8294,24 @@
       <c r="F33" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="172"/>
+      <c r="G33" s="177"/>
       <c r="H33" s="24"/>
       <c r="I33" s="4" t="s">
         <v>275</v>
       </c>
       <c r="J33" s="50"/>
-      <c r="W33" s="129" t="str">
+      <c r="W33" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X33" s="129" t="str">
+      <c r="X33" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X33))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:24" ht="69">
-      <c r="A34" s="168"/>
-      <c r="B34" s="168" t="s">
+      <c r="A34" s="173"/>
+      <c r="B34" s="173" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="84"/>
@@ -8259,19 +8332,19 @@
         <v>275</v>
       </c>
       <c r="J34" s="50"/>
-      <c r="W34" s="129" t="str">
+      <c r="W34" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X34" s="129" t="str">
+      <c r="X34" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X34))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:24" ht="69">
-      <c r="A35" s="168"/>
-      <c r="B35" s="168"/>
-      <c r="C35" s="168" t="s">
+      <c r="A35" s="173"/>
+      <c r="B35" s="173"/>
+      <c r="C35" s="173" t="s">
         <v>124</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -8291,57 +8364,57 @@
         <v>275</v>
       </c>
       <c r="J35" s="50"/>
-      <c r="W35" s="129" t="str">
+      <c r="W35" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X35" s="129" t="str">
+      <c r="X35" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X35))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:24" ht="232.05" customHeight="1">
-      <c r="A36" s="168"/>
-      <c r="B36" s="168"/>
-      <c r="C36" s="168"/>
-      <c r="D36" s="203" t="s">
+      <c r="A36" s="173"/>
+      <c r="B36" s="173"/>
+      <c r="C36" s="173"/>
+      <c r="D36" s="208" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="168" t="s">
+      <c r="E36" s="173" t="s">
         <v>255</v>
       </c>
-      <c r="F36" s="168" t="s">
+      <c r="F36" s="173" t="s">
         <v>261</v>
       </c>
-      <c r="G36" s="168" t="s">
+      <c r="G36" s="173" t="s">
         <v>518</v>
       </c>
-      <c r="H36" s="168"/>
-      <c r="I36" s="168" t="s">
+      <c r="H36" s="173"/>
+      <c r="I36" s="173" t="s">
         <v>275</v>
       </c>
-      <c r="W36" s="129" t="str">
+      <c r="W36" s="128" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="X36" s="129" t="str">
+      <c r="X36" s="128" t="str">
         <f>IFERROR(INDEX($G$2:$G$100,SMALL($W$2:$W$100,ROWS($X$2:X36))-ROW($G$2)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" s="168"/>
-      <c r="B37" s="168"/>
-      <c r="C37" s="168"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="168"/>
+      <c r="A37" s="173"/>
+      <c r="B37" s="173"/>
+      <c r="C37" s="173"/>
+      <c r="D37" s="208"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="173"/>
       <c r="J37" s="50"/>
       <c r="W37" s="89" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W3:W37" si="1">IF(I39="No",ROW(), "")</f>
         <v/>
       </c>
       <c r="X37" s="89" t="str">
@@ -8390,29 +8463,29 @@
     <mergeCell ref="C29:C30"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:D1">
-    <cfRule type="expression" dxfId="35" priority="7">
+    <cfRule type="expression" dxfId="39" priority="7">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I1">
-    <cfRule type="expression" dxfId="34" priority="5">
+    <cfRule type="expression" dxfId="38" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="6">
+    <cfRule type="expression" dxfId="37" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I36">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8445,11 +8518,11 @@
     <col min="7" max="7" width="31.44140625" customWidth="1"/>
     <col min="8" max="9" width="50.33203125" customWidth="1"/>
     <col min="11" max="11" width="7.44140625" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" customWidth="1"/>
-    <col min="13" max="13" width="31.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" customWidth="1"/>
     <col min="14" max="14" width="30.21875" customWidth="1"/>
     <col min="15" max="15" width="25.77734375" customWidth="1"/>
-    <col min="16" max="16" width="22.44140625" customWidth="1"/>
+    <col min="16" max="16" width="28.88671875" customWidth="1"/>
     <col min="17" max="17" width="19.109375" customWidth="1"/>
     <col min="18" max="18" width="38.5546875" customWidth="1"/>
     <col min="21" max="21" width="112.44140625" customWidth="1"/>
@@ -8477,10 +8550,10 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="186" t="s">
+      <c r="L2" s="191" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="187"/>
+      <c r="M2" s="192"/>
       <c r="N2" s="112" t="s">
         <v>600</v>
       </c>
@@ -8525,46 +8598,46 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="176">
+      <c r="L3" s="181">
         <f>COUNTA(H4:H25)</f>
         <v>21</v>
       </c>
-      <c r="M3" s="188"/>
-      <c r="N3" s="204">
+      <c r="M3" s="193"/>
+      <c r="N3" s="209">
         <f>L3-Q3</f>
         <v>20</v>
       </c>
-      <c r="O3" s="191">
+      <c r="O3" s="196">
         <f>COUNTIF(J4:J21,"Yes")</f>
         <v>6</v>
       </c>
-      <c r="P3" s="194">
+      <c r="P3" s="199">
         <f>COUNTIF(J4:J21,"No")</f>
         <v>10</v>
       </c>
-      <c r="Q3" s="197">
+      <c r="Q3" s="202">
         <f>COUNTIF(J4:J21,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R3" s="179">
+      <c r="R3" s="184">
         <f>O3/N3</f>
         <v>0.3</v>
       </c>
-      <c r="T3" s="219"/>
-      <c r="U3" s="219"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="151"/>
     </row>
     <row r="4" spans="1:21" ht="94.5" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="169" t="s">
+      <c r="B4" s="174" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="163" t="s">
+      <c r="C4" s="168" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="173" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="212" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -8573,64 +8646,70 @@
       <c r="G4" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="172" t="s">
+      <c r="H4" s="177" t="s">
         <v>321</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="J4" s="168" t="s">
+      <c r="J4" s="173" t="s">
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="189"/>
-      <c r="N4" s="205"/>
-      <c r="O4" s="192"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="198"/>
-      <c r="R4" s="180"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="194"/>
+      <c r="N4" s="210"/>
+      <c r="O4" s="197"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="203"/>
+      <c r="R4" s="185"/>
+      <c r="T4" s="153" t="str">
+        <f t="shared" ref="T4:T25" si="0">IF(J4="No",ROW(), "")</f>
+        <v/>
+      </c>
+      <c r="U4" s="149" t="str">
+        <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U4))-ROW($H$4)+1),"")</f>
+        <v>La communication peut-elle être maintenue si les systèmes internes sont compromis ?</v>
+      </c>
     </row>
     <row r="5" spans="1:21" ht="81" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="170"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="207"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="212"/>
       <c r="F5" s="12" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="H5" s="172"/>
+      <c r="H5" s="177"/>
       <c r="I5" s="24" t="s">
         <v>568</v>
       </c>
-      <c r="J5" s="168"/>
+      <c r="J5" s="173"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="206"/>
-      <c r="O5" s="193"/>
-      <c r="P5" s="196"/>
-      <c r="Q5" s="199"/>
-      <c r="R5" s="181"/>
-      <c r="T5" s="144" t="str">
-        <f t="shared" ref="T5:T25" si="0">IF(J5="No",ROW(), "")</f>
-        <v/>
-      </c>
-      <c r="U5" s="144" t="str">
+      <c r="L5" s="183"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="211"/>
+      <c r="O5" s="198"/>
+      <c r="P5" s="201"/>
+      <c r="Q5" s="204"/>
+      <c r="R5" s="186"/>
+      <c r="T5" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U5" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U5))-ROW($H$4)+1),"")</f>
         <v>Les membres de la cellule de crise sont-ils identifiés (IT, sécurité, juridique, communication, direction) ?</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="111" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="170"/>
-      <c r="C6" s="165"/>
+      <c r="B6" s="175"/>
+      <c r="C6" s="170"/>
       <c r="D6" s="2" t="s">
         <v>384</v>
       </c>
@@ -8649,7 +8728,7 @@
       <c r="I6" s="24" t="s">
         <v>569</v>
       </c>
-      <c r="J6" s="132" t="s">
+      <c r="J6" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K6" s="50"/>
@@ -8659,31 +8738,31 @@
       <c r="P6" s="67"/>
       <c r="Q6" s="67"/>
       <c r="R6" s="50"/>
-      <c r="T6" s="144">
+      <c r="T6" s="140">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="U6" s="144" t="str">
+      <c r="U6" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U6))-ROW($H$4)+1),"")</f>
         <v>Les rôles et responsabilités sont-ils clairement définis et compris ? Existe-t-il des remplaçants en cas d’indisponibilité ?</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="61.95" customHeight="1" thickBot="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="168" t="s">
+      <c r="B7" s="175"/>
+      <c r="C7" s="173" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="168" t="s">
+      <c r="D7" s="173" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="207" t="s">
+      <c r="E7" s="212" t="s">
         <v>546</v>
       </c>
-      <c r="F7" s="208" t="s">
+      <c r="F7" s="213" t="s">
         <v>547</v>
       </c>
-      <c r="G7" s="209" t="s">
+      <c r="G7" s="214" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -8692,42 +8771,42 @@
       <c r="I7" s="24" t="s">
         <v>570</v>
       </c>
-      <c r="J7" s="132" t="s">
+      <c r="J7" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K7" s="50"/>
       <c r="L7" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="M7" s="121" t="s">
+      <c r="M7" s="120" t="s">
         <v>612</v>
       </c>
       <c r="N7" s="50"/>
       <c r="O7" s="109"/>
-      <c r="T7" s="144">
+      <c r="T7" s="140">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="U7" s="144" t="str">
+      <c r="U7" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U7))-ROW($H$4)+1),"")</f>
         <v>Les outils de monitoring permettent-ils une détection en temps réel des incidents majeurs ?</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="53.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="170"/>
-      <c r="C8" s="168"/>
-      <c r="D8" s="168"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="209"/>
+      <c r="B8" s="175"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="212"/>
+      <c r="F8" s="213"/>
+      <c r="G8" s="214"/>
       <c r="H8" s="24" t="s">
         <v>320</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>570</v>
       </c>
-      <c r="J8" s="132" t="s">
+      <c r="J8" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K8" s="50"/>
@@ -8735,18 +8814,18 @@
       <c r="M8" s="50"/>
       <c r="N8" s="50"/>
       <c r="O8" s="110"/>
-      <c r="T8" s="144">
+      <c r="T8" s="140">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="U8" s="144" t="str">
+      <c r="U8" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U8))-ROW($H$4)+1),"")</f>
         <v>Combien de temps faut-il en moyenne pour isoler un système compromis ?</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="57.6">
       <c r="A9" s="50"/>
-      <c r="B9" s="170"/>
+      <c r="B9" s="175"/>
       <c r="C9" s="4" t="s">
         <v>306</v>
       </c>
@@ -8768,7 +8847,7 @@
       <c r="I9" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="J9" s="132" t="s">
+      <c r="J9" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K9" s="50"/>
@@ -8776,22 +8855,22 @@
       <c r="M9" s="50"/>
       <c r="N9" s="50"/>
       <c r="O9" s="50"/>
-      <c r="T9" s="144">
+      <c r="T9" s="140">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="U9" s="144" t="str">
+      <c r="U9" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U9))-ROW($H$4)+1),"")</f>
         <v>Des runbooks sont-ils disponibles pour les scénarios cyber majeurs</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="58.05" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="170"/>
-      <c r="C10" s="200" t="s">
+      <c r="B10" s="175"/>
+      <c r="C10" s="205" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="163" t="s">
+      <c r="D10" s="168" t="s">
         <v>439</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -8809,7 +8888,7 @@
       <c r="I10" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="J10" s="132" t="s">
+      <c r="J10" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K10" s="50"/>
@@ -8817,20 +8896,20 @@
       <c r="M10" s="50"/>
       <c r="N10" s="50"/>
       <c r="O10" s="50"/>
-      <c r="T10" s="144">
+      <c r="T10" s="140">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="U10" s="144" t="str">
+      <c r="U10" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U10))-ROW($H$4)+1),"")</f>
         <v>Un prestataire de réponse à incident (IR) est-il contractuellement prévu ?</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="43.2">
       <c r="A11" s="50"/>
-      <c r="B11" s="170"/>
-      <c r="C11" s="200"/>
-      <c r="D11" s="165"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="205"/>
+      <c r="D11" s="170"/>
       <c r="E11" s="2" t="s">
         <v>392</v>
       </c>
@@ -8846,7 +8925,7 @@
       <c r="I11" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="J11" s="132" t="s">
+      <c r="J11" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K11" s="50"/>
@@ -8854,22 +8933,22 @@
       <c r="M11" s="50"/>
       <c r="N11" s="50"/>
       <c r="O11" s="50"/>
-      <c r="T11" s="144">
+      <c r="T11" s="140">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="U11" s="144" t="str">
+      <c r="U11" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U11))-ROW($H$4)+1),"")</f>
         <v>Existe-t-il un mécanisme de communication avec CERT/autorités ?</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="52.05" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="170"/>
-      <c r="C12" s="169" t="s">
+      <c r="B12" s="175"/>
+      <c r="C12" s="174" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="200" t="s">
+      <c r="D12" s="205" t="s">
         <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -8887,27 +8966,27 @@
       <c r="I12" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="J12" s="132" t="s">
+      <c r="J12" s="131" t="s">
         <v>273</v>
       </c>
       <c r="L12" s="50"/>
       <c r="M12" s="50"/>
       <c r="N12" s="50"/>
       <c r="O12" s="50"/>
-      <c r="T12" s="144">
+      <c r="T12" s="140">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="U12" s="144" t="str">
+      <c r="U12" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U12))-ROW($H$4)+1),"")</f>
         <v>Comment La coordination avec fournisseurs, cloud providers et partenaires est-elle intégrée dans la gestion de crise ?</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="58.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="170"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="200"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="205"/>
       <c r="E13" s="2" t="s">
         <v>401</v>
       </c>
@@ -8923,26 +9002,26 @@
       <c r="I13" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="J13" s="132" t="s">
+      <c r="J13" s="131" t="s">
         <v>273</v>
       </c>
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
       <c r="N13" s="50"/>
       <c r="O13" s="50"/>
-      <c r="T13" s="144">
+      <c r="T13" s="140">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="U13" s="144" t="str">
+      <c r="U13" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U13))-ROW($H$4)+1),"")</f>
         <v>Le temps de détection (MTTD) et de réponse (MTTR) est-il mesuré ?</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="170"/>
-      <c r="C14" s="171"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="176"/>
       <c r="D14" s="3" t="s">
         <v>441</v>
       </c>
@@ -8961,24 +9040,24 @@
       <c r="I14" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="J14" s="132" t="s">
+      <c r="J14" s="131" t="s">
         <v>273</v>
       </c>
-      <c r="T14" s="144">
+      <c r="T14" s="140">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U14" s="144" t="str">
+      <c r="U14" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U14))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:21" ht="66" customHeight="1">
-      <c r="B15" s="170"/>
-      <c r="C15" s="168" t="s">
+      <c r="B15" s="175"/>
+      <c r="C15" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="D15" s="169" t="s">
+      <c r="D15" s="174" t="s">
         <v>442</v>
       </c>
       <c r="E15" s="24" t="s">
@@ -8996,22 +9075,22 @@
       <c r="I15" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="J15" s="132" t="s">
+      <c r="J15" s="131" t="s">
         <v>273</v>
       </c>
-      <c r="T15" s="144">
+      <c r="T15" s="140">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U15" s="144" t="str">
+      <c r="U15" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($T$4:$T$100,ROWS($U$4:U15))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:21" ht="43.2">
-      <c r="B16" s="170"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="171"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="176"/>
       <c r="E16" s="24" t="s">
         <v>407</v>
       </c>
@@ -9040,11 +9119,11 @@
       </c>
     </row>
     <row r="17" spans="2:21" ht="77.55" customHeight="1">
-      <c r="B17" s="170"/>
-      <c r="C17" s="163" t="s">
+      <c r="B17" s="175"/>
+      <c r="C17" s="168" t="s">
         <v>316</v>
       </c>
-      <c r="D17" s="169" t="s">
+      <c r="D17" s="174" t="s">
         <v>443</v>
       </c>
       <c r="E17" s="74" t="s">
@@ -9075,9 +9154,9 @@
       </c>
     </row>
     <row r="18" spans="2:21" ht="57.6">
-      <c r="B18" s="170"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="171"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="170"/>
+      <c r="D18" s="176"/>
       <c r="E18" s="72" t="s">
         <v>413</v>
       </c>
@@ -9106,8 +9185,8 @@
       </c>
     </row>
     <row r="19" spans="2:21" ht="42" customHeight="1">
-      <c r="B19" s="170"/>
-      <c r="C19" s="200" t="s">
+      <c r="B19" s="175"/>
+      <c r="C19" s="205" t="s">
         <v>323</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -9141,8 +9220,8 @@
       </c>
     </row>
     <row r="20" spans="2:21" ht="39" customHeight="1">
-      <c r="B20" s="170"/>
-      <c r="C20" s="200"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="205"/>
       <c r="D20" s="3" t="s">
         <v>445</v>
       </c>
@@ -9174,11 +9253,11 @@
       </c>
     </row>
     <row r="21" spans="2:21" ht="43.2">
-      <c r="B21" s="170"/>
-      <c r="C21" s="168" t="s">
+      <c r="B21" s="175"/>
+      <c r="C21" s="173" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="169" t="s">
+      <c r="D21" s="174" t="s">
         <v>446</v>
       </c>
       <c r="E21" s="65" t="s">
@@ -9209,9 +9288,9 @@
       </c>
     </row>
     <row r="22" spans="2:21" ht="41.55" customHeight="1">
-      <c r="B22" s="170"/>
-      <c r="C22" s="168"/>
-      <c r="D22" s="171"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="173"/>
+      <c r="D22" s="176"/>
       <c r="E22" s="24" t="s">
         <v>427</v>
       </c>
@@ -9240,7 +9319,7 @@
       </c>
     </row>
     <row r="23" spans="2:21" ht="57.6">
-      <c r="B23" s="170"/>
+      <c r="B23" s="175"/>
       <c r="C23" s="4" t="s">
         <v>330</v>
       </c>
@@ -9275,8 +9354,8 @@
       </c>
     </row>
     <row r="24" spans="2:21" ht="43.2">
-      <c r="B24" s="170"/>
-      <c r="C24" s="200" t="s">
+      <c r="B24" s="175"/>
+      <c r="C24" s="205" t="s">
         <v>333</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -9310,8 +9389,8 @@
       </c>
     </row>
     <row r="25" spans="2:21" ht="43.2">
-      <c r="B25" s="171"/>
-      <c r="C25" s="200"/>
+      <c r="B25" s="176"/>
+      <c r="C25" s="205"/>
       <c r="D25" s="3" t="s">
         <v>447</v>
       </c>
@@ -9379,29 +9458,29 @@
     <mergeCell ref="Q3:Q5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="28" priority="11">
+    <cfRule type="expression" dxfId="32" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="27" priority="5">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="6">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6:J26">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9457,10 +9536,10 @@
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="186" t="s">
+      <c r="L2" s="191" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="187"/>
+      <c r="M2" s="192"/>
       <c r="N2" s="112" t="s">
         <v>601</v>
       </c>
@@ -9507,43 +9586,43 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="176">
+      <c r="L3" s="181">
         <f>COUNTA(H4:H25)</f>
         <v>11</v>
       </c>
-      <c r="M3" s="188"/>
-      <c r="N3" s="204">
+      <c r="M3" s="193"/>
+      <c r="N3" s="209">
         <f>L3-Q3</f>
         <v>9</v>
       </c>
-      <c r="O3" s="191">
+      <c r="O3" s="196">
         <f>COUNTIF(J4:J25,"Yes")</f>
         <v>4</v>
       </c>
-      <c r="P3" s="194">
+      <c r="P3" s="199">
         <f>COUNTIF(J4:J25,"No")</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="197">
+      <c r="Q3" s="202">
         <f>COUNTIF(J4:J25,"N/A")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="179">
+      <c r="R3" s="184">
         <f>O3/N3</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="V3" s="219"/>
-      <c r="W3" s="219"/>
+      <c r="V3" s="151"/>
+      <c r="W3" s="151"/>
     </row>
     <row r="4" spans="1:23" ht="120" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="173" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="173" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="218" t="s">
         <v>343</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -9555,43 +9634,43 @@
       <c r="G4" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="I4" s="210" t="s">
+      <c r="I4" s="215" t="s">
         <v>525</v>
       </c>
-      <c r="J4" s="168" t="s">
+      <c r="J4" s="173" t="s">
         <v>273</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="189"/>
-      <c r="N4" s="205"/>
-      <c r="O4" s="192"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="198"/>
-      <c r="R4" s="180"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="194"/>
+      <c r="N4" s="210"/>
+      <c r="O4" s="197"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="203"/>
+      <c r="R4" s="185"/>
       <c r="S4" s="90" t="s">
         <v>611</v>
       </c>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="120" t="s">
         <v>613</v>
       </c>
-      <c r="V4" s="144">
+      <c r="V4" s="140">
         <f>IF(J4="No",ROW(), "")</f>
         <v>4</v>
       </c>
-      <c r="W4" s="144" t="str">
+      <c r="W4" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W4:W$4))-ROW($H$4)+1),"")</f>
         <v>Comment les processus métiers sont-ils identifiés, priorisés et classifiés ?</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="169.05" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="218"/>
       <c r="E5" s="8" t="s">
         <v>347</v>
       </c>
@@ -9601,31 +9680,31 @@
       <c r="G5" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="213"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="168"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="173"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="206"/>
-      <c r="O5" s="193"/>
-      <c r="P5" s="196"/>
-      <c r="Q5" s="199"/>
-      <c r="R5" s="181"/>
-      <c r="V5" s="144" t="str">
+      <c r="L5" s="183"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="211"/>
+      <c r="O5" s="198"/>
+      <c r="P5" s="201"/>
+      <c r="Q5" s="204"/>
+      <c r="R5" s="186"/>
+      <c r="V5" s="140" t="str">
         <f t="shared" ref="V5:V25" si="0">IF(J5="No",ROW(), "")</f>
         <v/>
       </c>
-      <c r="W5" s="144" t="str">
+      <c r="W5" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W5))-ROW($H$4)+1),"")</f>
         <v>Toutes les dépendances internes et externes, y compris les fournisseurs, partenaires, systèmes informatiques et le personnel, ont-elles été identifiées et intégrées dans le BIA ?</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="141" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="168"/>
-      <c r="C6" s="168"/>
-      <c r="D6" s="213"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="173"/>
+      <c r="D6" s="218"/>
       <c r="E6" s="8" t="s">
         <v>349</v>
       </c>
@@ -9635,13 +9714,13 @@
       <c r="G6" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="213" t="s">
+      <c r="H6" s="218" t="s">
         <v>351</v>
       </c>
-      <c r="I6" s="210" t="s">
+      <c r="I6" s="215" t="s">
         <v>526</v>
       </c>
-      <c r="J6" s="168" t="s">
+      <c r="J6" s="173" t="s">
         <v>273</v>
       </c>
       <c r="K6" s="50"/>
@@ -9649,20 +9728,20 @@
       <c r="M6" s="57"/>
       <c r="N6" s="57"/>
       <c r="O6" s="50"/>
-      <c r="V6" s="144">
+      <c r="V6" s="140">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="W6" s="144" t="str">
+      <c r="W6" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W6))-ROW($H$4)+1),"")</f>
         <v>Comment l’entreprise s’assure-t-elle que les équipes connaissent leurs rôles en cas de crise ?</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="151.94999999999999" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="168"/>
-      <c r="C7" s="168"/>
-      <c r="D7" s="213"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="218"/>
       <c r="E7" s="27" t="s">
         <v>352</v>
       </c>
@@ -9672,28 +9751,28 @@
       <c r="G7" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="213"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="168"/>
+      <c r="H7" s="218"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="173"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
       <c r="O7" s="109"/>
-      <c r="V7" s="144" t="str">
+      <c r="V7" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W7" s="144" t="str">
+      <c r="W7" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W7))-ROW($H$4)+1),"")</f>
         <v>Le personnel critique a-t-il été identifié et formé de manière appropriée pour faire face aux perturbations ?</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="109.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="168"/>
-      <c r="C8" s="168"/>
-      <c r="D8" s="172" t="s">
+      <c r="B8" s="173"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="177" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="27" t="s">
@@ -9705,31 +9784,31 @@
       <c r="G8" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="172" t="s">
+      <c r="H8" s="177" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="163" t="s">
+      <c r="I8" s="168" t="s">
         <v>527</v>
       </c>
-      <c r="J8" s="168" t="s">
+      <c r="J8" s="173" t="s">
         <v>274</v>
       </c>
       <c r="K8" s="50"/>
       <c r="O8" s="110"/>
-      <c r="V8" s="144" t="str">
+      <c r="V8" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W8" s="144" t="str">
+      <c r="W8" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W8))-ROW($H$4)+1),"")</f>
         <v>Quand les scénarios du BIA ont-ils été testés pour la dernière fois et quels types de tests ont été réalisés ?</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="136.05000000000001" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="172"/>
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="177"/>
       <c r="E9" s="27" t="s">
         <v>356</v>
       </c>
@@ -9739,26 +9818,26 @@
       <c r="G9" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="H9" s="172"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="168"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="170"/>
+      <c r="J9" s="173"/>
       <c r="K9" s="50"/>
-      <c r="V9" s="144" t="str">
+      <c r="V9" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W9" s="144" t="str">
+      <c r="W9" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W9))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:23" ht="132.44999999999999" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="168"/>
-      <c r="C10" s="168" t="s">
+      <c r="B10" s="173"/>
+      <c r="C10" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="172" t="s">
+      <c r="D10" s="177" t="s">
         <v>358</v>
       </c>
       <c r="E10" s="27" t="s">
@@ -9770,30 +9849,30 @@
       <c r="G10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="213" t="s">
+      <c r="H10" s="218" t="s">
         <v>528</v>
       </c>
-      <c r="I10" s="210" t="s">
+      <c r="I10" s="215" t="s">
         <v>529</v>
       </c>
-      <c r="J10" s="168" t="s">
+      <c r="J10" s="173" t="s">
         <v>275</v>
       </c>
       <c r="K10" s="50"/>
-      <c r="V10" s="144" t="str">
+      <c r="V10" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W10" s="144" t="str">
+      <c r="W10" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W10))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:23" ht="138.44999999999999" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="168"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="172"/>
+      <c r="B11" s="173"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="177"/>
       <c r="E11" s="31" t="s">
         <v>361</v>
       </c>
@@ -9803,24 +9882,24 @@
       <c r="G11" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="213"/>
-      <c r="I11" s="211"/>
-      <c r="J11" s="168"/>
+      <c r="H11" s="218"/>
+      <c r="I11" s="216"/>
+      <c r="J11" s="173"/>
       <c r="K11" s="50"/>
-      <c r="V11" s="144" t="str">
+      <c r="V11" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W11" s="144" t="str">
+      <c r="W11" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W11))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:23" ht="121.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="168"/>
-      <c r="C12" s="168"/>
-      <c r="D12" s="172" t="s">
+      <c r="B12" s="173"/>
+      <c r="C12" s="173"/>
+      <c r="D12" s="177" t="s">
         <v>307</v>
       </c>
       <c r="E12" s="31" t="s">
@@ -9832,30 +9911,30 @@
       <c r="G12" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="213" t="s">
+      <c r="H12" s="218" t="s">
         <v>342</v>
       </c>
-      <c r="I12" s="210" t="s">
+      <c r="I12" s="215" t="s">
         <v>530</v>
       </c>
-      <c r="J12" s="168" t="s">
+      <c r="J12" s="173" t="s">
         <v>274</v>
       </c>
       <c r="K12" s="50"/>
-      <c r="V12" s="144" t="str">
+      <c r="V12" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W12" s="144" t="str">
+      <c r="W12" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W12))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:23" ht="154.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="168"/>
-      <c r="C13" s="168"/>
-      <c r="D13" s="172"/>
+      <c r="B13" s="173"/>
+      <c r="C13" s="173"/>
+      <c r="D13" s="177"/>
       <c r="E13" s="31" t="s">
         <v>364</v>
       </c>
@@ -9865,23 +9944,23 @@
       <c r="G13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="213"/>
-      <c r="I13" s="215"/>
-      <c r="J13" s="168"/>
+      <c r="H13" s="218"/>
+      <c r="I13" s="220"/>
+      <c r="J13" s="173"/>
       <c r="K13" s="50"/>
-      <c r="V13" s="144" t="str">
+      <c r="V13" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W13" s="144" t="str">
+      <c r="W13" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W13))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:23" ht="144.44999999999999" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="168"/>
-      <c r="C14" s="168"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="173"/>
       <c r="D14" s="24" t="s">
         <v>18</v>
       </c>
@@ -9894,33 +9973,33 @@
       <c r="G14" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="213"/>
-      <c r="I14" s="211"/>
-      <c r="J14" s="168"/>
+      <c r="H14" s="218"/>
+      <c r="I14" s="216"/>
+      <c r="J14" s="173"/>
       <c r="K14" s="50"/>
-      <c r="V14" s="144" t="str">
+      <c r="V14" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W14" s="144" t="str">
+      <c r="W14" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W14))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:23" ht="52.95" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="168" t="s">
+      <c r="B15" s="173"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="173" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="216" t="s">
+      <c r="E15" s="221" t="s">
         <v>369</v>
       </c>
-      <c r="F15" s="214" t="s">
+      <c r="F15" s="219" t="s">
         <v>370</v>
       </c>
-      <c r="G15" s="217" t="s">
+      <c r="G15" s="222" t="s">
         <v>169</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -9929,50 +10008,50 @@
       <c r="I15" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="J15" s="132" t="s">
+      <c r="J15" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K15" s="50"/>
-      <c r="V15" s="144">
+      <c r="V15" s="140">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="W15" s="144" t="str">
+      <c r="W15" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W15))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:23" ht="91.05" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="168"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="214"/>
-      <c r="G16" s="217"/>
+      <c r="B16" s="173"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="221"/>
+      <c r="F16" s="219"/>
+      <c r="G16" s="222"/>
       <c r="H16" s="70" t="s">
         <v>532</v>
       </c>
       <c r="I16" s="70" t="s">
         <v>533</v>
       </c>
-      <c r="J16" s="132" t="s">
+      <c r="J16" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K16" s="50"/>
-      <c r="V16" s="144">
+      <c r="V16" s="140">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="W16" s="144" t="str">
+      <c r="W16" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W16))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:23" ht="124.05" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="168"/>
-      <c r="C17" s="168"/>
+      <c r="B17" s="173"/>
+      <c r="C17" s="173"/>
       <c r="D17" s="60" t="s">
         <v>368</v>
       </c>
@@ -9985,29 +10064,29 @@
       <c r="G17" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H17" s="213" t="s">
+      <c r="H17" s="218" t="s">
         <v>371</v>
       </c>
-      <c r="I17" s="210" t="s">
+      <c r="I17" s="215" t="s">
         <v>534</v>
       </c>
-      <c r="J17" s="168" t="s">
+      <c r="J17" s="173" t="s">
         <v>273</v>
       </c>
       <c r="K17" s="50"/>
-      <c r="V17" s="144">
+      <c r="V17" s="140">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="W17" s="144" t="str">
+      <c r="W17" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W17))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:23" ht="123" customHeight="1">
       <c r="A18" s="50"/>
-      <c r="B18" s="168"/>
-      <c r="C18" s="168"/>
+      <c r="B18" s="173"/>
+      <c r="C18" s="173"/>
       <c r="D18" s="24" t="s">
         <v>19</v>
       </c>
@@ -10020,24 +10099,24 @@
       <c r="G18" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="213"/>
-      <c r="I18" s="211"/>
-      <c r="J18" s="168"/>
+      <c r="H18" s="218"/>
+      <c r="I18" s="216"/>
+      <c r="J18" s="173"/>
       <c r="K18" s="50"/>
-      <c r="V18" s="144" t="str">
+      <c r="V18" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W18" s="144" t="str">
+      <c r="W18" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W18))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:23" ht="118.05" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="168"/>
-      <c r="C19" s="168"/>
-      <c r="D19" s="172" t="s">
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="177" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="31" t="s">
@@ -10049,32 +10128,32 @@
       <c r="G19" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="212" t="s">
+      <c r="H19" s="217" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="210" t="s">
+      <c r="I19" s="215" t="s">
         <v>535</v>
       </c>
-      <c r="J19" s="168" t="s">
+      <c r="J19" s="173" t="s">
         <v>275</v>
       </c>
       <c r="K19" s="50"/>
       <c r="M19" s="47"/>
       <c r="N19" s="47"/>
-      <c r="V19" s="144" t="str">
+      <c r="V19" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W19" s="144" t="str">
+      <c r="W19" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W19))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:23" ht="123" customHeight="1">
       <c r="A20" s="50"/>
-      <c r="B20" s="168"/>
-      <c r="C20" s="168"/>
-      <c r="D20" s="172"/>
+      <c r="B20" s="173"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="177"/>
       <c r="E20" s="31" t="s">
         <v>30</v>
       </c>
@@ -10084,28 +10163,28 @@
       <c r="G20" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="212"/>
-      <c r="I20" s="215"/>
-      <c r="J20" s="168"/>
+      <c r="H20" s="217"/>
+      <c r="I20" s="220"/>
+      <c r="J20" s="173"/>
       <c r="K20" s="51"/>
       <c r="L20" s="45"/>
       <c r="M20" s="45"/>
       <c r="N20" s="45"/>
       <c r="O20" s="46"/>
-      <c r="V20" s="144" t="str">
+      <c r="V20" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W20" s="144" t="str">
+      <c r="W20" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W20))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:23" ht="106.05" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="168"/>
-      <c r="C21" s="168"/>
-      <c r="D21" s="172"/>
+      <c r="B21" s="173"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="177"/>
       <c r="E21" s="31" t="s">
         <v>26</v>
       </c>
@@ -10115,83 +10194,83 @@
       <c r="G21" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="212"/>
-      <c r="I21" s="211"/>
-      <c r="J21" s="168"/>
+      <c r="H21" s="217"/>
+      <c r="I21" s="216"/>
+      <c r="J21" s="173"/>
       <c r="K21" s="50"/>
-      <c r="V21" s="144" t="str">
+      <c r="V21" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W21" s="144" t="str">
+      <c r="W21" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W21))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:23" ht="78" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="168"/>
-      <c r="C22" s="168" t="s">
+      <c r="B22" s="173"/>
+      <c r="C22" s="173" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="168" t="s">
+      <c r="D22" s="173" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="216" t="s">
+      <c r="E22" s="221" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="214" t="s">
+      <c r="F22" s="219" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="H22" s="213" t="s">
+      <c r="H22" s="218" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="210" t="s">
+      <c r="I22" s="215" t="s">
         <v>536</v>
       </c>
-      <c r="J22" s="168" t="s">
+      <c r="J22" s="173" t="s">
         <v>275</v>
       </c>
       <c r="K22" s="50"/>
-      <c r="V22" s="144" t="str">
+      <c r="V22" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W22" s="144" t="str">
+      <c r="W22" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W22))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:23" ht="72">
       <c r="A23" s="50"/>
-      <c r="B23" s="168"/>
-      <c r="C23" s="168"/>
-      <c r="D23" s="168"/>
-      <c r="E23" s="216"/>
-      <c r="F23" s="214"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="219"/>
       <c r="G23" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="H23" s="213"/>
-      <c r="I23" s="215"/>
-      <c r="J23" s="168"/>
+      <c r="H23" s="218"/>
+      <c r="I23" s="220"/>
+      <c r="J23" s="173"/>
       <c r="K23" s="50"/>
-      <c r="V23" s="144" t="str">
+      <c r="V23" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W23" s="144" t="str">
+      <c r="W23" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W23))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:23" ht="72">
       <c r="A24" s="50"/>
-      <c r="B24" s="168"/>
-      <c r="C24" s="168"/>
+      <c r="B24" s="173"/>
+      <c r="C24" s="173"/>
       <c r="D24" s="24" t="s">
         <v>12</v>
       </c>
@@ -10204,23 +10283,23 @@
       <c r="G24" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="213"/>
-      <c r="I24" s="211"/>
-      <c r="J24" s="168"/>
+      <c r="H24" s="218"/>
+      <c r="I24" s="216"/>
+      <c r="J24" s="173"/>
       <c r="K24" s="50"/>
-      <c r="V24" s="144" t="str">
+      <c r="V24" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W24" s="144" t="str">
+      <c r="W24" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W24))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:23" ht="100.8">
       <c r="A25" s="50"/>
-      <c r="B25" s="168"/>
-      <c r="C25" s="168"/>
+      <c r="B25" s="173"/>
+      <c r="C25" s="173"/>
       <c r="D25" s="2" t="s">
         <v>17</v>
       </c>
@@ -10239,15 +10318,15 @@
       <c r="I25" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="J25" s="123" t="s">
+      <c r="J25" s="122" t="s">
         <v>275</v>
       </c>
       <c r="K25" s="50"/>
-      <c r="V25" s="144" t="str">
+      <c r="V25" s="140" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="W25" s="144" t="str">
+      <c r="W25" s="140" t="str">
         <f>IFERROR(INDEX($H$4:$H$100,SMALL($V$4:$V$100,ROWS($W$4:W25))-ROW($H$4)+1),"")</f>
         <v/>
       </c>
@@ -10316,59 +10395,59 @@
     <mergeCell ref="I10:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:D3 E3:E4">
-    <cfRule type="expression" dxfId="21" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="20" priority="5">
+    <cfRule type="expression" dxfId="24" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="23" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="22" priority="18">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$A6="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="19" priority="13">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$A5="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F4">
-    <cfRule type="expression" dxfId="12" priority="9">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>$A4="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J8 J10 J12 J19 J22 J25 J6 J15:J17">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10427,13 +10506,13 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
-      <c r="K2" s="136"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-      <c r="N2" s="186" t="s">
+      <c r="N2" s="191" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="187"/>
+      <c r="O2" s="192"/>
       <c r="P2" s="112" t="s">
         <v>601</v>
       </c>
@@ -10479,46 +10558,46 @@
       <c r="J3" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="K3" s="137"/>
+      <c r="K3" s="136"/>
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="176">
+      <c r="N3" s="181">
         <f>COUNTA(H4:H13)</f>
         <v>4</v>
       </c>
-      <c r="O3" s="188"/>
-      <c r="P3" s="204">
+      <c r="O3" s="193"/>
+      <c r="P3" s="209">
         <f>N3-S3</f>
         <v>4</v>
       </c>
-      <c r="Q3" s="191">
+      <c r="Q3" s="196">
         <f>COUNTIF(J4:J10,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="194">
+      <c r="R3" s="199">
         <f>COUNTIF(J4:J11,"No")</f>
         <v>2</v>
       </c>
-      <c r="S3" s="197">
+      <c r="S3" s="202">
         <f>COUNTIF(J4:J10,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="T3" s="191">
+      <c r="T3" s="196">
         <f>Q3/P3</f>
         <v>0.5</v>
       </c>
-      <c r="V3" s="219"/>
-      <c r="W3" s="219"/>
+      <c r="V3" s="151"/>
+      <c r="W3" s="151"/>
     </row>
     <row r="4" spans="1:23" ht="78" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="173" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="173" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="173" t="s">
         <v>102</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -10530,25 +10609,25 @@
       <c r="G4" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="H4" s="172" t="s">
+      <c r="H4" s="177" t="s">
         <v>268</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>544</v>
       </c>
-      <c r="J4" s="168" t="s">
+      <c r="J4" s="173" t="s">
         <v>275</v>
       </c>
-      <c r="K4" s="136"/>
+      <c r="K4" s="135"/>
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
-      <c r="N4" s="177"/>
-      <c r="O4" s="189"/>
-      <c r="P4" s="205"/>
-      <c r="Q4" s="192"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="198"/>
-      <c r="T4" s="192"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="194"/>
+      <c r="P4" s="210"/>
+      <c r="Q4" s="197"/>
+      <c r="R4" s="200"/>
+      <c r="S4" s="203"/>
+      <c r="T4" s="197"/>
       <c r="V4" s="7" t="str">
         <f>IF(J4="No",ROW(), "")</f>
         <v/>
@@ -10560,9 +10639,9 @@
     </row>
     <row r="5" spans="1:23" ht="82.95" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
       <c r="E5" s="12" t="s">
         <v>107</v>
       </c>
@@ -10572,21 +10651,21 @@
       <c r="G5" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="172"/>
+      <c r="H5" s="177"/>
       <c r="I5" s="24" t="s">
         <v>545</v>
       </c>
-      <c r="J5" s="168"/>
+      <c r="J5" s="173"/>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
-      <c r="N5" s="218"/>
-      <c r="O5" s="190"/>
-      <c r="P5" s="206"/>
-      <c r="Q5" s="193"/>
-      <c r="R5" s="196"/>
-      <c r="S5" s="199"/>
-      <c r="T5" s="193"/>
+      <c r="N5" s="223"/>
+      <c r="O5" s="195"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="198"/>
+      <c r="R5" s="201"/>
+      <c r="S5" s="204"/>
+      <c r="T5" s="198"/>
       <c r="V5" s="7" t="str">
         <f t="shared" ref="V5:V11" si="0">IF(J5="No",ROW(), "")</f>
         <v/>
@@ -10598,9 +10677,9 @@
     </row>
     <row r="6" spans="1:23" ht="88.5" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="168"/>
-      <c r="C6" s="168"/>
-      <c r="D6" s="168" t="s">
+      <c r="B6" s="173"/>
+      <c r="C6" s="173"/>
+      <c r="D6" s="173" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -10612,22 +10691,22 @@
       <c r="G6" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H6" s="166" t="s">
+      <c r="H6" s="171" t="s">
         <v>267</v>
       </c>
       <c r="I6" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="J6" s="168" t="s">
+      <c r="J6" s="173" t="s">
         <v>275</v>
       </c>
       <c r="K6" s="50"/>
       <c r="L6" s="50"/>
       <c r="M6" s="50"/>
-      <c r="N6" s="131" t="s">
+      <c r="N6" s="130" t="s">
         <v>611</v>
       </c>
-      <c r="O6" s="130" t="s">
+      <c r="O6" s="129" t="s">
         <v>612</v>
       </c>
       <c r="P6" s="57"/>
@@ -10642,9 +10721,9 @@
     </row>
     <row r="7" spans="1:23" ht="76.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="168"/>
-      <c r="C7" s="168"/>
-      <c r="D7" s="168"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
       <c r="E7" s="12" t="s">
         <v>109</v>
       </c>
@@ -10654,11 +10733,11 @@
       <c r="G7" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="H7" s="167"/>
+      <c r="H7" s="172"/>
       <c r="I7" s="24" t="s">
         <v>539</v>
       </c>
-      <c r="J7" s="168"/>
+      <c r="J7" s="173"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
@@ -10677,9 +10756,9 @@
     </row>
     <row r="8" spans="1:23" ht="98.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="168"/>
-      <c r="C8" s="168"/>
-      <c r="D8" s="168" t="s">
+      <c r="B8" s="173"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173" t="s">
         <v>110</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -10691,13 +10770,13 @@
       <c r="G8" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="H8" s="172" t="s">
+      <c r="H8" s="177" t="s">
         <v>266</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>540</v>
       </c>
-      <c r="J8" s="163" t="s">
+      <c r="J8" s="168" t="s">
         <v>273</v>
       </c>
       <c r="K8" s="50"/>
@@ -10716,9 +10795,9 @@
     </row>
     <row r="9" spans="1:23" ht="75.45" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="168"/>
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
       <c r="E9" s="12" t="s">
         <v>112</v>
       </c>
@@ -10728,11 +10807,11 @@
       <c r="G9" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H9" s="172"/>
+      <c r="H9" s="177"/>
       <c r="I9" s="24" t="s">
         <v>541</v>
       </c>
-      <c r="J9" s="164"/>
+      <c r="J9" s="169"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
@@ -10748,23 +10827,23 @@
     </row>
     <row r="10" spans="1:23" ht="109.95" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="168"/>
-      <c r="C10" s="168"/>
-      <c r="D10" s="168"/>
-      <c r="E10" s="208" t="s">
+      <c r="B10" s="173"/>
+      <c r="C10" s="173"/>
+      <c r="D10" s="173"/>
+      <c r="E10" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="208" t="s">
+      <c r="F10" s="213" t="s">
         <v>227</v>
       </c>
-      <c r="G10" s="209" t="s">
+      <c r="G10" s="214" t="s">
         <v>206</v>
       </c>
-      <c r="H10" s="172"/>
+      <c r="H10" s="177"/>
       <c r="I10" s="24" t="s">
         <v>542</v>
       </c>
-      <c r="J10" s="165"/>
+      <c r="J10" s="170"/>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
@@ -10780,19 +10859,19 @@
     </row>
     <row r="11" spans="1:23" ht="63" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="168"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="168"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="208"/>
-      <c r="G11" s="209"/>
+      <c r="B11" s="173"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="213"/>
+      <c r="F11" s="213"/>
+      <c r="G11" s="214"/>
       <c r="H11" s="2" t="s">
         <v>280</v>
       </c>
       <c r="I11" s="24" t="s">
         <v>543</v>
       </c>
-      <c r="J11" s="132" t="s">
+      <c r="J11" s="131" t="s">
         <v>273</v>
       </c>
       <c r="K11" s="50"/>
@@ -10838,29 +10917,29 @@
     <mergeCell ref="R3:R5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:K3">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J11">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10881,18 +10960,24 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="2" max="2" width="19.77734375" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="5" max="6" width="18.6640625" customWidth="1"/>
     <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="31.6640625" customWidth="1"/>
+    <col min="13" max="13" width="33.109375" customWidth="1"/>
+    <col min="14" max="14" width="38.5546875" customWidth="1"/>
+    <col min="15" max="15" width="29.44140625" customWidth="1"/>
+    <col min="16" max="16" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:16">
       <c r="A1" s="115" t="s">
         <v>148</v>
       </c>
@@ -10920,8 +11005,26 @@
       <c r="I1" s="115" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.55" customHeight="1">
+      <c r="K1" s="116" t="s">
+        <v>595</v>
+      </c>
+      <c r="L1" s="116" t="s">
+        <v>596</v>
+      </c>
+      <c r="M1" s="116" t="s">
+        <v>597</v>
+      </c>
+      <c r="N1" s="116" t="s">
+        <v>598</v>
+      </c>
+      <c r="O1" s="116" t="s">
+        <v>599</v>
+      </c>
+      <c r="P1" s="116" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.55" customHeight="1">
       <c r="A2" s="115" t="s">
         <v>595</v>
       </c>
@@ -10949,16 +11052,40 @@
         <f>'Questionnaire Domain Forensics'!$T$3</f>
         <v>0.5</v>
       </c>
-      <c r="H2" s="120">
+      <c r="H2" s="119">
         <f>PONDERATION!$L$20</f>
         <v>6</v>
       </c>
-      <c r="I2" s="122" t="str">
+      <c r="I2" s="121" t="str">
         <f>'Questionnaire Domain Forensics'!$O$6</f>
         <v>Oumayma</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.55" customHeight="1">
+      <c r="K2" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W4</f>
+        <v>Où sont stockées les preuves et qui peut y accéder ?</v>
+      </c>
+      <c r="L2" s="148" t="str">
+        <f>'Question Continuité d’activité'!W4</f>
+        <v>Comment les processus métiers sont-ils identifiés, priorisés et classifiés ?</v>
+      </c>
+      <c r="M2" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U4</f>
+        <v>La communication peut-elle être maintenue si les systèmes internes sont compromis ?</v>
+      </c>
+      <c r="N2" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U2</f>
+        <v>Is a formal incident logging register or ticketing system implemented to ensure proper tracking, documentation, and traceability of incidents?</v>
+      </c>
+      <c r="O2" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V4</f>
+        <v>Pouvez-vous fournir les rapports d’audit réalisés au cours des 12 derniers mois, ainsi que les preuves de leur dépôt auprès de l’ANSI ?</v>
+      </c>
+      <c r="P2" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X2</f>
+        <v>Les liens entre la gestion de crise, la gestion des incidents, la continuité d’activité et la sécurité sont-ils formalisés ?</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.55" customHeight="1">
       <c r="A3" s="115" t="s">
         <v>596</v>
       </c>
@@ -10986,16 +11113,40 @@
         <f>'Question Continuité d’activité'!$R$3</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="H3" s="120">
+      <c r="H3" s="119">
         <f>PONDERATION!$L$19</f>
         <v>23</v>
       </c>
-      <c r="I3" s="122" t="str">
+      <c r="I3" s="121" t="str">
         <f>'Question Continuité d’activité'!$T$4</f>
         <v>Dhia</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.55" customHeight="1">
+      <c r="K3" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W5</f>
+        <v>Comment l’entreprise s’assure-t-elle que les enregistrements sont complets et n’ont fait l’objet d’aucune altération ?</v>
+      </c>
+      <c r="L3" s="148" t="str">
+        <f>'Question Continuité d’activité'!W5</f>
+        <v>Toutes les dépendances internes et externes, y compris les fournisseurs, partenaires, systèmes informatiques et le personnel, ont-elles été identifiées et intégrées dans le BIA ?</v>
+      </c>
+      <c r="M3" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U5</f>
+        <v>Les membres de la cellule de crise sont-ils identifiés (IT, sécurité, juridique, communication, direction) ?</v>
+      </c>
+      <c r="N3" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U3</f>
+        <v>Comment l’entreprise s’assure-t-elle que les bâtiments hébergeant des systèmes d’information sont physiquement sécurisés, que l’accès physique est contrôlé et limité aux personnes autorisées, et que des systèmes d’alarme et de surveillance sont installés et opérationnels ?</v>
+      </c>
+      <c r="O3" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V5</f>
+        <v>Est-ce que vos équipements électroniques et logiciels, ainsi que vos fournisseurs de services cloud, possèdent respectivement les labels « Sécurisé » et « G-Cloud / N-Cloud » valides délivrés par l’ANSI ?</v>
+      </c>
+      <c r="P3" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X3</f>
+        <v>Le cadre formel de gouvernance de la gestion de crise cyber est-il documenté, daté et approuvé par l’autorité compétente afin de garantir sa validité et son application ?</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14.55" customHeight="1">
       <c r="A4" s="115" t="s">
         <v>597</v>
       </c>
@@ -11023,16 +11174,40 @@
         <f>'Questionnaire Gestion de crise'!$R$3</f>
         <v>0.3</v>
       </c>
-      <c r="H4" s="120">
+      <c r="H4" s="119">
         <f>PONDERATION!$L$18</f>
         <v>20</v>
       </c>
-      <c r="I4" s="122" t="str">
+      <c r="I4" s="121" t="str">
         <f>'Questionnaire Gestion de crise'!$M$7</f>
         <v>Oumayma</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.55" customHeight="1">
+      <c r="K4" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W6</f>
+        <v/>
+      </c>
+      <c r="L4" s="148" t="str">
+        <f>'Question Continuité d’activité'!W6</f>
+        <v>Comment l’entreprise s’assure-t-elle que les équipes connaissent leurs rôles en cas de crise ?</v>
+      </c>
+      <c r="M4" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U6</f>
+        <v>Les rôles et responsabilités sont-ils clairement définis et compris ? Existe-t-il des remplaçants en cas d’indisponibilité ?</v>
+      </c>
+      <c r="N4" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U4</f>
+        <v xml:space="preserve">Les données reçues via les réseaux, supports de stockage ou pièces jointes des emails, sont-elles systématiquement analysées avant utilisation ? </v>
+      </c>
+      <c r="O4" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V6</f>
+        <v>L’organisme dispose-t-il d’un centre de réponse aux urgences (propre ou adhérent) et prend-il les mesures de sécurité requises pour la gestion des infrastructures numériques d’importance vitale ?</v>
+      </c>
+      <c r="P4" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X4</f>
+        <v xml:space="preserve">Exsite t-il des cas specifique ou de periode qui declanche la revision du cadre de gouvernance ? </v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.55" customHeight="1">
       <c r="A5" s="115" t="s">
         <v>598</v>
       </c>
@@ -11046,11 +11221,11 @@
       </c>
       <c r="D5" s="118">
         <f>'Questionnaire Gestion Incidents'!$N$2</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="118">
         <f>'Questionnaire Gestion Incidents'!$N$3</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="118">
         <f>'Questionnaire Gestion Incidents'!$N$4</f>
@@ -11058,18 +11233,42 @@
       </c>
       <c r="G5" s="117">
         <f>'Questionnaire Gestion Incidents'!$L$2</f>
-        <v>0.82352941176470584</v>
-      </c>
-      <c r="H5" s="120">
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="H5" s="119">
         <f>PONDERATION!$L$17</f>
         <v>18.5</v>
       </c>
-      <c r="I5" s="122" t="str">
+      <c r="I5" s="121" t="str">
         <f>'Questionnaire Gestion Incidents'!$N$5</f>
         <v>Oumayma</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.55" customHeight="1">
+      <c r="K5" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W7</f>
+        <v/>
+      </c>
+      <c r="L5" s="148" t="str">
+        <f>'Question Continuité d’activité'!W7</f>
+        <v>Le personnel critique a-t-il été identifié et formé de manière appropriée pour faire face aux perturbations ?</v>
+      </c>
+      <c r="M5" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U7</f>
+        <v>Les outils de monitoring permettent-ils une détection en temps réel des incidents majeurs ?</v>
+      </c>
+      <c r="N5" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U5</f>
+        <v>Les configurations réseau sont-elles sauvegardées et versionnées pour assurer leur intégrité et leur restauration ?</v>
+      </c>
+      <c r="O5" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V7</f>
+        <v/>
+      </c>
+      <c r="P5" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X5</f>
+        <v>Existe-t-il une politique qui definie la modaliter et les ligne a suivre en terme de communication interne et externe dans le cas d'un crise cyber ?</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="14.55" customHeight="1">
       <c r="A6" s="115" t="s">
         <v>599</v>
       </c>
@@ -11097,54 +11296,102 @@
         <f>'Questionnaire Confirmitee'!$R$3</f>
         <v>0.25</v>
       </c>
-      <c r="H6" s="120">
+      <c r="H6" s="119">
         <f>PONDERATION!$L$21</f>
         <v>6</v>
       </c>
-      <c r="I6" s="122" t="str">
+      <c r="I6" s="121" t="str">
         <f>'Questionnaire Confirmitee'!$M$7</f>
         <v>Oumayma</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A7" s="124" t="s">
+      <c r="K6" s="150" t="str">
+        <f>'Questionnaire Domain Forensics'!W8</f>
+        <v/>
+      </c>
+      <c r="L6" s="148" t="str">
+        <f>'Question Continuité d’activité'!W8</f>
+        <v>Quand les scénarios du BIA ont-ils été testés pour la dernière fois et quels types de tests ont été réalisés ?</v>
+      </c>
+      <c r="M6" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U8</f>
+        <v>Combien de temps faut-il en moyenne pour isoler un système compromis ?</v>
+      </c>
+      <c r="N6" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U6</f>
+        <v>Des contrôles d’accès réseau (firewalls, ACL) sont-ils configurés ?</v>
+      </c>
+      <c r="O6" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V8</f>
+        <v/>
+      </c>
+      <c r="P6" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X6</f>
+        <v>Existe-t-il une repartition des  responsabilite pour chaque acteur et procedure operationelles ?</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.55" customHeight="1">
+      <c r="A7" s="123" t="s">
         <v>594</v>
       </c>
-      <c r="B7" s="125">
+      <c r="B7" s="124">
         <f>'Questionnaire Gouvernance '!$Q$2</f>
         <v>35</v>
       </c>
-      <c r="C7" s="125">
+      <c r="C7" s="124">
         <f>'Questionnaire Gouvernance '!$S$2</f>
         <v>35</v>
       </c>
-      <c r="D7" s="125">
+      <c r="D7" s="124">
         <f>'Questionnaire Gouvernance '!$O$2</f>
-        <v>26</v>
-      </c>
-      <c r="E7" s="125">
+        <v>19</v>
+      </c>
+      <c r="E7" s="124">
         <f>'Questionnaire Gouvernance '!$O$3</f>
-        <v>9</v>
-      </c>
-      <c r="F7" s="125">
+        <v>16</v>
+      </c>
+      <c r="F7" s="124">
         <f>'Questionnaire Gouvernance '!$O$4</f>
         <v>0</v>
       </c>
-      <c r="G7" s="126">
+      <c r="G7" s="125">
         <f>'Questionnaire Gouvernance '!$L$2</f>
-        <v>0.74285714285714288</v>
-      </c>
-      <c r="H7" s="127">
+        <v>0.54285714285714282</v>
+      </c>
+      <c r="H7" s="126">
         <f>PONDERATION!$L$16</f>
         <v>26.5</v>
       </c>
-      <c r="I7" s="122" t="str">
+      <c r="I7" s="121" t="str">
         <f>'Questionnaire Gouvernance '!$U$2</f>
         <v>Dhia</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="128" t="s">
+      <c r="K7" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W9</f>
+        <v/>
+      </c>
+      <c r="L7" s="148" t="str">
+        <f>'Question Continuité d’activité'!W9</f>
+        <v/>
+      </c>
+      <c r="M7" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U9</f>
+        <v>Des runbooks sont-ils disponibles pour les scénarios cyber majeurs</v>
+      </c>
+      <c r="N7" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U7</f>
+        <v/>
+      </c>
+      <c r="O7" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V9</f>
+        <v/>
+      </c>
+      <c r="P7" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X7</f>
+        <v>Qui a l'autorite de decision directionnelle en cas de crise cyber? Cette information est t-elle communiqué ?</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15" customHeight="1">
+      <c r="A8" s="127" t="s">
         <v>272</v>
       </c>
       <c r="B8" s="18">
@@ -11157,34 +11404,102 @@
       </c>
       <c r="D8" s="18">
         <f t="shared" ref="D8:F8" si="0">SUM(D2:D7)</f>
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E8" s="18">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F8" s="18">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G8" s="129">
+      <c r="G8" s="128">
         <f>G2*H2+G3*H3+G4*H4+G5*H5+G6*H6+G7*H7</f>
-        <v>55.64323062558357</v>
+        <v>48.166760037348276</v>
       </c>
       <c r="H8" s="18">
         <f>SUM(H2:H7)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="K8" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W10</f>
+        <v/>
+      </c>
+      <c r="L8" s="148" t="str">
+        <f>'Question Continuité d’activité'!W10</f>
+        <v/>
+      </c>
+      <c r="M8" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U10</f>
+        <v>Un prestataire de réponse à incident (IR) est-il contractuellement prévu ?</v>
+      </c>
+      <c r="N8" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U8</f>
+        <v/>
+      </c>
+      <c r="O8" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V10</f>
+        <v/>
+      </c>
+      <c r="P8" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X8</f>
+        <v>Exsite t-il un document formel de plan de contunite d'activite ?</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="28.8">
+      <c r="K9" s="148" t="str">
+        <f>'Questionnaire Domain Forensics'!W11</f>
+        <v/>
+      </c>
+      <c r="L9" s="148" t="str">
+        <f>'Question Continuité d’activité'!W11</f>
+        <v/>
+      </c>
+      <c r="M9" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U11</f>
+        <v>Existe-t-il un mécanisme de communication avec CERT/autorités ?</v>
+      </c>
+      <c r="N9" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U9</f>
+        <v/>
+      </c>
+      <c r="O9" s="148" t="str">
+        <f>'Questionnaire Confirmitee'!V11</f>
+        <v/>
+      </c>
+      <c r="P9" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X9</f>
+        <v>Les versions des documents sont-elles contrôlées et régulièrement mises à jour ?</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="57.6">
       <c r="A10" s="47"/>
       <c r="B10" s="47"/>
       <c r="C10" s="47"/>
       <c r="D10" s="47"/>
       <c r="E10" s="47"/>
       <c r="F10" s="47"/>
-    </row>
-    <row r="11" spans="1:9" ht="21">
+      <c r="K10" s="148"/>
+      <c r="L10" s="148" t="str">
+        <f>'Question Continuité d’activité'!W12</f>
+        <v/>
+      </c>
+      <c r="M10" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U12</f>
+        <v>Comment La coordination avec fournisseurs, cloud providers et partenaires est-elle intégrée dans la gestion de crise ?</v>
+      </c>
+      <c r="N10" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U10</f>
+        <v/>
+      </c>
+      <c r="O10" s="148"/>
+      <c r="P10" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X10</f>
+        <v>Les procédures de sauvegarde et de restauration des données sont-elles formellement documentées</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="28.8">
       <c r="A11" s="108" t="s">
         <v>603</v>
       </c>
@@ -11201,8 +11516,26 @@
         <v>606</v>
       </c>
       <c r="F11" s="114"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="K11" s="148"/>
+      <c r="L11" s="148" t="str">
+        <f>'Question Continuité d’activité'!W13</f>
+        <v/>
+      </c>
+      <c r="M11" s="148" t="str">
+        <f>'Questionnaire Gestion de crise'!U13</f>
+        <v>Le temps de détection (MTTD) et de réponse (MTTR) est-il mesuré ?</v>
+      </c>
+      <c r="N11" s="148" t="str">
+        <f>'Questionnaire Gestion Incidents'!U11</f>
+        <v/>
+      </c>
+      <c r="O11" s="148"/>
+      <c r="P11" s="155" t="str">
+        <f>'Questionnaire Gouvernance '!X11</f>
+        <v>Des stratégies de reprise sont-elles définies pour chaque processus critique</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="116">
         <v>1</v>
       </c>
@@ -11218,8 +11551,24 @@
       <c r="E12" s="107">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="L12" s="73" t="str">
+        <f>'Question Continuité d’activité'!W14</f>
+        <v/>
+      </c>
+      <c r="M12" s="73" t="str">
+        <f>'Questionnaire Gestion de crise'!U14</f>
+        <v/>
+      </c>
+      <c r="N12" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U12</f>
+        <v/>
+      </c>
+      <c r="P12" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X12</f>
+        <v>Les résultats des tests sont-ils formellement documentés et analysés afin d’identifier les écarts et axes d’amélioration ?</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="116">
         <v>2</v>
       </c>
@@ -11235,8 +11584,24 @@
       <c r="E13" s="107">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="L13" s="73" t="str">
+        <f>'Question Continuité d’activité'!W15</f>
+        <v/>
+      </c>
+      <c r="M13" s="73" t="str">
+        <f>'Questionnaire Gestion de crise'!U15</f>
+        <v/>
+      </c>
+      <c r="N13" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U13</f>
+        <v/>
+      </c>
+      <c r="P13" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X13</f>
+        <v>Les employés sont-ils sensibilisés au PCA et à leurs rôles</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="116">
         <v>3</v>
       </c>
@@ -11252,8 +11617,20 @@
       <c r="E14" s="107">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="L14" s="73" t="str">
+        <f>'Question Continuité d’activité'!W16</f>
+        <v/>
+      </c>
+      <c r="N14" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U14</f>
+        <v/>
+      </c>
+      <c r="P14" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X14</f>
+        <v>Les choix de stratégies de continuité sont-ils formellement justifiés (coût, efficacité, risques) afin de garantir des décisions adaptées et optimisées ?</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="116">
         <v>4</v>
       </c>
@@ -11269,8 +11646,20 @@
       <c r="E15" s="107">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="L15" s="73" t="str">
+        <f>'Question Continuité d’activité'!W17</f>
+        <v/>
+      </c>
+      <c r="N15" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U15</f>
+        <v/>
+      </c>
+      <c r="P15" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X15</f>
+        <v>Existe-t-il une grille formelle de qualification des incidents?</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="116">
         <v>5</v>
       </c>
@@ -11286,8 +11675,20 @@
       <c r="E16" s="107">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="L16" s="73" t="str">
+        <f>'Question Continuité d’activité'!W18</f>
+        <v/>
+      </c>
+      <c r="N16" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U16</f>
+        <v/>
+      </c>
+      <c r="P16" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X16</f>
+        <v>Des seuils d’escalade vers la gestion de crise sont-ils définis afin de déclencher rapidement les actions appropriées ?</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="116">
         <v>6</v>
       </c>
@@ -11303,39 +11704,185 @@
       <c r="E17" s="107">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="141" t="s">
-        <v>595</v>
-      </c>
-      <c r="B20" s="141" t="s">
-        <v>596</v>
-      </c>
-      <c r="C20" s="141" t="s">
-        <v>597</v>
-      </c>
-      <c r="D20" s="141" t="s">
-        <v>598</v>
-      </c>
-      <c r="E20" s="141" t="s">
-        <v>599</v>
-      </c>
-      <c r="F20" s="141" t="s">
-        <v>594</v>
-      </c>
-      <c r="G20" s="140"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="138"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="139"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="138"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="138"/>
+      <c r="L17" s="73" t="str">
+        <f>'Question Continuité d’activité'!W19</f>
+        <v/>
+      </c>
+      <c r="N17" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U17</f>
+        <v/>
+      </c>
+      <c r="P17" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X17</f>
+        <v>Existe-t-il des playbooks formels de confinement et de réponse pour les scénarios d’incidents majeurs afin de guider les actions et réduire les erreurs opérationnelles ?</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="L18" s="73" t="str">
+        <f>'Question Continuité d’activité'!W20</f>
+        <v/>
+      </c>
+      <c r="N18" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U18</f>
+        <v/>
+      </c>
+      <c r="P18" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="L19" s="73" t="str">
+        <f>'Question Continuité d’activité'!W21</f>
+        <v/>
+      </c>
+      <c r="N19" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U19</f>
+        <v/>
+      </c>
+      <c r="P19" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="G20" s="137"/>
+      <c r="L20" s="73" t="str">
+        <f>'Question Continuité d’activité'!W22</f>
+        <v/>
+      </c>
+      <c r="N20" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U20</f>
+        <v/>
+      </c>
+      <c r="P20" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="73" t="str">
+        <f>'Question Continuité d’activité'!W23</f>
+        <v/>
+      </c>
+      <c r="D40" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U21</f>
+        <v/>
+      </c>
+      <c r="F40" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="73" t="str">
+        <f>'Question Continuité d’activité'!W24</f>
+        <v/>
+      </c>
+      <c r="D41" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U22</f>
+        <v/>
+      </c>
+      <c r="F41" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="73" t="str">
+        <f>'Question Continuité d’activité'!W25</f>
+        <v/>
+      </c>
+      <c r="D42" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U23</f>
+        <v/>
+      </c>
+      <c r="F42" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="D43" s="73" t="str">
+        <f>'Questionnaire Gestion Incidents'!U24</f>
+        <v/>
+      </c>
+      <c r="F43" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="F44" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="F45" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="F46" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="F47" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="F48" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="6:6">
+      <c r="F49" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="6:6">
+      <c r="F50" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="6:6">
+      <c r="F51" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="6:6">
+      <c r="F52" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="6:6">
+      <c r="F53" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="6:6">
+      <c r="F54" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="6:6">
+      <c r="F55" s="154" t="str">
+        <f>'Questionnaire Gouvernance '!X36</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
